--- a/jogos_2026-08-19.xlsx
+++ b/jogos_2026-08-19.xlsx
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.76</v>
+        <v>2.2</v>
       </c>
       <c r="O22">
-        <v>3.66</v>
+        <v>3.6</v>
       </c>
       <c r="P22">
-        <v>5.44</v>
+        <v>2.8</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -3940,10 +3940,10 @@
         <v>0</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.21</v>
+        <v>1.91</v>
       </c>
       <c r="O23">
-        <v>3.49</v>
+        <v>3.7</v>
       </c>
       <c r="P23">
-        <v>3.49</v>
+        <v>4.29</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -4097,10 +4097,10 @@
         <v>0</v>
       </c>
       <c r="AA23">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AB23">
-        <v>1.89</v>
+        <v>1.97</v>
       </c>
       <c r="AC23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.91</v>
+        <v>1.76</v>
       </c>
       <c r="O24">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="P24">
-        <v>4.29</v>
+        <v>5.44</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4260,10 +4260,10 @@
         <v>0</v>
       </c>
       <c r="AA24">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB24">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AC24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="O25">
-        <v>3.6</v>
+        <v>3.49</v>
       </c>
       <c r="P25">
-        <v>2.8</v>
+        <v>3.49</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4423,16 +4423,16 @@
         <v>0</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC25">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD25">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE25">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.13</v>
+        <v>1.58</v>
       </c>
       <c r="O34">
-        <v>4.36</v>
+        <v>4.8</v>
       </c>
       <c r="P34">
-        <v>3.01</v>
+        <v>5.25</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -5896,10 +5896,10 @@
         <v>0</v>
       </c>
       <c r="AC34">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AD34">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AE34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.58</v>
+        <v>2.37</v>
       </c>
       <c r="O35">
-        <v>4.8</v>
+        <v>4.02</v>
       </c>
       <c r="P35">
-        <v>5.25</v>
+        <v>2.78</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6053,16 +6053,16 @@
         <v>0</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC35">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD35">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.37</v>
+        <v>2.68</v>
       </c>
       <c r="O36">
-        <v>4.02</v>
+        <v>3.99</v>
       </c>
       <c r="P36">
-        <v>2.78</v>
+        <v>2.45</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6216,16 +6216,16 @@
         <v>0</v>
       </c>
       <c r="AA36">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB36">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="O37">
-        <v>3.99</v>
+        <v>4.23</v>
       </c>
       <c r="P37">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6385,10 +6385,10 @@
         <v>0</v>
       </c>
       <c r="AC37">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AD37">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AE37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.8</v>
+        <v>2.13</v>
       </c>
       <c r="O38">
-        <v>4.23</v>
+        <v>4.36</v>
       </c>
       <c r="P38">
-        <v>2.29</v>
+        <v>3.01</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6548,10 +6548,10 @@
         <v>0</v>
       </c>
       <c r="AC38">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AD38">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AE38">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O50">
-        <v>4.59</v>
+        <v>5.11</v>
       </c>
       <c r="P50">
-        <v>3.2</v>
+        <v>5.96</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -8504,10 +8504,10 @@
         <v>0</v>
       </c>
       <c r="AC50">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AD50">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AE50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.5</v>
+        <v>2.45</v>
       </c>
       <c r="O51">
-        <v>5.11</v>
+        <v>4.29</v>
       </c>
       <c r="P51">
-        <v>5.96</v>
+        <v>2.57</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -8667,10 +8667,10 @@
         <v>0</v>
       </c>
       <c r="AC51">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AD51">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AE51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="O52">
-        <v>4.29</v>
+        <v>4.59</v>
       </c>
       <c r="P52">
-        <v>2.57</v>
+        <v>3.2</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -8830,10 +8830,10 @@
         <v>0</v>
       </c>
       <c r="AC52">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AD52">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AE52">
         <v>0</v>

--- a/jogos_2026-08-19.xlsx
+++ b/jogos_2026-08-19.xlsx
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="O38">
-        <v>4.36</v>
+        <v>4</v>
       </c>
       <c r="P38">
-        <v>3.01</v>
+        <v>3.38</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6542,16 +6542,16 @@
         <v>0</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC38">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD38">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="O39">
-        <v>4</v>
+        <v>4.36</v>
       </c>
       <c r="P39">
-        <v>3.38</v>
+        <v>3.01</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -6705,16 +6705,16 @@
         <v>0</v>
       </c>
       <c r="AA39">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB39">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE39">
         <v>0</v>

--- a/jogos_2026-08-19.xlsx
+++ b/jogos_2026-08-19.xlsx
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -6829,13 +6829,13 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -6868,10 +6868,10 @@
         <v>0</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC40">
         <v>0</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7031,10 +7031,10 @@
         <v>0</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC41">
         <v>0</v>
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q45">
         <v>0</v>

--- a/jogos_2026-08-19.xlsx
+++ b/jogos_2026-08-19.xlsx
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G6">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G7">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="O51">
-        <v>4.29</v>
+        <v>4.59</v>
       </c>
       <c r="P51">
-        <v>2.57</v>
+        <v>3.2</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -8667,10 +8667,10 @@
         <v>0</v>
       </c>
       <c r="AC51">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AD51">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AE51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="O52">
-        <v>4.59</v>
+        <v>4.29</v>
       </c>
       <c r="P52">
-        <v>3.2</v>
+        <v>2.57</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -8830,10 +8830,10 @@
         <v>0</v>
       </c>
       <c r="AC52">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AD52">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AE52">
         <v>0</v>

--- a/jogos_2026-08-19.xlsx
+++ b/jogos_2026-08-19.xlsx
@@ -3089,55 +3089,55 @@
         <v>12.84</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5208,55 +5208,55 @@
         <v>2.35</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -6838,34 +6838,34 @@
         <v>3.38</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA40">
         <v>2.4</v>
@@ -6874,19 +6874,19 @@
         <v>1.5</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7001,34 +7001,34 @@
         <v>8.6</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA41">
         <v>1.71</v>
@@ -7037,19 +7037,19 @@
         <v>2</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7653,55 +7653,55 @@
         <v>2.66</v>
       </c>
       <c r="Q45">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R45">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S45">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T45">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U45">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="V45">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W45">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X45">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y45">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z45">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC45">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD45">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE45">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF45">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG45">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK45">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL45">
         <v>0</v>

--- a/jogos_2026-08-19.xlsx
+++ b/jogos_2026-08-19.xlsx
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>LASK Linz</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.2</v>
+        <v>1.76</v>
       </c>
       <c r="O22">
-        <v>3.6</v>
+        <v>3.66</v>
       </c>
       <c r="P22">
-        <v>2.8</v>
+        <v>5.44</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC22">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="AD22">
-        <v>1.65</v>
+        <v>1.35</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="O23">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P23">
-        <v>4.29</v>
+        <v>2.8</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA23">
-        <v>1.78</v>
+        <v>1.44</v>
       </c>
       <c r="AB23">
-        <v>1.97</v>
+        <v>2.7</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>LASK Linz</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="O24">
-        <v>3.66</v>
+        <v>3.7</v>
       </c>
       <c r="P24">
-        <v>5.44</v>
+        <v>4.29</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4393,34 +4393,34 @@
         <v>3.49</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA25">
         <v>1.85</v>
@@ -4429,19 +4429,19 @@
         <v>1.89</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -5697,40 +5697,40 @@
         <v>2</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC33">
         <v>1.9</v>
@@ -5739,13 +5739,13 @@
         <v>1.9</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5860,40 +5860,40 @@
         <v>5.25</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AC34">
         <v>2.25</v>
@@ -5902,13 +5902,13 @@
         <v>1.57</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6023,34 +6023,34 @@
         <v>2.78</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA35">
         <v>1.6</v>
@@ -6059,19 +6059,19 @@
         <v>2.15</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="O36">
-        <v>3.99</v>
+        <v>4.23</v>
       </c>
       <c r="P36">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC36">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="AD36">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.8</v>
+        <v>2.06</v>
       </c>
       <c r="O37">
-        <v>4.23</v>
+        <v>4</v>
       </c>
       <c r="P37">
-        <v>2.29</v>
+        <v>3.38</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6379,16 +6379,16 @@
         <v>0</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC37">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD37">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="O38">
-        <v>4</v>
+        <v>4.36</v>
       </c>
       <c r="P38">
-        <v>3.38</v>
+        <v>3.01</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AA38">
-        <v>1.68</v>
+        <v>1.38</v>
       </c>
       <c r="AB38">
-        <v>2.05</v>
+        <v>2.8</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.13</v>
+        <v>2.68</v>
       </c>
       <c r="O39">
-        <v>4.36</v>
+        <v>3.99</v>
       </c>
       <c r="P39">
-        <v>3.01</v>
+        <v>2.45</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC39">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AD39">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.18</v>
+        <v>1.36</v>
       </c>
       <c r="O40">
-        <v>3.14</v>
+        <v>4.5</v>
       </c>
       <c r="P40">
-        <v>3.38</v>
+        <v>8.6</v>
       </c>
       <c r="Q40">
-        <v>2.86</v>
+        <v>1.8</v>
       </c>
       <c r="R40">
-        <v>1.93</v>
+        <v>2.29</v>
       </c>
       <c r="S40">
+        <v>1.33</v>
+      </c>
+      <c r="T40">
+        <v>2.99</v>
+      </c>
+      <c r="U40">
+        <v>2.53</v>
+      </c>
+      <c r="V40">
         <v>1.45</v>
       </c>
-      <c r="T40">
-        <v>2.38</v>
-      </c>
-      <c r="U40">
-        <v>3.42</v>
-      </c>
-      <c r="V40">
-        <v>1.26</v>
-      </c>
       <c r="W40">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X40">
         <v>1.03</v>
       </c>
       <c r="Y40">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="Z40">
-        <v>2.55</v>
+        <v>3.82</v>
       </c>
       <c r="AA40">
-        <v>2.4</v>
+        <v>1.71</v>
       </c>
       <c r="AB40">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AC40">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="AD40">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="AE40">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="AF40">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AG40">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="AK40">
-        <v>1.62</v>
+        <v>2.96</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.36</v>
+        <v>2.18</v>
       </c>
       <c r="O41">
-        <v>4.5</v>
+        <v>3.14</v>
       </c>
       <c r="P41">
-        <v>8.6</v>
+        <v>3.38</v>
       </c>
       <c r="Q41">
-        <v>1.8</v>
+        <v>2.86</v>
       </c>
       <c r="R41">
-        <v>2.29</v>
+        <v>1.93</v>
       </c>
       <c r="S41">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="T41">
-        <v>2.99</v>
+        <v>2.38</v>
       </c>
       <c r="U41">
-        <v>2.53</v>
+        <v>3.42</v>
       </c>
       <c r="V41">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="W41">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X41">
         <v>1.03</v>
       </c>
       <c r="Y41">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="Z41">
-        <v>3.82</v>
+        <v>2.55</v>
       </c>
       <c r="AA41">
-        <v>1.71</v>
+        <v>2.4</v>
       </c>
       <c r="AB41">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AC41">
-        <v>2.7</v>
+        <v>4.6</v>
       </c>
       <c r="AD41">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AE41">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="AF41">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AG41">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="AK41">
-        <v>2.96</v>
+        <v>1.62</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7327,40 +7327,40 @@
         <v>2.07</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AC43">
         <v>2.15</v>
@@ -7369,13 +7369,13 @@
         <v>1.61</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7490,34 +7490,34 @@
         <v>4.62</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA44">
         <v>1.62</v>
@@ -7526,19 +7526,19 @@
         <v>2.15</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7816,34 +7816,34 @@
         <v>4.94</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA46">
         <v>1.58</v>
@@ -7852,19 +7852,19 @@
         <v>2.2</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.78</v>
+        <v>1.88</v>
       </c>
       <c r="O47">
-        <v>4.03</v>
+        <v>4.41</v>
       </c>
       <c r="P47">
-        <v>2.37</v>
+        <v>3.67</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA47">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AB47">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.88</v>
+        <v>2.78</v>
       </c>
       <c r="O48">
-        <v>4.41</v>
+        <v>4.03</v>
       </c>
       <c r="P48">
-        <v>3.67</v>
+        <v>2.37</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC48">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="AD48">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8468,40 +8468,40 @@
         <v>5.96</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AC50">
         <v>2.15</v>
@@ -8510,13 +8510,13 @@
         <v>1.6</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8631,40 +8631,40 @@
         <v>3.2</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC51">
         <v>1.83</v>
@@ -8673,13 +8673,13 @@
         <v>1.85</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8794,40 +8794,40 @@
         <v>2.57</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AC52">
         <v>2.05</v>
@@ -8836,13 +8836,13 @@
         <v>1.66</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL52">
         <v>0</v>

--- a/jogos_2026-08-19.xlsx
+++ b/jogos_2026-08-19.xlsx
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.8</v>
+        <v>2.06</v>
       </c>
       <c r="O36">
-        <v>4.23</v>
+        <v>4</v>
       </c>
       <c r="P36">
-        <v>2.29</v>
+        <v>3.38</v>
       </c>
       <c r="Q36">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R36">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S36">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T36">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U36">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V36">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="W36">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X36">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y36">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z36">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA36">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="AB36">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="AC36">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD36">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE36">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AF36">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG36">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK36">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.06</v>
+        <v>2.68</v>
       </c>
       <c r="O37">
+        <v>3.99</v>
+      </c>
+      <c r="P37">
+        <v>2.45</v>
+      </c>
+      <c r="Q37">
+        <v>2.8</v>
+      </c>
+      <c r="R37">
+        <v>2.5</v>
+      </c>
+      <c r="S37">
+        <v>1.19</v>
+      </c>
+      <c r="T37">
         <v>4</v>
       </c>
-      <c r="P37">
-        <v>3.38</v>
-      </c>
-      <c r="Q37">
-        <v>0</v>
-      </c>
-      <c r="R37">
-        <v>0</v>
-      </c>
-      <c r="S37">
-        <v>0</v>
-      </c>
-      <c r="T37">
-        <v>0</v>
-      </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA37">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="AB37">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,80 +6503,80 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.13</v>
+        <v>2.8</v>
       </c>
       <c r="O38">
-        <v>4.36</v>
+        <v>4.23</v>
       </c>
       <c r="P38">
-        <v>3.01</v>
+        <v>2.29</v>
       </c>
       <c r="Q38">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="R38">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="S38">
+        <v>1.25</v>
+      </c>
+      <c r="T38">
+        <v>3.8</v>
+      </c>
+      <c r="U38">
+        <v>2.2</v>
+      </c>
+      <c r="V38">
+        <v>1.58</v>
+      </c>
+      <c r="W38">
+        <v>1.14</v>
+      </c>
+      <c r="X38">
+        <v>1.03</v>
+      </c>
+      <c r="Y38">
+        <v>1.15</v>
+      </c>
+      <c r="Z38">
+        <v>5.5</v>
+      </c>
+      <c r="AA38">
+        <v>1.5</v>
+      </c>
+      <c r="AB38">
+        <v>2.55</v>
+      </c>
+      <c r="AC38">
+        <v>2.2</v>
+      </c>
+      <c r="AD38">
+        <v>1.58</v>
+      </c>
+      <c r="AE38">
+        <v>1.23</v>
+      </c>
+      <c r="AF38">
+        <v>1.44</v>
+      </c>
+      <c r="AG38">
+        <v>2.58</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38">
         <v>1.22</v>
       </c>
-      <c r="T38">
-        <v>4.1</v>
-      </c>
-      <c r="U38">
-        <v>2.02</v>
-      </c>
-      <c r="V38">
-        <v>1.67</v>
-      </c>
-      <c r="W38">
-        <v>1.18</v>
-      </c>
-      <c r="X38">
-        <v>1.02</v>
-      </c>
-      <c r="Y38">
-        <v>1.11</v>
-      </c>
-      <c r="Z38">
-        <v>6.1</v>
-      </c>
-      <c r="AA38">
-        <v>1.38</v>
-      </c>
-      <c r="AB38">
-        <v>2.8</v>
-      </c>
-      <c r="AC38">
-        <v>2</v>
-      </c>
-      <c r="AD38">
-        <v>1.7</v>
-      </c>
-      <c r="AE38">
-        <v>1.29</v>
-      </c>
-      <c r="AF38">
-        <v>1.4</v>
-      </c>
-      <c r="AG38">
-        <v>2.75</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ38">
-        <v>1.36</v>
-      </c>
       <c r="AK38">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,80 +6666,80 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.68</v>
+        <v>2.13</v>
       </c>
       <c r="O39">
-        <v>3.99</v>
+        <v>4.36</v>
       </c>
       <c r="P39">
+        <v>3.01</v>
+      </c>
+      <c r="Q39">
         <v>2.45</v>
       </c>
-      <c r="Q39">
-        <v>2.8</v>
-      </c>
       <c r="R39">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S39">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="T39">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="U39">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="V39">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="W39">
         <v>1.18</v>
       </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y39">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z39">
-        <v>5.75</v>
+        <v>6.1</v>
       </c>
       <c r="AA39">
+        <v>1.38</v>
+      </c>
+      <c r="AB39">
+        <v>2.8</v>
+      </c>
+      <c r="AC39">
+        <v>2</v>
+      </c>
+      <c r="AD39">
+        <v>1.7</v>
+      </c>
+      <c r="AE39">
+        <v>1.29</v>
+      </c>
+      <c r="AF39">
         <v>1.4</v>
       </c>
-      <c r="AB39">
+      <c r="AG39">
         <v>2.75</v>
       </c>
-      <c r="AC39">
-        <v>1.98</v>
-      </c>
-      <c r="AD39">
-        <v>1.73</v>
-      </c>
-      <c r="AE39">
-        <v>1.3</v>
-      </c>
-      <c r="AF39">
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39">
         <v>1.36</v>
       </c>
-      <c r="AG39">
-        <v>2.8</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39">
-        <v>1.24</v>
-      </c>
       <c r="AK39">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.36</v>
+        <v>2.18</v>
       </c>
       <c r="O40">
-        <v>4.5</v>
+        <v>3.14</v>
       </c>
       <c r="P40">
-        <v>8.6</v>
+        <v>3.38</v>
       </c>
       <c r="Q40">
-        <v>1.8</v>
+        <v>2.86</v>
       </c>
       <c r="R40">
-        <v>2.29</v>
+        <v>1.93</v>
       </c>
       <c r="S40">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="T40">
-        <v>2.99</v>
+        <v>2.38</v>
       </c>
       <c r="U40">
-        <v>2.53</v>
+        <v>3.42</v>
       </c>
       <c r="V40">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="W40">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X40">
         <v>1.03</v>
       </c>
       <c r="Y40">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="Z40">
-        <v>3.82</v>
+        <v>2.55</v>
       </c>
       <c r="AA40">
-        <v>1.71</v>
+        <v>2.4</v>
       </c>
       <c r="AB40">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AC40">
-        <v>2.7</v>
+        <v>4.6</v>
       </c>
       <c r="AD40">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AE40">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="AF40">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AG40">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="AK40">
-        <v>2.96</v>
+        <v>1.62</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.18</v>
+        <v>1.36</v>
       </c>
       <c r="O41">
-        <v>3.14</v>
+        <v>4.5</v>
       </c>
       <c r="P41">
-        <v>3.38</v>
+        <v>8.6</v>
       </c>
       <c r="Q41">
-        <v>2.86</v>
+        <v>1.8</v>
       </c>
       <c r="R41">
-        <v>1.93</v>
+        <v>2.29</v>
       </c>
       <c r="S41">
+        <v>1.33</v>
+      </c>
+      <c r="T41">
+        <v>2.99</v>
+      </c>
+      <c r="U41">
+        <v>2.53</v>
+      </c>
+      <c r="V41">
         <v>1.45</v>
       </c>
-      <c r="T41">
-        <v>2.38</v>
-      </c>
-      <c r="U41">
-        <v>3.42</v>
-      </c>
-      <c r="V41">
-        <v>1.26</v>
-      </c>
       <c r="W41">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X41">
         <v>1.03</v>
       </c>
       <c r="Y41">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="Z41">
-        <v>2.55</v>
+        <v>3.82</v>
       </c>
       <c r="AA41">
-        <v>2.4</v>
+        <v>1.71</v>
       </c>
       <c r="AB41">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AC41">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="AD41">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="AE41">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="AF41">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AG41">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="AK41">
-        <v>1.62</v>
+        <v>2.96</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O50">
-        <v>5.11</v>
+        <v>4.59</v>
       </c>
       <c r="P50">
-        <v>5.96</v>
+        <v>3.2</v>
       </c>
       <c r="Q50">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="R50">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="S50">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="T50">
-        <v>3.9</v>
+        <v>4.45</v>
       </c>
       <c r="U50">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="V50">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="W50">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="X50">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Z50">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AA50">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="AB50">
-        <v>2.51</v>
+        <v>3.1</v>
       </c>
       <c r="AC50">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="AD50">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AE50">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AF50">
-        <v>1.57</v>
+        <v>1.33</v>
       </c>
       <c r="AG50">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK50">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="O51">
-        <v>4.59</v>
+        <v>4.29</v>
       </c>
       <c r="P51">
-        <v>3.2</v>
+        <v>2.57</v>
       </c>
       <c r="Q51">
-        <v>2.3</v>
+        <v>2.78</v>
       </c>
       <c r="R51">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="S51">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="T51">
-        <v>4.45</v>
+        <v>4</v>
       </c>
       <c r="U51">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="V51">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="W51">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="X51">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z51">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AA51">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AB51">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="AC51">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AD51">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AE51">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AF51">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AG51">
-        <v>3</v>
+        <v>2.76</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>1.2</v>
       </c>
       <c r="AK51">
-        <v>1.8</v>
+        <v>1.56</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.45</v>
+        <v>1.5</v>
       </c>
       <c r="O52">
-        <v>4.29</v>
+        <v>5.11</v>
       </c>
       <c r="P52">
-        <v>2.57</v>
+        <v>5.96</v>
       </c>
       <c r="Q52">
-        <v>2.78</v>
+        <v>1.91</v>
       </c>
       <c r="R52">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="S52">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T52">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U52">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="V52">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W52">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X52">
         <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z52">
         <v>6</v>
       </c>
       <c r="AA52">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AB52">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="AC52">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AD52">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AE52">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AF52">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="AG52">
-        <v>2.76</v>
+        <v>2.2</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK52">
-        <v>1.56</v>
+        <v>2.6</v>
       </c>
       <c r="AL52">
         <v>0</v>

--- a/jogos_2026-08-19.xlsx
+++ b/jogos_2026-08-19.xlsx
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Slovan Bratislava</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,80 +4058,80 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="O23">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P23">
-        <v>2.8</v>
+        <v>4.29</v>
       </c>
       <c r="Q23">
-        <v>3.02</v>
+        <v>2.18</v>
       </c>
       <c r="R23">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S23">
+        <v>1.3</v>
+      </c>
+      <c r="T23">
+        <v>3.25</v>
+      </c>
+      <c r="U23">
+        <v>2.52</v>
+      </c>
+      <c r="V23">
+        <v>1.48</v>
+      </c>
+      <c r="W23">
+        <v>1.11</v>
+      </c>
+      <c r="X23">
+        <v>1.04</v>
+      </c>
+      <c r="Y23">
+        <v>1.25</v>
+      </c>
+      <c r="Z23">
+        <v>3.8</v>
+      </c>
+      <c r="AA23">
+        <v>1.78</v>
+      </c>
+      <c r="AB23">
+        <v>1.97</v>
+      </c>
+      <c r="AC23">
+        <v>2.9</v>
+      </c>
+      <c r="AD23">
+        <v>1.36</v>
+      </c>
+      <c r="AE23">
+        <v>1.09</v>
+      </c>
+      <c r="AF23">
+        <v>1.7</v>
+      </c>
+      <c r="AG23">
+        <v>2</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
         <v>1.22</v>
       </c>
-      <c r="T23">
-        <v>3.75</v>
-      </c>
-      <c r="U23">
-        <v>2.03</v>
-      </c>
-      <c r="V23">
-        <v>1.7</v>
-      </c>
-      <c r="W23">
-        <v>1.17</v>
-      </c>
-      <c r="X23">
-        <v>1.02</v>
-      </c>
-      <c r="Y23">
-        <v>1.13</v>
-      </c>
-      <c r="Z23">
-        <v>6</v>
-      </c>
-      <c r="AA23">
-        <v>1.44</v>
-      </c>
-      <c r="AB23">
-        <v>2.7</v>
-      </c>
-      <c r="AC23">
-        <v>2.1</v>
-      </c>
-      <c r="AD23">
-        <v>1.65</v>
-      </c>
-      <c r="AE23">
-        <v>1.27</v>
-      </c>
-      <c r="AF23">
-        <v>1.36</v>
-      </c>
-      <c r="AG23">
-        <v>2.75</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23">
-        <v>1.4</v>
-      </c>
       <c r="AK23">
-        <v>1.47</v>
+        <v>2.04</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Slovan Bratislava</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,61 +4221,61 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.91</v>
+        <v>2.21</v>
       </c>
       <c r="O24">
-        <v>3.7</v>
+        <v>3.49</v>
       </c>
       <c r="P24">
-        <v>4.29</v>
+        <v>3.49</v>
       </c>
       <c r="Q24">
-        <v>2.18</v>
+        <v>2.85</v>
       </c>
       <c r="R24">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S24">
+        <v>1.36</v>
+      </c>
+      <c r="T24">
+        <v>2.66</v>
+      </c>
+      <c r="U24">
+        <v>2.78</v>
+      </c>
+      <c r="V24">
+        <v>1.41</v>
+      </c>
+      <c r="W24">
+        <v>1.1</v>
+      </c>
+      <c r="X24">
+        <v>1.05</v>
+      </c>
+      <c r="Y24">
         <v>1.3</v>
       </c>
-      <c r="T24">
-        <v>3.25</v>
-      </c>
-      <c r="U24">
-        <v>2.52</v>
-      </c>
-      <c r="V24">
-        <v>1.48</v>
-      </c>
-      <c r="W24">
-        <v>1.11</v>
-      </c>
-      <c r="X24">
-        <v>1.04</v>
-      </c>
-      <c r="Y24">
-        <v>1.25</v>
-      </c>
       <c r="Z24">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="AA24">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AB24">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="AC24">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="AD24">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE24">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AF24">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AG24">
         <v>2</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="AK24">
-        <v>2.04</v>
+        <v>1.57</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="O25">
-        <v>3.49</v>
+        <v>3.6</v>
       </c>
       <c r="P25">
-        <v>3.49</v>
+        <v>2.8</v>
       </c>
       <c r="Q25">
-        <v>2.85</v>
+        <v>3.02</v>
       </c>
       <c r="R25">
+        <v>2.38</v>
+      </c>
+      <c r="S25">
+        <v>1.22</v>
+      </c>
+      <c r="T25">
+        <v>3.75</v>
+      </c>
+      <c r="U25">
+        <v>2.03</v>
+      </c>
+      <c r="V25">
+        <v>1.7</v>
+      </c>
+      <c r="W25">
+        <v>1.17</v>
+      </c>
+      <c r="X25">
+        <v>1.02</v>
+      </c>
+      <c r="Y25">
+        <v>1.13</v>
+      </c>
+      <c r="Z25">
+        <v>6</v>
+      </c>
+      <c r="AA25">
+        <v>1.44</v>
+      </c>
+      <c r="AB25">
+        <v>2.7</v>
+      </c>
+      <c r="AC25">
         <v>2.1</v>
       </c>
-      <c r="S25">
+      <c r="AD25">
+        <v>1.65</v>
+      </c>
+      <c r="AE25">
+        <v>1.27</v>
+      </c>
+      <c r="AF25">
         <v>1.36</v>
       </c>
-      <c r="T25">
-        <v>2.66</v>
-      </c>
-      <c r="U25">
-        <v>2.78</v>
-      </c>
-      <c r="V25">
-        <v>1.41</v>
-      </c>
-      <c r="W25">
-        <v>1.1</v>
-      </c>
-      <c r="X25">
-        <v>1.05</v>
-      </c>
-      <c r="Y25">
-        <v>1.3</v>
-      </c>
-      <c r="Z25">
-        <v>3.1</v>
-      </c>
-      <c r="AA25">
-        <v>1.85</v>
-      </c>
-      <c r="AB25">
-        <v>1.89</v>
-      </c>
-      <c r="AC25">
-        <v>3.3</v>
-      </c>
-      <c r="AD25">
-        <v>1.3</v>
-      </c>
-      <c r="AE25">
-        <v>1.06</v>
-      </c>
-      <c r="AF25">
-        <v>1.75</v>
-      </c>
       <c r="AG25">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AK25">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AL25">
         <v>0</v>

--- a/jogos_2026-08-19.xlsx
+++ b/jogos_2026-08-19.xlsx
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="O2">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="P2">
         <v>3.5</v>
       </c>
       <c r="Q2">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="R2">
-        <v>2.3</v>
+        <v>2.54</v>
       </c>
       <c r="S2">
         <v>1.22</v>
@@ -656,13 +656,13 @@
         <v>3.8</v>
       </c>
       <c r="U2">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V2">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="W2">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X2">
         <v>1.03</v>
@@ -671,7 +671,7 @@
         <v>1.17</v>
       </c>
       <c r="Z2">
-        <v>4.4</v>
+        <v>6.98</v>
       </c>
       <c r="AA2">
         <v>1.57</v>
@@ -683,10 +683,10 @@
         <v>2.38</v>
       </c>
       <c r="AD2">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AE2">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AF2">
         <v>1.45</v>
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="O17">
         <v>6.4</v>
@@ -3098,7 +3098,7 @@
         <v>1.25</v>
       </c>
       <c r="T17">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U17">
         <v>2.3</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AK17">
         <v>4</v>
@@ -3406,25 +3406,25 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="O19">
         <v>2.65</v>
       </c>
       <c r="P19">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="Q19">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="R19">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="S19">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="T19">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="U19">
         <v>3.75</v>
@@ -3445,16 +3445,16 @@
         <v>2.23</v>
       </c>
       <c r="AA19">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AB19">
         <v>1.36</v>
       </c>
       <c r="AC19">
-        <v>6.15</v>
+        <v>5.5</v>
       </c>
       <c r="AD19">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AE19">
         <v>1.03</v>
@@ -3479,7 +3479,7 @@
         <v>1.35</v>
       </c>
       <c r="AK19">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.18</v>
+        <v>1.36</v>
       </c>
       <c r="O40">
-        <v>3.14</v>
+        <v>4.5</v>
       </c>
       <c r="P40">
-        <v>3.38</v>
+        <v>8.6</v>
       </c>
       <c r="Q40">
-        <v>2.86</v>
+        <v>1.8</v>
       </c>
       <c r="R40">
-        <v>1.93</v>
+        <v>2.29</v>
       </c>
       <c r="S40">
+        <v>1.33</v>
+      </c>
+      <c r="T40">
+        <v>2.99</v>
+      </c>
+      <c r="U40">
+        <v>2.53</v>
+      </c>
+      <c r="V40">
         <v>1.45</v>
       </c>
-      <c r="T40">
-        <v>2.38</v>
-      </c>
-      <c r="U40">
-        <v>3.42</v>
-      </c>
-      <c r="V40">
-        <v>1.26</v>
-      </c>
       <c r="W40">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="X40">
         <v>1.03</v>
       </c>
       <c r="Y40">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="Z40">
-        <v>2.55</v>
+        <v>3.82</v>
       </c>
       <c r="AA40">
-        <v>2.4</v>
+        <v>1.71</v>
       </c>
       <c r="AB40">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AC40">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="AD40">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="AE40">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="AF40">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AG40">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="AK40">
-        <v>1.62</v>
+        <v>2.96</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.36</v>
+        <v>2.18</v>
       </c>
       <c r="O41">
-        <v>4.5</v>
+        <v>3.14</v>
       </c>
       <c r="P41">
-        <v>8.6</v>
+        <v>3.38</v>
       </c>
       <c r="Q41">
-        <v>1.8</v>
+        <v>2.86</v>
       </c>
       <c r="R41">
-        <v>2.29</v>
+        <v>1.93</v>
       </c>
       <c r="S41">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="T41">
-        <v>2.99</v>
+        <v>2.38</v>
       </c>
       <c r="U41">
-        <v>2.53</v>
+        <v>3.42</v>
       </c>
       <c r="V41">
-        <v>1.45</v>
+        <v>1.26</v>
       </c>
       <c r="W41">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X41">
         <v>1.03</v>
       </c>
       <c r="Y41">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="Z41">
-        <v>3.82</v>
+        <v>2.55</v>
       </c>
       <c r="AA41">
-        <v>1.71</v>
+        <v>2.4</v>
       </c>
       <c r="AB41">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AC41">
-        <v>2.7</v>
+        <v>4.6</v>
       </c>
       <c r="AD41">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AE41">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="AF41">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AG41">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="AK41">
-        <v>2.96</v>
+        <v>1.62</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="O46">
-        <v>4.12</v>
+        <v>4.41</v>
       </c>
       <c r="P46">
-        <v>4.94</v>
+        <v>3.67</v>
       </c>
       <c r="Q46">
+        <v>2.33</v>
+      </c>
+      <c r="R46">
+        <v>2.4</v>
+      </c>
+      <c r="S46">
+        <v>1.25</v>
+      </c>
+      <c r="T46">
+        <v>3.75</v>
+      </c>
+      <c r="U46">
         <v>2.1</v>
       </c>
-      <c r="R46">
-        <v>2.45</v>
-      </c>
-      <c r="S46">
-        <v>1.27</v>
-      </c>
-      <c r="T46">
-        <v>3.4</v>
-      </c>
-      <c r="U46">
-        <v>2.4</v>
-      </c>
       <c r="V46">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="W46">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X46">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z46">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AA46">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AB46">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AC46">
+        <v>2.15</v>
+      </c>
+      <c r="AD46">
+        <v>1.6</v>
+      </c>
+      <c r="AE46">
+        <v>1.25</v>
+      </c>
+      <c r="AF46">
+        <v>1.44</v>
+      </c>
+      <c r="AG46">
         <v>2.5</v>
-      </c>
-      <c r="AD46">
-        <v>1.44</v>
-      </c>
-      <c r="AE46">
-        <v>1.18</v>
-      </c>
-      <c r="AF46">
-        <v>1.62</v>
-      </c>
-      <c r="AG46">
-        <v>2.14</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         <v>1.2</v>
       </c>
       <c r="AK46">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.88</v>
+        <v>1.71</v>
       </c>
       <c r="O47">
-        <v>4.41</v>
+        <v>4.12</v>
       </c>
       <c r="P47">
-        <v>3.67</v>
+        <v>4.94</v>
       </c>
       <c r="Q47">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="R47">
+        <v>2.45</v>
+      </c>
+      <c r="S47">
+        <v>1.27</v>
+      </c>
+      <c r="T47">
+        <v>3.4</v>
+      </c>
+      <c r="U47">
         <v>2.4</v>
       </c>
-      <c r="S47">
-        <v>1.25</v>
-      </c>
-      <c r="T47">
-        <v>3.75</v>
-      </c>
-      <c r="U47">
-        <v>2.1</v>
-      </c>
       <c r="V47">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="W47">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X47">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y47">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z47">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AA47">
+        <v>1.58</v>
+      </c>
+      <c r="AB47">
+        <v>2.2</v>
+      </c>
+      <c r="AC47">
+        <v>2.5</v>
+      </c>
+      <c r="AD47">
         <v>1.44</v>
       </c>
-      <c r="AB47">
-        <v>2.5</v>
-      </c>
-      <c r="AC47">
-        <v>2.15</v>
-      </c>
-      <c r="AD47">
-        <v>1.6</v>
-      </c>
       <c r="AE47">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AF47">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AG47">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>1.2</v>
       </c>
       <c r="AK47">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.45</v>
+        <v>1.5</v>
       </c>
       <c r="O51">
-        <v>4.29</v>
+        <v>5.11</v>
       </c>
       <c r="P51">
-        <v>2.57</v>
+        <v>5.96</v>
       </c>
       <c r="Q51">
-        <v>2.78</v>
+        <v>1.91</v>
       </c>
       <c r="R51">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="S51">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T51">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U51">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="V51">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W51">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X51">
         <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z51">
         <v>6</v>
       </c>
       <c r="AA51">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AB51">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="AC51">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AD51">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AE51">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AF51">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="AG51">
-        <v>2.76</v>
+        <v>2.2</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK51">
-        <v>1.56</v>
+        <v>2.6</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>1.5</v>
+        <v>2.45</v>
       </c>
       <c r="O52">
-        <v>5.11</v>
+        <v>4.29</v>
       </c>
       <c r="P52">
-        <v>5.96</v>
+        <v>2.57</v>
       </c>
       <c r="Q52">
-        <v>1.91</v>
+        <v>2.78</v>
       </c>
       <c r="R52">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="S52">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T52">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U52">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="V52">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="W52">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X52">
         <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z52">
         <v>6</v>
       </c>
       <c r="AA52">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AB52">
-        <v>2.51</v>
+        <v>2.63</v>
       </c>
       <c r="AC52">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AD52">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AE52">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AF52">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AG52">
-        <v>2.2</v>
+        <v>2.76</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK52">
-        <v>2.6</v>
+        <v>1.56</v>
       </c>
       <c r="AL52">
         <v>0</v>

--- a/jogos_2026-08-19.xlsx
+++ b/jogos_2026-08-19.xlsx
@@ -4550,7 +4550,7 @@
         <v>1.3</v>
       </c>
       <c r="O26">
-        <v>4.9</v>
+        <v>5.25</v>
       </c>
       <c r="P26">
         <v>11</v>
@@ -4559,10 +4559,10 @@
         <v>1.73</v>
       </c>
       <c r="R26">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="S26">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T26">
         <v>3.28</v>
@@ -4571,16 +4571,16 @@
         <v>2.5</v>
       </c>
       <c r="V26">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W26">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X26">
         <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z26">
         <v>4</v>
@@ -4589,7 +4589,7 @@
         <v>1.76</v>
       </c>
       <c r="AB26">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AC26">
         <v>2.76</v>
@@ -4601,10 +4601,10 @@
         <v>1.15</v>
       </c>
       <c r="AF26">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AG26">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AK26">
-        <v>3.23</v>
+        <v>3.35</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5211,19 +5211,19 @@
         <v>3.35</v>
       </c>
       <c r="R30">
-        <v>2.01</v>
+        <v>2.12</v>
       </c>
       <c r="S30">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T30">
-        <v>2.88</v>
+        <v>2.69</v>
       </c>
       <c r="U30">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="V30">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W30">
         <v>1.02</v>
@@ -5238,22 +5238,22 @@
         <v>3.2</v>
       </c>
       <c r="AA30">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AB30">
+        <v>1.74</v>
+      </c>
+      <c r="AC30">
+        <v>3.65</v>
+      </c>
+      <c r="AD30">
+        <v>1.25</v>
+      </c>
+      <c r="AE30">
+        <v>1.04</v>
+      </c>
+      <c r="AF30">
         <v>1.75</v>
-      </c>
-      <c r="AC30">
-        <v>3.5</v>
-      </c>
-      <c r="AD30">
-        <v>1.22</v>
-      </c>
-      <c r="AE30">
-        <v>1.07</v>
-      </c>
-      <c r="AF30">
-        <v>1.77</v>
       </c>
       <c r="AG30">
         <v>1.94</v>
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="AK30">
         <v>1.37</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Montreal Impact</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>3.2</v>
+        <v>1.58</v>
       </c>
       <c r="O33">
-        <v>4.59</v>
+        <v>4.8</v>
       </c>
       <c r="P33">
+        <v>5.25</v>
+      </c>
+      <c r="Q33">
         <v>2</v>
       </c>
-      <c r="Q33">
-        <v>2.95</v>
-      </c>
       <c r="R33">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="S33">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="T33">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="U33">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="V33">
-        <v>1.79</v>
+        <v>1.63</v>
       </c>
       <c r="W33">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="X33">
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="Z33">
-        <v>6.1</v>
+        <v>5</v>
       </c>
       <c r="AA33">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="AB33">
-        <v>3.1</v>
+        <v>2.34</v>
       </c>
       <c r="AC33">
-        <v>1.9</v>
+        <v>2.25</v>
       </c>
       <c r="AD33">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AE33">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AF33">
-        <v>1.32</v>
+        <v>1.6</v>
       </c>
       <c r="AG33">
-        <v>3.04</v>
+        <v>2.25</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.67</v>
+        <v>1.17</v>
       </c>
       <c r="AK33">
-        <v>1.36</v>
+        <v>2.3</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Montreal Impact</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.58</v>
+        <v>2.37</v>
       </c>
       <c r="O34">
+        <v>4.02</v>
+      </c>
+      <c r="P34">
+        <v>2.78</v>
+      </c>
+      <c r="Q34">
+        <v>2.6</v>
+      </c>
+      <c r="R34">
+        <v>2.26</v>
+      </c>
+      <c r="S34">
+        <v>1.26</v>
+      </c>
+      <c r="T34">
+        <v>3.45</v>
+      </c>
+      <c r="U34">
+        <v>2.32</v>
+      </c>
+      <c r="V34">
+        <v>1.57</v>
+      </c>
+      <c r="W34">
+        <v>1.12</v>
+      </c>
+      <c r="X34">
+        <v>1.04</v>
+      </c>
+      <c r="Y34">
+        <v>1.17</v>
+      </c>
+      <c r="Z34">
         <v>4.8</v>
       </c>
-      <c r="P34">
-        <v>5.25</v>
-      </c>
-      <c r="Q34">
-        <v>2</v>
-      </c>
-      <c r="R34">
-        <v>2.45</v>
-      </c>
-      <c r="S34">
-        <v>1.22</v>
-      </c>
-      <c r="T34">
-        <v>3.6</v>
-      </c>
-      <c r="U34">
+      <c r="AA34">
+        <v>1.6</v>
+      </c>
+      <c r="AB34">
         <v>2.15</v>
       </c>
-      <c r="V34">
-        <v>1.63</v>
-      </c>
-      <c r="W34">
-        <v>1.17</v>
-      </c>
-      <c r="X34">
-        <v>1.01</v>
-      </c>
-      <c r="Y34">
-        <v>1.12</v>
-      </c>
-      <c r="Z34">
-        <v>5</v>
-      </c>
-      <c r="AA34">
-        <v>1.48</v>
-      </c>
-      <c r="AB34">
-        <v>2.34</v>
-      </c>
       <c r="AC34">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AD34">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AE34">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF34">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AG34">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK34">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Toronto</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.37</v>
+        <v>2.68</v>
       </c>
       <c r="O35">
-        <v>4.02</v>
+        <v>3.99</v>
       </c>
       <c r="P35">
-        <v>2.78</v>
+        <v>2.45</v>
       </c>
       <c r="Q35">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="R35">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="S35">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="T35">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="U35">
-        <v>2.32</v>
+        <v>2.01</v>
       </c>
       <c r="V35">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="W35">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="X35">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z35">
-        <v>4.8</v>
+        <v>5.75</v>
       </c>
       <c r="AA35">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AB35">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="AC35">
-        <v>2.5</v>
+        <v>1.98</v>
       </c>
       <c r="AD35">
-        <v>1.52</v>
+        <v>1.73</v>
       </c>
       <c r="AE35">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AF35">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AG35">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK35">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.06</v>
+        <v>2.8</v>
       </c>
       <c r="O36">
-        <v>4</v>
+        <v>4.23</v>
       </c>
       <c r="P36">
-        <v>3.38</v>
+        <v>2.29</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA36">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="AB36">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,80 +6340,80 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.68</v>
+        <v>2.13</v>
       </c>
       <c r="O37">
-        <v>3.99</v>
+        <v>4.36</v>
       </c>
       <c r="P37">
+        <v>3.01</v>
+      </c>
+      <c r="Q37">
         <v>2.45</v>
       </c>
-      <c r="Q37">
-        <v>2.8</v>
-      </c>
       <c r="R37">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S37">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="T37">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="U37">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="V37">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="W37">
         <v>1.18</v>
       </c>
       <c r="X37">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z37">
-        <v>5.75</v>
+        <v>6.1</v>
       </c>
       <c r="AA37">
+        <v>1.38</v>
+      </c>
+      <c r="AB37">
+        <v>2.8</v>
+      </c>
+      <c r="AC37">
+        <v>2</v>
+      </c>
+      <c r="AD37">
+        <v>1.7</v>
+      </c>
+      <c r="AE37">
+        <v>1.29</v>
+      </c>
+      <c r="AF37">
         <v>1.4</v>
       </c>
-      <c r="AB37">
+      <c r="AG37">
         <v>2.75</v>
       </c>
-      <c r="AC37">
-        <v>1.98</v>
-      </c>
-      <c r="AD37">
-        <v>1.73</v>
-      </c>
-      <c r="AE37">
-        <v>1.3</v>
-      </c>
-      <c r="AF37">
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ37">
         <v>1.36</v>
       </c>
-      <c r="AG37">
-        <v>2.8</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ37">
-        <v>1.24</v>
-      </c>
       <c r="AK37">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="O38">
-        <v>4.23</v>
+        <v>4.59</v>
       </c>
       <c r="P38">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="Q38">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="R38">
-        <v>2.35</v>
+        <v>2.63</v>
       </c>
       <c r="S38">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="T38">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="U38">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="V38">
-        <v>1.58</v>
+        <v>1.79</v>
       </c>
       <c r="W38">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="X38">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="Z38">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="AA38">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AB38">
-        <v>2.55</v>
+        <v>3.1</v>
       </c>
       <c r="AC38">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AD38">
-        <v>1.58</v>
+        <v>1.9</v>
       </c>
       <c r="AE38">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AF38">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AG38">
-        <v>2.58</v>
+        <v>3.04</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="AK38">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="O39">
-        <v>4.36</v>
+        <v>4</v>
       </c>
       <c r="P39">
-        <v>3.01</v>
+        <v>3.38</v>
       </c>
       <c r="Q39">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R39">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S39">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="T39">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="U39">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="V39">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="W39">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X39">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y39">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Z39">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AA39">
-        <v>1.38</v>
+        <v>1.68</v>
       </c>
       <c r="AB39">
-        <v>2.8</v>
+        <v>2.05</v>
       </c>
       <c r="AC39">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD39">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE39">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AF39">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG39">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK39">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL39">
         <v>0</v>

--- a/jogos_2026-08-19.xlsx
+++ b/jogos_2026-08-19.xlsx
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="O19">
         <v>2.65</v>
       </c>
       <c r="P19">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Q19">
         <v>2.8</v>
@@ -3448,7 +3448,7 @@
         <v>2.88</v>
       </c>
       <c r="AB19">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AC19">
         <v>5.5</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,80 +6014,80 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.68</v>
+        <v>2.13</v>
       </c>
       <c r="O35">
-        <v>3.99</v>
+        <v>4.36</v>
       </c>
       <c r="P35">
+        <v>3.01</v>
+      </c>
+      <c r="Q35">
         <v>2.45</v>
       </c>
-      <c r="Q35">
-        <v>2.8</v>
-      </c>
       <c r="R35">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S35">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="T35">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="U35">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="V35">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="W35">
         <v>1.18</v>
       </c>
       <c r="X35">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z35">
-        <v>5.75</v>
+        <v>6.1</v>
       </c>
       <c r="AA35">
+        <v>1.38</v>
+      </c>
+      <c r="AB35">
+        <v>2.8</v>
+      </c>
+      <c r="AC35">
+        <v>2</v>
+      </c>
+      <c r="AD35">
+        <v>1.7</v>
+      </c>
+      <c r="AE35">
+        <v>1.29</v>
+      </c>
+      <c r="AF35">
         <v>1.4</v>
       </c>
-      <c r="AB35">
+      <c r="AG35">
         <v>2.75</v>
       </c>
-      <c r="AC35">
-        <v>1.98</v>
-      </c>
-      <c r="AD35">
-        <v>1.73</v>
-      </c>
-      <c r="AE35">
-        <v>1.3</v>
-      </c>
-      <c r="AF35">
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ35">
         <v>1.36</v>
       </c>
-      <c r="AG35">
-        <v>2.8</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ35">
-        <v>1.24</v>
-      </c>
       <c r="AK35">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.8</v>
+        <v>2.06</v>
       </c>
       <c r="O36">
-        <v>4.23</v>
+        <v>4</v>
       </c>
       <c r="P36">
-        <v>2.29</v>
+        <v>3.38</v>
       </c>
       <c r="Q36">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R36">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S36">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T36">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U36">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V36">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="W36">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X36">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y36">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Z36">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA36">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="AB36">
-        <v>2.55</v>
+        <v>2.05</v>
       </c>
       <c r="AC36">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD36">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE36">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AF36">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG36">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK36">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,65 +6340,65 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.13</v>
+        <v>2.68</v>
       </c>
       <c r="O37">
-        <v>4.36</v>
+        <v>3.99</v>
       </c>
       <c r="P37">
-        <v>3.01</v>
+        <v>2.45</v>
       </c>
       <c r="Q37">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="R37">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S37">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="T37">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="U37">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="V37">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="W37">
         <v>1.18</v>
       </c>
       <c r="X37">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z37">
-        <v>6.1</v>
+        <v>5.75</v>
       </c>
       <c r="AA37">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AB37">
+        <v>2.75</v>
+      </c>
+      <c r="AC37">
+        <v>1.98</v>
+      </c>
+      <c r="AD37">
+        <v>1.73</v>
+      </c>
+      <c r="AE37">
+        <v>1.3</v>
+      </c>
+      <c r="AF37">
+        <v>1.36</v>
+      </c>
+      <c r="AG37">
         <v>2.8</v>
       </c>
-      <c r="AC37">
-        <v>2</v>
-      </c>
-      <c r="AD37">
-        <v>1.7</v>
-      </c>
-      <c r="AE37">
-        <v>1.29</v>
-      </c>
-      <c r="AF37">
-        <v>1.4</v>
-      </c>
-      <c r="AG37">
-        <v>2.75</v>
-      </c>
       <c r="AH37" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AK37">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,80 +6503,80 @@
         </is>
       </c>
       <c r="N38">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="O38">
-        <v>4.59</v>
+        <v>4.23</v>
       </c>
       <c r="P38">
-        <v>2</v>
+        <v>2.29</v>
       </c>
       <c r="Q38">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="R38">
-        <v>2.63</v>
+        <v>2.35</v>
       </c>
       <c r="S38">
+        <v>1.25</v>
+      </c>
+      <c r="T38">
+        <v>3.8</v>
+      </c>
+      <c r="U38">
+        <v>2.2</v>
+      </c>
+      <c r="V38">
+        <v>1.58</v>
+      </c>
+      <c r="W38">
         <v>1.14</v>
       </c>
-      <c r="T38">
-        <v>4.8</v>
-      </c>
-      <c r="U38">
-        <v>1.85</v>
-      </c>
-      <c r="V38">
-        <v>1.79</v>
-      </c>
-      <c r="W38">
+      <c r="X38">
+        <v>1.03</v>
+      </c>
+      <c r="Y38">
+        <v>1.15</v>
+      </c>
+      <c r="Z38">
+        <v>5.5</v>
+      </c>
+      <c r="AA38">
+        <v>1.5</v>
+      </c>
+      <c r="AB38">
+        <v>2.55</v>
+      </c>
+      <c r="AC38">
+        <v>2.2</v>
+      </c>
+      <c r="AD38">
+        <v>1.58</v>
+      </c>
+      <c r="AE38">
+        <v>1.23</v>
+      </c>
+      <c r="AF38">
+        <v>1.44</v>
+      </c>
+      <c r="AG38">
+        <v>2.58</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38">
         <v>1.22</v>
       </c>
-      <c r="X38">
-        <v>1.01</v>
-      </c>
-      <c r="Y38">
-        <v>1.06</v>
-      </c>
-      <c r="Z38">
-        <v>6.1</v>
-      </c>
-      <c r="AA38">
-        <v>1.33</v>
-      </c>
-      <c r="AB38">
-        <v>3.1</v>
-      </c>
-      <c r="AC38">
-        <v>1.9</v>
-      </c>
-      <c r="AD38">
-        <v>1.9</v>
-      </c>
-      <c r="AE38">
-        <v>1.36</v>
-      </c>
-      <c r="AF38">
-        <v>1.32</v>
-      </c>
-      <c r="AG38">
-        <v>3.04</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ38">
-        <v>1.67</v>
-      </c>
       <c r="AK38">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.06</v>
+        <v>3.2</v>
       </c>
       <c r="O39">
-        <v>4</v>
+        <v>4.59</v>
       </c>
       <c r="P39">
-        <v>3.38</v>
+        <v>2</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AA39">
-        <v>1.68</v>
+        <v>1.33</v>
       </c>
       <c r="AB39">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.88</v>
+        <v>1.71</v>
       </c>
       <c r="O46">
-        <v>4.41</v>
+        <v>4.12</v>
       </c>
       <c r="P46">
-        <v>3.67</v>
+        <v>4.94</v>
       </c>
       <c r="Q46">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="R46">
+        <v>2.45</v>
+      </c>
+      <c r="S46">
+        <v>1.27</v>
+      </c>
+      <c r="T46">
+        <v>3.4</v>
+      </c>
+      <c r="U46">
         <v>2.4</v>
       </c>
-      <c r="S46">
-        <v>1.25</v>
-      </c>
-      <c r="T46">
-        <v>3.75</v>
-      </c>
-      <c r="U46">
-        <v>2.1</v>
-      </c>
       <c r="V46">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="W46">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="X46">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y46">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z46">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AA46">
+        <v>1.58</v>
+      </c>
+      <c r="AB46">
+        <v>2.2</v>
+      </c>
+      <c r="AC46">
+        <v>2.5</v>
+      </c>
+      <c r="AD46">
         <v>1.44</v>
       </c>
-      <c r="AB46">
-        <v>2.5</v>
-      </c>
-      <c r="AC46">
-        <v>2.15</v>
-      </c>
-      <c r="AD46">
-        <v>1.6</v>
-      </c>
       <c r="AE46">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AF46">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AG46">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         <v>1.2</v>
       </c>
       <c r="AK46">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,37 +7970,37 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.71</v>
+        <v>2.78</v>
       </c>
       <c r="O47">
-        <v>4.12</v>
+        <v>4.03</v>
       </c>
       <c r="P47">
-        <v>4.94</v>
+        <v>2.37</v>
       </c>
       <c r="Q47">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="R47">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="S47">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T47">
         <v>3.4</v>
       </c>
       <c r="U47">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="V47">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W47">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X47">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y47">
         <v>1.18</v>
@@ -8018,16 +8018,16 @@
         <v>2.5</v>
       </c>
       <c r="AD47">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AE47">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF47">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AG47">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.2</v>
+        <v>1.57</v>
       </c>
       <c r="AK47">
-        <v>2.08</v>
+        <v>1.38</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,61 +8133,61 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.78</v>
+        <v>1.88</v>
       </c>
       <c r="O48">
-        <v>4.03</v>
+        <v>4.41</v>
       </c>
       <c r="P48">
-        <v>2.37</v>
+        <v>3.67</v>
       </c>
       <c r="Q48">
-        <v>3.1</v>
+        <v>2.33</v>
       </c>
       <c r="R48">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="S48">
         <v>1.25</v>
       </c>
       <c r="T48">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="U48">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="V48">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="W48">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X48">
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z48">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AA48">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AB48">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AC48">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="AD48">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AE48">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF48">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG48">
         <v>2.5</v>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.57</v>
+        <v>1.2</v>
       </c>
       <c r="AK48">
-        <v>1.38</v>
+        <v>1.9</v>
       </c>
       <c r="AL48">
         <v>0</v>

--- a/jogos_2026-08-19.xlsx
+++ b/jogos_2026-08-19.xlsx
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AK17">
         <v>4</v>
@@ -3895,61 +3895,61 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.76</v>
+        <v>1.59</v>
       </c>
       <c r="O22">
-        <v>3.66</v>
+        <v>4.12</v>
       </c>
       <c r="P22">
-        <v>5.44</v>
+        <v>5.5</v>
       </c>
       <c r="Q22">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="R22">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="S22">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T22">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U22">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="V22">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W22">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X22">
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z22">
-        <v>3.54</v>
+        <v>3.9</v>
       </c>
       <c r="AA22">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB22">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AC22">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AD22">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE22">
         <v>1.11</v>
       </c>
       <c r="AF22">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG22">
         <v>1.87</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AK22">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,16 +4058,16 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="O23">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="P23">
-        <v>4.29</v>
+        <v>4.5</v>
       </c>
       <c r="Q23">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="R23">
         <v>2.25</v>
@@ -4076,16 +4076,16 @@
         <v>1.3</v>
       </c>
       <c r="T23">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U23">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="V23">
         <v>1.48</v>
       </c>
       <c r="W23">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X23">
         <v>1.04</v>
@@ -4097,10 +4097,10 @@
         <v>3.8</v>
       </c>
       <c r="AA23">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AB23">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AC23">
         <v>2.9</v>
@@ -4112,10 +4112,10 @@
         <v>1.09</v>
       </c>
       <c r="AF23">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AG23">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>1.22</v>
       </c>
       <c r="AK23">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="O24">
-        <v>3.49</v>
+        <v>3.15</v>
       </c>
       <c r="P24">
-        <v>3.49</v>
+        <v>3.14</v>
       </c>
       <c r="Q24">
         <v>2.85</v>
@@ -4236,7 +4236,7 @@
         <v>2.1</v>
       </c>
       <c r="S24">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T24">
         <v>2.66</v>
@@ -4245,13 +4245,13 @@
         <v>2.78</v>
       </c>
       <c r="V24">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="W24">
         <v>1.1</v>
       </c>
       <c r="X24">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
         <v>1.3</v>
@@ -4260,16 +4260,16 @@
         <v>3.1</v>
       </c>
       <c r="AA24">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AB24">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AC24">
         <v>3.3</v>
       </c>
       <c r="AD24">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE24">
         <v>1.06</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AK24">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,31 +4384,31 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="O25">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P25">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="Q25">
-        <v>3.02</v>
+        <v>2.99</v>
       </c>
       <c r="R25">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S25">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T25">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U25">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="V25">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="W25">
         <v>1.17</v>
@@ -4417,31 +4417,31 @@
         <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z25">
         <v>6</v>
       </c>
       <c r="AA25">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB25">
         <v>2.7</v>
       </c>
       <c r="AC25">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="AD25">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AE25">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AF25">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AG25">
-        <v>2.75</v>
+        <v>2.94</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AK25">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4550,28 +4550,28 @@
         <v>1.3</v>
       </c>
       <c r="O26">
-        <v>5.25</v>
+        <v>5.65</v>
       </c>
       <c r="P26">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Q26">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="R26">
         <v>2.49</v>
       </c>
       <c r="S26">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T26">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
       <c r="U26">
         <v>2.5</v>
       </c>
       <c r="V26">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W26">
         <v>1.11</v>
@@ -4586,10 +4586,10 @@
         <v>4</v>
       </c>
       <c r="AA26">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AB26">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AC26">
         <v>2.76</v>
@@ -4946,7 +4946,7 @@
         <v>0</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="O29">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P29">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5211,7 +5211,7 @@
         <v>3.35</v>
       </c>
       <c r="R30">
-        <v>2.12</v>
+        <v>2.01</v>
       </c>
       <c r="S30">
         <v>1.4</v>
@@ -5220,7 +5220,7 @@
         <v>2.69</v>
       </c>
       <c r="U30">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="V30">
         <v>1.34</v>
@@ -5238,16 +5238,16 @@
         <v>3.2</v>
       </c>
       <c r="AA30">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AB30">
         <v>1.74</v>
       </c>
       <c r="AC30">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="AD30">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE30">
         <v>1.04</v>
@@ -5688,16 +5688,16 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="O33">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="P33">
-        <v>5.25</v>
+        <v>5.11</v>
       </c>
       <c r="Q33">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="R33">
         <v>2.45</v>
@@ -5706,13 +5706,13 @@
         <v>1.22</v>
       </c>
       <c r="T33">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="U33">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="V33">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="W33">
         <v>1.17</v>
@@ -5721,25 +5721,25 @@
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="Z33">
         <v>5</v>
       </c>
       <c r="AA33">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AB33">
-        <v>2.34</v>
+        <v>2.45</v>
       </c>
       <c r="AC33">
         <v>2.25</v>
       </c>
       <c r="AD33">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AE33">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF33">
         <v>1.6</v>
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="O34">
-        <v>4.02</v>
+        <v>3.5</v>
       </c>
       <c r="P34">
-        <v>2.78</v>
+        <v>3.07</v>
       </c>
       <c r="Q34">
         <v>2.6</v>
       </c>
       <c r="R34">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="S34">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="T34">
-        <v>3.45</v>
+        <v>3.22</v>
       </c>
       <c r="U34">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="V34">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="W34">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X34">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
         <v>1.17</v>
       </c>
       <c r="Z34">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="AA34">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AB34">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AC34">
         <v>2.5</v>
       </c>
       <c r="AD34">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="AE34">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AF34">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG34">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>1.25</v>
       </c>
       <c r="AK34">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,16 +6014,16 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="O35">
-        <v>4.36</v>
+        <v>4</v>
       </c>
       <c r="P35">
-        <v>3.01</v>
+        <v>2.8</v>
       </c>
       <c r="Q35">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="R35">
         <v>2.45</v>
@@ -6047,22 +6047,22 @@
         <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z35">
-        <v>6.1</v>
+        <v>5.75</v>
       </c>
       <c r="AA35">
         <v>1.38</v>
       </c>
       <c r="AB35">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AC35">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AD35">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AE35">
         <v>1.29</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AK35">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="O36">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="P36">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6216,10 +6216,10 @@
         <v>0</v>
       </c>
       <c r="AA36">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB36">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC36">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.68</v>
+        <v>2.47</v>
       </c>
       <c r="O37">
-        <v>3.99</v>
+        <v>3.8</v>
       </c>
       <c r="P37">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="Q37">
         <v>2.8</v>
@@ -6355,46 +6355,46 @@
         <v>2.5</v>
       </c>
       <c r="S37">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="T37">
         <v>4</v>
       </c>
       <c r="U37">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="V37">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="W37">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X37">
         <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z37">
-        <v>5.75</v>
+        <v>6.25</v>
       </c>
       <c r="AA37">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AB37">
-        <v>2.75</v>
+        <v>3.15</v>
       </c>
       <c r="AC37">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AD37">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AE37">
         <v>1.3</v>
       </c>
       <c r="AF37">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG37">
         <v>2.8</v>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK37">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,16 +6503,16 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="O38">
-        <v>4.23</v>
+        <v>4.16</v>
       </c>
       <c r="P38">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="Q38">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="R38">
         <v>2.35</v>
@@ -6521,16 +6521,16 @@
         <v>1.25</v>
       </c>
       <c r="T38">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="U38">
         <v>2.2</v>
       </c>
       <c r="V38">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W38">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X38">
         <v>1.03</v>
@@ -6539,7 +6539,7 @@
         <v>1.15</v>
       </c>
       <c r="Z38">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AA38">
         <v>1.5</v>
@@ -6548,10 +6548,10 @@
         <v>2.55</v>
       </c>
       <c r="AC38">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AD38">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AE38">
         <v>1.23</v>
@@ -6560,7 +6560,7 @@
         <v>1.44</v>
       </c>
       <c r="AG38">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="AK38">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,22 +6666,22 @@
         </is>
       </c>
       <c r="N39">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="O39">
-        <v>4.59</v>
+        <v>3.75</v>
       </c>
       <c r="P39">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Q39">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="R39">
         <v>2.63</v>
       </c>
       <c r="S39">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="T39">
         <v>4.8</v>
@@ -6690,7 +6690,7 @@
         <v>1.85</v>
       </c>
       <c r="V39">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="W39">
         <v>1.22</v>
@@ -6699,31 +6699,31 @@
         <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z39">
-        <v>6.1</v>
+        <v>7.5</v>
       </c>
       <c r="AA39">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AB39">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="AC39">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AD39">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AE39">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AF39">
         <v>1.32</v>
       </c>
       <c r="AG39">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="AK39">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6838,71 +6838,71 @@
         <v>8.6</v>
       </c>
       <c r="Q40">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="R40">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="S40">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T40">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="U40">
-        <v>2.53</v>
+        <v>2.81</v>
       </c>
       <c r="V40">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="W40">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X40">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y40">
+        <v>1.25</v>
+      </c>
+      <c r="Z40">
+        <v>3.45</v>
+      </c>
+      <c r="AA40">
+        <v>1.74</v>
+      </c>
+      <c r="AB40">
+        <v>2.02</v>
+      </c>
+      <c r="AC40">
+        <v>3.2</v>
+      </c>
+      <c r="AD40">
+        <v>1.26</v>
+      </c>
+      <c r="AE40">
+        <v>1.11</v>
+      </c>
+      <c r="AF40">
+        <v>2.2</v>
+      </c>
+      <c r="AG40">
+        <v>1.6</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ40">
         <v>1.18</v>
       </c>
-      <c r="Z40">
-        <v>3.82</v>
-      </c>
-      <c r="AA40">
-        <v>1.71</v>
-      </c>
-      <c r="AB40">
-        <v>2</v>
-      </c>
-      <c r="AC40">
-        <v>2.7</v>
-      </c>
-      <c r="AD40">
-        <v>1.36</v>
-      </c>
-      <c r="AE40">
-        <v>1.12</v>
-      </c>
-      <c r="AF40">
-        <v>2</v>
-      </c>
-      <c r="AG40">
-        <v>1.71</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ40">
-        <v>1.17</v>
-      </c>
       <c r="AK40">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="O41">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="P41">
-        <v>3.38</v>
+        <v>3.2</v>
       </c>
       <c r="Q41">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="R41">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="S41">
         <v>1.45</v>
       </c>
       <c r="T41">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="U41">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="V41">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W41">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X41">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y41">
         <v>1.4</v>
       </c>
       <c r="Z41">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="AA41">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AB41">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AC41">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="AD41">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AE41">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF41">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AG41">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7318,37 +7318,37 @@
         </is>
       </c>
       <c r="N43">
-        <v>3.37</v>
+        <v>3.17</v>
       </c>
       <c r="O43">
-        <v>3.98</v>
+        <v>3.7</v>
       </c>
       <c r="P43">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="Q43">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R43">
         <v>2.5</v>
       </c>
       <c r="S43">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T43">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U43">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="V43">
         <v>1.62</v>
       </c>
       <c r="W43">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X43">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y43">
         <v>1.13</v>
@@ -7360,10 +7360,10 @@
         <v>1.45</v>
       </c>
       <c r="AB43">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AC43">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AD43">
         <v>1.61</v>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.79</v>
+        <v>1.22</v>
       </c>
       <c r="AK43">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,37 +7481,37 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="O44">
-        <v>4.37</v>
+        <v>4.16</v>
       </c>
       <c r="P44">
-        <v>4.62</v>
+        <v>3.9</v>
       </c>
       <c r="Q44">
         <v>2.2</v>
       </c>
       <c r="R44">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S44">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T44">
         <v>3.3</v>
       </c>
       <c r="U44">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="V44">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W44">
         <v>1.08</v>
       </c>
       <c r="X44">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y44">
         <v>1.19</v>
@@ -7520,10 +7520,10 @@
         <v>4.33</v>
       </c>
       <c r="AA44">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AB44">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AC44">
         <v>2.65</v>
@@ -7532,10 +7532,10 @@
         <v>1.48</v>
       </c>
       <c r="AE44">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF44">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AG44">
         <v>2.15</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK44">
         <v>2.02</v>
@@ -7653,55 +7653,55 @@
         <v>2.66</v>
       </c>
       <c r="Q45">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R45">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="S45">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="T45">
-        <v>2.41</v>
+        <v>2.23</v>
       </c>
       <c r="U45">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="V45">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="W45">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X45">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y45">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="Z45">
-        <v>2.56</v>
+        <v>2.33</v>
       </c>
       <c r="AA45">
-        <v>2.35</v>
+        <v>2.62</v>
       </c>
       <c r="AB45">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="AC45">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AD45">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AE45">
         <v>1.01</v>
       </c>
       <c r="AF45">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="AG45">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AK45">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="O46">
-        <v>4.12</v>
+        <v>4.1</v>
       </c>
       <c r="P46">
-        <v>4.94</v>
+        <v>4.33</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
@@ -7834,53 +7834,53 @@
         <v>1.5</v>
       </c>
       <c r="W46">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="X46">
         <v>1.03</v>
       </c>
       <c r="Y46">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z46">
         <v>4.5</v>
       </c>
       <c r="AA46">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AB46">
         <v>2.2</v>
       </c>
       <c r="AC46">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="AD46">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AE46">
+        <v>1.2</v>
+      </c>
+      <c r="AF46">
+        <v>1.65</v>
+      </c>
+      <c r="AG46">
+        <v>2.15</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ46">
         <v>1.18</v>
       </c>
-      <c r="AF46">
-        <v>1.62</v>
-      </c>
-      <c r="AG46">
-        <v>2.14</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ46">
-        <v>1.2</v>
-      </c>
       <c r="AK46">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,55 +7970,55 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="O47">
-        <v>4.03</v>
+        <v>4.01</v>
       </c>
       <c r="P47">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="Q47">
         <v>3.1</v>
       </c>
       <c r="R47">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="S47">
         <v>1.25</v>
       </c>
       <c r="T47">
-        <v>3.4</v>
+        <v>3.34</v>
       </c>
       <c r="U47">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="V47">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W47">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X47">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y47">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z47">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA47">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AB47">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="AC47">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AD47">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AE47">
         <v>1.2</v>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AK47">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,43 +8133,43 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="O48">
-        <v>4.41</v>
+        <v>4.34</v>
       </c>
       <c r="P48">
-        <v>3.67</v>
+        <v>3.62</v>
       </c>
       <c r="Q48">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="R48">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S48">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T48">
-        <v>3.75</v>
+        <v>3.66</v>
       </c>
       <c r="U48">
         <v>2.1</v>
       </c>
       <c r="V48">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W48">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X48">
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="Z48">
-        <v>5</v>
+        <v>6.1</v>
       </c>
       <c r="AA48">
         <v>1.44</v>
@@ -8178,13 +8178,13 @@
         <v>2.5</v>
       </c>
       <c r="AC48">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AD48">
         <v>1.6</v>
       </c>
       <c r="AE48">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF48">
         <v>1.44</v>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK48">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8459,34 +8459,34 @@
         </is>
       </c>
       <c r="N50">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="O50">
-        <v>4.59</v>
+        <v>4.5</v>
       </c>
       <c r="P50">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="Q50">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="R50">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="S50">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="T50">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="U50">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="V50">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="W50">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X50">
         <v>1.01</v>
@@ -8498,19 +8498,19 @@
         <v>6.5</v>
       </c>
       <c r="AA50">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AB50">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AC50">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AD50">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AE50">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AF50">
         <v>1.33</v>
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="O51">
-        <v>5.11</v>
+        <v>4.75</v>
       </c>
       <c r="P51">
-        <v>5.96</v>
+        <v>6.32</v>
       </c>
       <c r="Q51">
         <v>1.91</v>
@@ -8640,7 +8640,7 @@
         <v>1.22</v>
       </c>
       <c r="T51">
-        <v>3.9</v>
+        <v>3.66</v>
       </c>
       <c r="U51">
         <v>2.05</v>
@@ -8649,7 +8649,7 @@
         <v>1.67</v>
       </c>
       <c r="W51">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X51">
         <v>1.02</v>
@@ -8658,28 +8658,28 @@
         <v>1.14</v>
       </c>
       <c r="Z51">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AA51">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AB51">
-        <v>2.51</v>
+        <v>2.75</v>
       </c>
       <c r="AC51">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AD51">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AE51">
         <v>1.25</v>
       </c>
       <c r="AF51">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG51">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8785,16 +8785,16 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="O52">
-        <v>4.29</v>
+        <v>3.7</v>
       </c>
       <c r="P52">
-        <v>2.57</v>
+        <v>2.78</v>
       </c>
       <c r="Q52">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="R52">
         <v>2.4</v>
@@ -8806,10 +8806,10 @@
         <v>4</v>
       </c>
       <c r="U52">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V52">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="W52">
         <v>1.18</v>
@@ -8821,25 +8821,25 @@
         <v>1.12</v>
       </c>
       <c r="Z52">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AA52">
         <v>1.4</v>
       </c>
       <c r="AB52">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AC52">
         <v>2.05</v>
       </c>
       <c r="AD52">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AE52">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AF52">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AG52">
         <v>2.76</v>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AK52">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AL52">
         <v>0</v>

--- a/jogos_2026-08-19.xlsx
+++ b/jogos_2026-08-19.xlsx
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="O24">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="P24">
-        <v>3.14</v>
+        <v>2.5</v>
       </c>
       <c r="Q24">
-        <v>2.85</v>
+        <v>2.99</v>
       </c>
       <c r="R24">
+        <v>2.4</v>
+      </c>
+      <c r="S24">
+        <v>1.2</v>
+      </c>
+      <c r="T24">
+        <v>4</v>
+      </c>
+      <c r="U24">
         <v>2.1</v>
       </c>
-      <c r="S24">
-        <v>1.4</v>
-      </c>
-      <c r="T24">
-        <v>2.66</v>
-      </c>
-      <c r="U24">
-        <v>2.78</v>
-      </c>
       <c r="V24">
-        <v>1.37</v>
+        <v>1.75</v>
       </c>
       <c r="W24">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X24">
         <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="Z24">
-        <v>3.1</v>
+        <v>6</v>
       </c>
       <c r="AA24">
-        <v>1.93</v>
+        <v>1.4</v>
       </c>
       <c r="AB24">
-        <v>1.83</v>
+        <v>2.7</v>
       </c>
       <c r="AC24">
-        <v>3.3</v>
+        <v>1.99</v>
       </c>
       <c r="AD24">
-        <v>1.25</v>
+        <v>1.78</v>
       </c>
       <c r="AE24">
-        <v>1.06</v>
+        <v>1.28</v>
       </c>
       <c r="AF24">
-        <v>1.75</v>
+        <v>1.35</v>
       </c>
       <c r="AG24">
-        <v>2</v>
+        <v>2.94</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="AK24">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="O25">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="P25">
-        <v>2.5</v>
+        <v>3.14</v>
       </c>
       <c r="Q25">
-        <v>2.99</v>
+        <v>2.85</v>
       </c>
       <c r="R25">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="S25">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="T25">
-        <v>4</v>
+        <v>2.66</v>
       </c>
       <c r="U25">
-        <v>2.1</v>
+        <v>2.78</v>
       </c>
       <c r="V25">
-        <v>1.75</v>
+        <v>1.37</v>
       </c>
       <c r="W25">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="X25">
         <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="Z25">
-        <v>6</v>
+        <v>3.1</v>
       </c>
       <c r="AA25">
-        <v>1.4</v>
+        <v>1.93</v>
       </c>
       <c r="AB25">
-        <v>2.7</v>
+        <v>1.83</v>
       </c>
       <c r="AC25">
-        <v>1.99</v>
+        <v>3.3</v>
       </c>
       <c r="AD25">
-        <v>1.78</v>
+        <v>1.25</v>
       </c>
       <c r="AE25">
-        <v>1.28</v>
+        <v>1.06</v>
       </c>
       <c r="AF25">
-        <v>1.35</v>
+        <v>1.75</v>
       </c>
       <c r="AG25">
-        <v>2.94</v>
+        <v>2</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="AK25">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -8305,55 +8305,55 @@
         <v>2.75</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL49">
         <v>0</v>

--- a/jogos_2026-08-19.xlsx
+++ b/jogos_2026-08-19.xlsx
@@ -638,10 +638,10 @@
         <v>1.91</v>
       </c>
       <c r="O2">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P2">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="Q2">
         <v>2.5</v>
@@ -1794,7 +1794,7 @@
         <v>1.43</v>
       </c>
       <c r="T9">
-        <v>2.59</v>
+        <v>2.72</v>
       </c>
       <c r="U9">
         <v>3.1</v>
@@ -1815,7 +1815,7 @@
         <v>3</v>
       </c>
       <c r="AA9">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="AB9">
         <v>1.71</v>

--- a/jogos_2026-08-19.xlsx
+++ b/jogos_2026-08-19.xlsx
@@ -1133,55 +1133,55 @@
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1812,7 +1812,7 @@
         <v>1.36</v>
       </c>
       <c r="Z9">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AA9">
         <v>2.16</v>
@@ -1833,7 +1833,7 @@
         <v>1.97</v>
       </c>
       <c r="AG9">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>1.29</v>
       </c>
       <c r="AK9">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -3086,7 +3086,7 @@
         <v>6.4</v>
       </c>
       <c r="P17">
-        <v>12.84</v>
+        <v>9.5</v>
       </c>
       <c r="Q17">
         <v>1.57</v>

--- a/jogos_2026-08-19.xlsx
+++ b/jogos_2026-08-19.xlsx
@@ -638,10 +638,10 @@
         <v>1.91</v>
       </c>
       <c r="O2">
+        <v>3.5</v>
+      </c>
+      <c r="P2">
         <v>3.6</v>
-      </c>
-      <c r="P2">
-        <v>3.05</v>
       </c>
       <c r="Q2">
         <v>2.5</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="Q5">
-        <v>2.8</v>
+        <v>2.37</v>
       </c>
       <c r="R5">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="S5">
         <v>1.43</v>
       </c>
       <c r="T5">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="U5">
-        <v>2.9</v>
+        <v>3.18</v>
       </c>
       <c r="V5">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W5">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X5">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z5">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="AA5">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AB5">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AC5">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="AD5">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE5">
         <v>1.04</v>
       </c>
       <c r="AF5">
-        <v>1.88</v>
+        <v>1.97</v>
       </c>
       <c r="AG5">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AK5">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1794,7 +1794,7 @@
         <v>1.43</v>
       </c>
       <c r="T9">
-        <v>2.72</v>
+        <v>2.59</v>
       </c>
       <c r="U9">
         <v>3.1</v>
@@ -1809,22 +1809,22 @@
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="Z9">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AA9">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="AB9">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AC9">
         <v>3.83</v>
       </c>
       <c r="AD9">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AE9">
         <v>1.02</v>
@@ -1849,7 +1849,7 @@
         <v>1.29</v>
       </c>
       <c r="AK9">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="O17">
-        <v>6.4</v>
+        <v>6.25</v>
       </c>
       <c r="P17">
         <v>9.5</v>
@@ -3095,7 +3095,7 @@
         <v>2.62</v>
       </c>
       <c r="S17">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T17">
         <v>3.4</v>
@@ -3107,7 +3107,7 @@
         <v>1.55</v>
       </c>
       <c r="W17">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X17">
         <v>1.03</v>
@@ -3137,7 +3137,7 @@
         <v>2.25</v>
       </c>
       <c r="AG17">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3895,25 +3895,25 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="O22">
-        <v>4.12</v>
+        <v>4</v>
       </c>
       <c r="P22">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="Q22">
         <v>2.1</v>
       </c>
       <c r="R22">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="S22">
         <v>1.3</v>
       </c>
       <c r="T22">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="U22">
         <v>2.49</v>
@@ -3934,19 +3934,19 @@
         <v>3.9</v>
       </c>
       <c r="AA22">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AB22">
         <v>2</v>
       </c>
       <c r="AC22">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AD22">
         <v>1.4</v>
       </c>
       <c r="AE22">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF22">
         <v>1.78</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AK22">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4061,13 +4061,13 @@
         <v>1.73</v>
       </c>
       <c r="O23">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P23">
         <v>4.5</v>
       </c>
       <c r="Q23">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="R23">
         <v>2.25</v>
@@ -4076,13 +4076,13 @@
         <v>1.3</v>
       </c>
       <c r="T23">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="U23">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="V23">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="W23">
         <v>1.07</v>
@@ -4091,16 +4091,16 @@
         <v>1.04</v>
       </c>
       <c r="Y23">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z23">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="AA23">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AB23">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AC23">
         <v>2.9</v>
@@ -4115,7 +4115,7 @@
         <v>1.73</v>
       </c>
       <c r="AG23">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>1.22</v>
       </c>
       <c r="AK23">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4242,13 +4242,13 @@
         <v>4</v>
       </c>
       <c r="U24">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="V24">
         <v>1.75</v>
       </c>
       <c r="W24">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X24">
         <v>1.02</v>
@@ -4257,28 +4257,28 @@
         <v>1.12</v>
       </c>
       <c r="Z24">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AA24">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB24">
         <v>2.7</v>
       </c>
       <c r="AC24">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AD24">
         <v>1.78</v>
       </c>
       <c r="AE24">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AF24">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AG24">
-        <v>2.94</v>
+        <v>2.7</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AK24">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="O25">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="P25">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="Q25">
         <v>2.85</v>
@@ -4399,40 +4399,40 @@
         <v>2.1</v>
       </c>
       <c r="S25">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T25">
         <v>2.66</v>
       </c>
       <c r="U25">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
       <c r="V25">
         <v>1.37</v>
       </c>
       <c r="W25">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X25">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y25">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z25">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AA25">
         <v>1.93</v>
       </c>
       <c r="AB25">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC25">
         <v>3.3</v>
       </c>
       <c r="AD25">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE25">
         <v>1.06</v>
@@ -4441,7 +4441,7 @@
         <v>1.75</v>
       </c>
       <c r="AG25">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AK25">
         <v>1.51</v>
@@ -4550,10 +4550,10 @@
         <v>1.3</v>
       </c>
       <c r="O26">
-        <v>5.65</v>
+        <v>5.7</v>
       </c>
       <c r="P26">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Q26">
         <v>1.79</v>
@@ -4568,16 +4568,16 @@
         <v>3.29</v>
       </c>
       <c r="U26">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="V26">
         <v>1.47</v>
       </c>
       <c r="W26">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X26">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
         <v>1.19</v>
@@ -4586,10 +4586,10 @@
         <v>4</v>
       </c>
       <c r="AA26">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AB26">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AC26">
         <v>2.76</v>
@@ -4598,13 +4598,13 @@
         <v>1.38</v>
       </c>
       <c r="AE26">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AF26">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AG26">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>1.06</v>
       </c>
       <c r="AK26">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="O29">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5208,55 +5208,55 @@
         <v>2.35</v>
       </c>
       <c r="Q30">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="R30">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="S30">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="T30">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="U30">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="V30">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="W30">
+        <v>1.05</v>
+      </c>
+      <c r="X30">
+        <v>1.09</v>
+      </c>
+      <c r="Y30">
+        <v>1.33</v>
+      </c>
+      <c r="Z30">
+        <v>2.83</v>
+      </c>
+      <c r="AA30">
+        <v>2.17</v>
+      </c>
+      <c r="AB30">
+        <v>1.65</v>
+      </c>
+      <c r="AC30">
+        <v>3.65</v>
+      </c>
+      <c r="AD30">
+        <v>1.25</v>
+      </c>
+      <c r="AE30">
         <v>1.02</v>
-      </c>
-      <c r="X30">
-        <v>1.01</v>
-      </c>
-      <c r="Y30">
-        <v>1.32</v>
-      </c>
-      <c r="Z30">
-        <v>3.2</v>
-      </c>
-      <c r="AA30">
-        <v>2.04</v>
-      </c>
-      <c r="AB30">
-        <v>1.74</v>
-      </c>
-      <c r="AC30">
-        <v>3.5</v>
-      </c>
-      <c r="AD30">
-        <v>1.22</v>
-      </c>
-      <c r="AE30">
-        <v>1.04</v>
       </c>
       <c r="AF30">
         <v>1.75</v>
       </c>
       <c r="AG30">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="AK30">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -6838,16 +6838,16 @@
         <v>8.6</v>
       </c>
       <c r="Q40">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="R40">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="S40">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T40">
-        <v>3.2</v>
+        <v>2.66</v>
       </c>
       <c r="U40">
         <v>2.81</v>
@@ -6865,28 +6865,28 @@
         <v>1.25</v>
       </c>
       <c r="Z40">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AA40">
-        <v>1.74</v>
+        <v>1.91</v>
       </c>
       <c r="AB40">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="AC40">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD40">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE40">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF40">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AG40">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK40">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O41">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="P41">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="Q41">
         <v>2.8</v>
@@ -7007,46 +7007,46 @@
         <v>1.91</v>
       </c>
       <c r="S41">
-        <v>1.45</v>
+        <v>1.61</v>
       </c>
       <c r="T41">
-        <v>2.35</v>
+        <v>2.21</v>
       </c>
       <c r="U41">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="V41">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="W41">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X41">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Y41">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="Z41">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="AA41">
         <v>2.43</v>
       </c>
       <c r="AB41">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AC41">
-        <v>4.55</v>
+        <v>5</v>
       </c>
       <c r="AD41">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AE41">
         <v>1.03</v>
       </c>
       <c r="AF41">
-        <v>2.01</v>
+        <v>2.18</v>
       </c>
       <c r="AG41">
         <v>1.68</v>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="AK41">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7653,16 +7653,16 @@
         <v>2.66</v>
       </c>
       <c r="Q45">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R45">
         <v>1.8</v>
       </c>
       <c r="S45">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="T45">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="U45">
         <v>3.6</v>
@@ -7674,16 +7674,16 @@
         <v>1.04</v>
       </c>
       <c r="X45">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="Y45">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="Z45">
         <v>2.33</v>
       </c>
       <c r="AA45">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="AB45">
         <v>1.46</v>
@@ -7695,7 +7695,7 @@
         <v>1.16</v>
       </c>
       <c r="AE45">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF45">
         <v>2.08</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AK45">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AL45">
         <v>0</v>

--- a/jogos_2026-08-19.xlsx
+++ b/jogos_2026-08-19.xlsx
@@ -3415,56 +3415,56 @@
         <v>4.6</v>
       </c>
       <c r="Q19">
-        <v>2.8</v>
+        <v>2.44</v>
       </c>
       <c r="R19">
-        <v>1.74</v>
+        <v>1.89</v>
       </c>
       <c r="S19">
+        <v>1.5</v>
+      </c>
+      <c r="T19">
+        <v>2.3</v>
+      </c>
+      <c r="U19">
+        <v>3.5</v>
+      </c>
+      <c r="V19">
+        <v>1.3</v>
+      </c>
+      <c r="W19">
+        <v>1.05</v>
+      </c>
+      <c r="X19">
+        <v>1.1</v>
+      </c>
+      <c r="Y19">
+        <v>1.5</v>
+      </c>
+      <c r="Z19">
+        <v>2.53</v>
+      </c>
+      <c r="AA19">
+        <v>2.49</v>
+      </c>
+      <c r="AB19">
+        <v>1.47</v>
+      </c>
+      <c r="AC19">
+        <v>4.7</v>
+      </c>
+      <c r="AD19">
+        <v>1.11</v>
+      </c>
+      <c r="AE19">
+        <v>1.05</v>
+      </c>
+      <c r="AF19">
+        <v>2.23</v>
+      </c>
+      <c r="AG19">
         <v>1.6</v>
       </c>
-      <c r="T19">
-        <v>2.2</v>
-      </c>
-      <c r="U19">
-        <v>3.75</v>
-      </c>
-      <c r="V19">
-        <v>1.22</v>
-      </c>
-      <c r="W19">
-        <v>1.03</v>
-      </c>
-      <c r="X19">
-        <v>1.15</v>
-      </c>
-      <c r="Y19">
-        <v>1.65</v>
-      </c>
-      <c r="Z19">
-        <v>2.23</v>
-      </c>
-      <c r="AA19">
-        <v>2.88</v>
-      </c>
-      <c r="AB19">
-        <v>1.4</v>
-      </c>
-      <c r="AC19">
-        <v>5.5</v>
-      </c>
-      <c r="AD19">
-        <v>1.08</v>
-      </c>
-      <c r="AE19">
-        <v>1.03</v>
-      </c>
-      <c r="AF19">
-        <v>2.4</v>
-      </c>
-      <c r="AG19">
-        <v>1.5</v>
-      </c>
       <c r="AH19" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AK19">
-        <v>1.69</v>
+        <v>1.95</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -4882,55 +4882,55 @@
         <v>0</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK28">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.63</v>
+        <v>2.94</v>
       </c>
       <c r="O29">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P29">
-        <v>5</v>
+        <v>2.35</v>
       </c>
       <c r="Q29">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="R29">
-        <v>2.19</v>
+        <v>2</v>
       </c>
       <c r="S29">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="T29">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="U29">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="V29">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W29">
         <v>1.05</v>
       </c>
       <c r="X29">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y29">
         <v>1.33</v>
       </c>
       <c r="Z29">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="AA29">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="AB29">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AC29">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="AD29">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE29">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF29">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AG29">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK29">
-        <v>2.2</v>
+        <v>1.35</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,80 +5199,80 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.94</v>
+        <v>1.68</v>
       </c>
       <c r="O30">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P30">
-        <v>2.35</v>
+        <v>4.75</v>
       </c>
       <c r="Q30">
-        <v>3.25</v>
+        <v>2.25</v>
       </c>
       <c r="R30">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="S30">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="T30">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="U30">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="V30">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W30">
         <v>1.05</v>
       </c>
       <c r="X30">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="Y30">
         <v>1.33</v>
       </c>
       <c r="Z30">
-        <v>2.83</v>
+        <v>2.99</v>
       </c>
       <c r="AA30">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AB30">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC30">
-        <v>3.65</v>
+        <v>3.93</v>
       </c>
       <c r="AD30">
+        <v>1.21</v>
+      </c>
+      <c r="AE30">
+        <v>1.04</v>
+      </c>
+      <c r="AF30">
+        <v>2</v>
+      </c>
+      <c r="AG30">
+        <v>1.67</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30">
         <v>1.25</v>
       </c>
-      <c r="AE30">
-        <v>1.02</v>
-      </c>
-      <c r="AF30">
-        <v>1.75</v>
-      </c>
-      <c r="AG30">
-        <v>1.86</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ30">
-        <v>1.32</v>
-      </c>
       <c r="AK30">
-        <v>1.42</v>
+        <v>2.2</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5688,16 +5688,16 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="O33">
-        <v>4.2</v>
+        <v>4.74</v>
       </c>
       <c r="P33">
-        <v>5.11</v>
+        <v>5.09</v>
       </c>
       <c r="Q33">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="R33">
         <v>2.45</v>
@@ -5706,7 +5706,7 @@
         <v>1.22</v>
       </c>
       <c r="T33">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="U33">
         <v>2.2</v>
@@ -5715,13 +5715,13 @@
         <v>1.62</v>
       </c>
       <c r="W33">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X33">
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Z33">
         <v>5</v>
@@ -5730,19 +5730,19 @@
         <v>1.5</v>
       </c>
       <c r="AB33">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="AC33">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AD33">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AE33">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF33">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AG33">
         <v>2.25</v>
@@ -5851,43 +5851,43 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="O34">
-        <v>3.5</v>
+        <v>3.94</v>
       </c>
       <c r="P34">
-        <v>3.07</v>
+        <v>2.9</v>
       </c>
       <c r="Q34">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="R34">
-        <v>2.23</v>
+        <v>2.41</v>
       </c>
       <c r="S34">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T34">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="U34">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="V34">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="W34">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X34">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y34">
         <v>1.17</v>
       </c>
       <c r="Z34">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
       <c r="AA34">
         <v>1.65</v>
@@ -5896,10 +5896,10 @@
         <v>2.3</v>
       </c>
       <c r="AC34">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AD34">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AE34">
         <v>1.13</v>
@@ -5908,7 +5908,7 @@
         <v>1.53</v>
       </c>
       <c r="AG34">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AK34">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6017,13 +6017,13 @@
         <v>2</v>
       </c>
       <c r="O35">
-        <v>4</v>
+        <v>4.37</v>
       </c>
       <c r="P35">
-        <v>2.8</v>
+        <v>2.97</v>
       </c>
       <c r="Q35">
-        <v>2.55</v>
+        <v>2.32</v>
       </c>
       <c r="R35">
         <v>2.45</v>
@@ -6035,10 +6035,10 @@
         <v>4.1</v>
       </c>
       <c r="U35">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="V35">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W35">
         <v>1.18</v>
@@ -6047,16 +6047,16 @@
         <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z35">
         <v>5.75</v>
       </c>
       <c r="AA35">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AB35">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AC35">
         <v>2.08</v>
@@ -6065,7 +6065,7 @@
         <v>1.72</v>
       </c>
       <c r="AE35">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF35">
         <v>1.4</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AK35">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="O36">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P36">
-        <v>3.36</v>
+        <v>3.1</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6349,7 +6349,7 @@
         <v>2.42</v>
       </c>
       <c r="Q37">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="R37">
         <v>2.5</v>
@@ -6373,31 +6373,31 @@
         <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z37">
-        <v>6.25</v>
+        <v>5.75</v>
       </c>
       <c r="AA37">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AB37">
-        <v>3.15</v>
+        <v>2.75</v>
       </c>
       <c r="AC37">
         <v>2.05</v>
       </c>
       <c r="AD37">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AE37">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AF37">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="AG37">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK37">
         <v>1.5</v>
@@ -6503,31 +6503,31 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="O38">
-        <v>4.16</v>
+        <v>3.9</v>
       </c>
       <c r="P38">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="Q38">
         <v>2.9</v>
       </c>
       <c r="R38">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="S38">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T38">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="U38">
         <v>2.2</v>
       </c>
       <c r="V38">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W38">
         <v>1.17</v>
@@ -6536,31 +6536,31 @@
         <v>1.03</v>
       </c>
       <c r="Y38">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z38">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AA38">
         <v>1.5</v>
       </c>
       <c r="AB38">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AC38">
         <v>2.28</v>
       </c>
       <c r="AD38">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AE38">
         <v>1.23</v>
       </c>
       <c r="AF38">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG38">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6669,10 +6669,10 @@
         <v>2.6</v>
       </c>
       <c r="O39">
-        <v>3.75</v>
+        <v>4.38</v>
       </c>
       <c r="P39">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="Q39">
         <v>3.5</v>
@@ -6681,7 +6681,7 @@
         <v>2.63</v>
       </c>
       <c r="S39">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T39">
         <v>4.8</v>
@@ -6699,19 +6699,19 @@
         <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Z39">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA39">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AB39">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="AC39">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="AD39">
         <v>1.83</v>
@@ -6723,7 +6723,7 @@
         <v>1.32</v>
       </c>
       <c r="AG39">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6844,10 +6844,10 @@
         <v>2.42</v>
       </c>
       <c r="S40">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T40">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="U40">
         <v>2.81</v>
@@ -6886,7 +6886,7 @@
         <v>2.1</v>
       </c>
       <c r="AG40">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>3.4</v>
       </c>
       <c r="Q41">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R41">
         <v>1.91</v>
@@ -7010,10 +7010,10 @@
         <v>1.61</v>
       </c>
       <c r="T41">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="U41">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="V41">
         <v>1.21</v>
@@ -7022,7 +7022,7 @@
         <v>1.04</v>
       </c>
       <c r="X41">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Y41">
         <v>1.46</v>
@@ -7034,19 +7034,19 @@
         <v>2.43</v>
       </c>
       <c r="AB41">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AC41">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AD41">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AE41">
         <v>1.03</v>
       </c>
       <c r="AF41">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="AG41">
         <v>1.68</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>3.17</v>
+        <v>3.4</v>
       </c>
       <c r="O43">
         <v>3.7</v>
       </c>
       <c r="P43">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="Q43">
         <v>3.5</v>
@@ -7333,40 +7333,40 @@
         <v>2.5</v>
       </c>
       <c r="S43">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T43">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U43">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="V43">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W43">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X43">
         <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z43">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AA43">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AB43">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AC43">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AD43">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AE43">
         <v>1.25</v>
@@ -7375,7 +7375,7 @@
         <v>1.44</v>
       </c>
       <c r="AG43">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>1.22</v>
       </c>
       <c r="AK43">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,19 +7481,19 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="O44">
-        <v>4.16</v>
+        <v>3.75</v>
       </c>
       <c r="P44">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q44">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="R44">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S44">
         <v>1.3</v>
@@ -7505,19 +7505,19 @@
         <v>2.41</v>
       </c>
       <c r="V44">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W44">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X44">
         <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z44">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AA44">
         <v>1.68</v>
@@ -7532,7 +7532,7 @@
         <v>1.48</v>
       </c>
       <c r="AE44">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF44">
         <v>1.61</v>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK44">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7819,46 +7819,46 @@
         <v>2.1</v>
       </c>
       <c r="R46">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="S46">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T46">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U46">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="V46">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W46">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X46">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z46">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA46">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AB46">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC46">
         <v>2.39</v>
       </c>
       <c r="AD46">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AE46">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF46">
         <v>1.65</v>
@@ -7880,7 +7880,7 @@
         <v>1.18</v>
       </c>
       <c r="AK46">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.77</v>
+        <v>2.62</v>
       </c>
       <c r="O47">
-        <v>4.01</v>
+        <v>3.5</v>
       </c>
       <c r="P47">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q47">
         <v>3.1</v>
@@ -7988,31 +7988,31 @@
         <v>1.25</v>
       </c>
       <c r="T47">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="U47">
         <v>2.3</v>
       </c>
       <c r="V47">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W47">
         <v>1.08</v>
       </c>
       <c r="X47">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y47">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z47">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="AA47">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AB47">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AC47">
         <v>2.55</v>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AK47">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8136,16 +8136,16 @@
         <v>1.85</v>
       </c>
       <c r="O48">
-        <v>4.34</v>
+        <v>4</v>
       </c>
       <c r="P48">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="Q48">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="R48">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S48">
         <v>1.2</v>
@@ -8154,7 +8154,7 @@
         <v>3.66</v>
       </c>
       <c r="U48">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="V48">
         <v>1.65</v>
@@ -8184,7 +8184,7 @@
         <v>1.6</v>
       </c>
       <c r="AE48">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF48">
         <v>1.44</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="O49">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P49">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="Q49">
         <v>2.85</v>
@@ -8317,10 +8317,10 @@
         <v>3.08</v>
       </c>
       <c r="U49">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="V49">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W49">
         <v>1.09</v>
@@ -8332,28 +8332,28 @@
         <v>1.17</v>
       </c>
       <c r="Z49">
-        <v>3.95</v>
+        <v>3.94</v>
       </c>
       <c r="AA49">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB49">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="AC49">
-        <v>2.52</v>
+        <v>2.43</v>
       </c>
       <c r="AD49">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AE49">
         <v>1.13</v>
       </c>
       <c r="AF49">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG49">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK49">
         <v>1.47</v>
@@ -8459,58 +8459,58 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="O50">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="P50">
         <v>2.9</v>
       </c>
       <c r="Q50">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="R50">
         <v>2.54</v>
       </c>
       <c r="S50">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="T50">
         <v>4.4</v>
       </c>
       <c r="U50">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="V50">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="W50">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X50">
         <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="Z50">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AA50">
         <v>1.28</v>
       </c>
       <c r="AB50">
-        <v>3.08</v>
+        <v>3.45</v>
       </c>
       <c r="AC50">
+        <v>1.77</v>
+      </c>
+      <c r="AD50">
         <v>1.85</v>
       </c>
-      <c r="AD50">
-        <v>2</v>
-      </c>
       <c r="AE50">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AF50">
         <v>1.33</v>
@@ -8625,16 +8625,16 @@
         <v>1.46</v>
       </c>
       <c r="O51">
-        <v>4.75</v>
+        <v>5.22</v>
       </c>
       <c r="P51">
-        <v>6.32</v>
+        <v>5</v>
       </c>
       <c r="Q51">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="R51">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="S51">
         <v>1.22</v>
@@ -8652,31 +8652,31 @@
         <v>1.18</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z51">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="AA51">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AB51">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AC51">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AD51">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AE51">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AF51">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AG51">
         <v>2.18</v>
@@ -8695,7 +8695,7 @@
         <v>1.18</v>
       </c>
       <c r="AK51">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8791,34 +8791,34 @@
         <v>3.7</v>
       </c>
       <c r="P52">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="Q52">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="R52">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="S52">
         <v>1.2</v>
       </c>
       <c r="T52">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="U52">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V52">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="W52">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X52">
         <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Z52">
         <v>5.5</v>
@@ -8836,7 +8836,7 @@
         <v>1.7</v>
       </c>
       <c r="AE52">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF52">
         <v>1.4</v>
@@ -8855,7 +8855,7 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AK52">
         <v>1.6</v>

--- a/jogos_2026-08-19.xlsx
+++ b/jogos_2026-08-19.xlsx
@@ -4550,7 +4550,7 @@
         <v>1.3</v>
       </c>
       <c r="O26">
-        <v>5.7</v>
+        <v>5.65</v>
       </c>
       <c r="P26">
         <v>10</v>
@@ -4565,7 +4565,7 @@
         <v>1.3</v>
       </c>
       <c r="T26">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="U26">
         <v>2.44</v>
@@ -5045,7 +5045,7 @@
         <v>2.35</v>
       </c>
       <c r="Q29">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="R29">
         <v>2</v>
@@ -5066,13 +5066,13 @@
         <v>1.05</v>
       </c>
       <c r="X29">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y29">
         <v>1.33</v>
       </c>
       <c r="Z29">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="AA29">
         <v>2.17</v>
@@ -5081,7 +5081,7 @@
         <v>1.65</v>
       </c>
       <c r="AC29">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="AD29">
         <v>1.22</v>
@@ -5199,10 +5199,10 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="O30">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P30">
         <v>4.75</v>
@@ -5220,7 +5220,7 @@
         <v>2.62</v>
       </c>
       <c r="U30">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="V30">
         <v>1.32</v>
@@ -5238,13 +5238,13 @@
         <v>2.99</v>
       </c>
       <c r="AA30">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AB30">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AC30">
-        <v>3.93</v>
+        <v>3.58</v>
       </c>
       <c r="AD30">
         <v>1.21</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="O33">
-        <v>4.74</v>
+        <v>4.64</v>
       </c>
       <c r="P33">
-        <v>5.09</v>
+        <v>4.98</v>
       </c>
       <c r="Q33">
         <v>2</v>
@@ -5712,7 +5712,7 @@
         <v>2.2</v>
       </c>
       <c r="V33">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="W33">
         <v>1.15</v>
@@ -5745,7 +5745,7 @@
         <v>1.56</v>
       </c>
       <c r="AG33">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5860,10 +5860,10 @@
         <v>2.9</v>
       </c>
       <c r="Q34">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="R34">
-        <v>2.41</v>
+        <v>2.25</v>
       </c>
       <c r="S34">
         <v>1.3</v>
@@ -5872,7 +5872,7 @@
         <v>3.3</v>
       </c>
       <c r="U34">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="V34">
         <v>1.53</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
+        <v>2.1</v>
+      </c>
+      <c r="O35">
+        <v>3.4</v>
+      </c>
+      <c r="P35">
+        <v>3</v>
+      </c>
+      <c r="Q35">
+        <v>0</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35">
+        <v>0</v>
+      </c>
+      <c r="T35">
+        <v>0</v>
+      </c>
+      <c r="U35">
+        <v>0</v>
+      </c>
+      <c r="V35">
+        <v>0</v>
+      </c>
+      <c r="W35">
+        <v>0</v>
+      </c>
+      <c r="X35">
+        <v>0</v>
+      </c>
+      <c r="Y35">
+        <v>0</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+      <c r="AA35">
+        <v>1.8</v>
+      </c>
+      <c r="AB35">
         <v>2</v>
       </c>
-      <c r="O35">
-        <v>4.37</v>
-      </c>
-      <c r="P35">
-        <v>2.97</v>
-      </c>
-      <c r="Q35">
-        <v>2.32</v>
-      </c>
-      <c r="R35">
-        <v>2.45</v>
-      </c>
-      <c r="S35">
-        <v>1.22</v>
-      </c>
-      <c r="T35">
-        <v>4.1</v>
-      </c>
-      <c r="U35">
-        <v>2.07</v>
-      </c>
-      <c r="V35">
-        <v>1.68</v>
-      </c>
-      <c r="W35">
-        <v>1.18</v>
-      </c>
-      <c r="X35">
-        <v>1.02</v>
-      </c>
-      <c r="Y35">
-        <v>1.11</v>
-      </c>
-      <c r="Z35">
-        <v>5.75</v>
-      </c>
-      <c r="AA35">
-        <v>1.44</v>
-      </c>
-      <c r="AB35">
-        <v>2.75</v>
-      </c>
       <c r="AC35">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AD35">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE35">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AF35">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG35">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK35">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
+        <v>2.34</v>
+      </c>
+      <c r="O36">
+        <v>3.75</v>
+      </c>
+      <c r="P36">
+        <v>2.57</v>
+      </c>
+      <c r="Q36">
+        <v>2.7</v>
+      </c>
+      <c r="R36">
+        <v>2.5</v>
+      </c>
+      <c r="S36">
+        <v>1.22</v>
+      </c>
+      <c r="T36">
+        <v>4</v>
+      </c>
+      <c r="U36">
         <v>2.07</v>
       </c>
-      <c r="O36">
-        <v>3.5</v>
-      </c>
-      <c r="P36">
-        <v>3.1</v>
-      </c>
-      <c r="Q36">
-        <v>0</v>
-      </c>
-      <c r="R36">
-        <v>0</v>
-      </c>
-      <c r="S36">
-        <v>0</v>
-      </c>
-      <c r="T36">
-        <v>0</v>
-      </c>
-      <c r="U36">
-        <v>0</v>
-      </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA36">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="AB36">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.47</v>
+        <v>2.6</v>
       </c>
       <c r="O37">
-        <v>3.8</v>
+        <v>4.38</v>
       </c>
       <c r="P37">
-        <v>2.42</v>
+        <v>2.12</v>
       </c>
       <c r="Q37">
-        <v>2.75</v>
+        <v>3.13</v>
       </c>
       <c r="R37">
         <v>2.5</v>
       </c>
       <c r="S37">
+        <v>1.2</v>
+      </c>
+      <c r="T37">
+        <v>4.8</v>
+      </c>
+      <c r="U37">
+        <v>1.85</v>
+      </c>
+      <c r="V37">
+        <v>1.77</v>
+      </c>
+      <c r="W37">
         <v>1.22</v>
-      </c>
-      <c r="T37">
-        <v>4</v>
-      </c>
-      <c r="U37">
-        <v>2.02</v>
-      </c>
-      <c r="V37">
-        <v>1.74</v>
-      </c>
-      <c r="W37">
-        <v>1.2</v>
       </c>
       <c r="X37">
         <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z37">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="AA37">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB37">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AC37">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AD37">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AE37">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AF37">
         <v>1.32</v>
       </c>
       <c r="AG37">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>1.2</v>
       </c>
       <c r="AK37">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,55 +6503,55 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.7</v>
+        <v>2.03</v>
       </c>
       <c r="O38">
-        <v>3.9</v>
+        <v>4.36</v>
       </c>
       <c r="P38">
-        <v>2.25</v>
+        <v>3.15</v>
       </c>
       <c r="Q38">
-        <v>2.9</v>
+        <v>2.32</v>
       </c>
       <c r="R38">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S38">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T38">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="U38">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="V38">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="W38">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X38">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="Z38">
-        <v>5.3</v>
+        <v>5.55</v>
       </c>
       <c r="AA38">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AB38">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="AC38">
-        <v>2.28</v>
+        <v>2.13</v>
       </c>
       <c r="AD38">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AE38">
         <v>1.23</v>
@@ -6560,7 +6560,7 @@
         <v>1.4</v>
       </c>
       <c r="AG38">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="AK38">
-        <v>1.4</v>
+        <v>1.77</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,80 +6666,80 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="O39">
-        <v>4.38</v>
+        <v>3.6</v>
       </c>
       <c r="P39">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="Q39">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="R39">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="S39">
         <v>1.2</v>
       </c>
       <c r="T39">
-        <v>4.8</v>
+        <v>3.55</v>
       </c>
       <c r="U39">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="V39">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="W39">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="X39">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y39">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z39">
-        <v>6.5</v>
+        <v>5.3</v>
       </c>
       <c r="AA39">
+        <v>1.5</v>
+      </c>
+      <c r="AB39">
+        <v>2.4</v>
+      </c>
+      <c r="AC39">
+        <v>2.28</v>
+      </c>
+      <c r="AD39">
+        <v>1.57</v>
+      </c>
+      <c r="AE39">
+        <v>1.23</v>
+      </c>
+      <c r="AF39">
+        <v>1.4</v>
+      </c>
+      <c r="AG39">
+        <v>2.6</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39">
+        <v>1.6</v>
+      </c>
+      <c r="AK39">
         <v>1.36</v>
-      </c>
-      <c r="AB39">
-        <v>3</v>
-      </c>
-      <c r="AC39">
-        <v>1.89</v>
-      </c>
-      <c r="AD39">
-        <v>1.83</v>
-      </c>
-      <c r="AE39">
-        <v>1.38</v>
-      </c>
-      <c r="AF39">
-        <v>1.32</v>
-      </c>
-      <c r="AG39">
-        <v>3.1</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39">
-        <v>1.22</v>
-      </c>
-      <c r="AK39">
-        <v>1.4</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6844,22 +6844,22 @@
         <v>2.42</v>
       </c>
       <c r="S40">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T40">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="U40">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="V40">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W40">
         <v>1.06</v>
       </c>
       <c r="X40">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y40">
         <v>1.25</v>
@@ -6880,13 +6880,13 @@
         <v>1.29</v>
       </c>
       <c r="AE40">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF40">
         <v>2.1</v>
       </c>
       <c r="AG40">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK40">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7046,7 +7046,7 @@
         <v>1.03</v>
       </c>
       <c r="AF41">
-        <v>2.16</v>
+        <v>2.04</v>
       </c>
       <c r="AG41">
         <v>1.68</v>
@@ -7324,7 +7324,7 @@
         <v>3.7</v>
       </c>
       <c r="P43">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="Q43">
         <v>3.5</v>
@@ -7351,7 +7351,7 @@
         <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="Z43">
         <v>5</v>
@@ -7363,13 +7363,13 @@
         <v>2.6</v>
       </c>
       <c r="AC43">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="AD43">
         <v>1.62</v>
       </c>
       <c r="AE43">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF43">
         <v>1.44</v>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="O44">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P44">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="Q44">
         <v>2.27</v>
@@ -7526,7 +7526,7 @@
         <v>2.08</v>
       </c>
       <c r="AC44">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="AD44">
         <v>1.48</v>
@@ -7674,10 +7674,10 @@
         <v>1.04</v>
       </c>
       <c r="X45">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="Y45">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Z45">
         <v>2.33</v>
@@ -7807,10 +7807,10 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="O46">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="P46">
         <v>4.33</v>
@@ -7840,10 +7840,10 @@
         <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z46">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AA46">
         <v>1.61</v>
@@ -7982,7 +7982,7 @@
         <v>3.1</v>
       </c>
       <c r="R47">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="S47">
         <v>1.25</v>
@@ -8003,13 +8003,13 @@
         <v>1.03</v>
       </c>
       <c r="Y47">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z47">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="AA47">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB47">
         <v>2.25</v>
@@ -8027,7 +8027,7 @@
         <v>1.5</v>
       </c>
       <c r="AG47">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         <v>4</v>
       </c>
       <c r="P48">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="Q48">
         <v>2.25</v>
@@ -8151,10 +8151,10 @@
         <v>1.2</v>
       </c>
       <c r="T48">
-        <v>3.66</v>
+        <v>3.8</v>
       </c>
       <c r="U48">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V48">
         <v>1.65</v>
@@ -8187,7 +8187,7 @@
         <v>1.25</v>
       </c>
       <c r="AF48">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AG48">
         <v>2.5</v>
@@ -8299,22 +8299,22 @@
         <v>2.4</v>
       </c>
       <c r="O49">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P49">
         <v>2.6</v>
       </c>
       <c r="Q49">
-        <v>2.85</v>
+        <v>2.93</v>
       </c>
       <c r="R49">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="S49">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T49">
-        <v>3.08</v>
+        <v>3.02</v>
       </c>
       <c r="U49">
         <v>2.5</v>
@@ -8323,19 +8323,19 @@
         <v>1.5</v>
       </c>
       <c r="W49">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X49">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="Z49">
-        <v>3.94</v>
+        <v>3.74</v>
       </c>
       <c r="AA49">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB49">
         <v>2.12</v>
@@ -8344,10 +8344,10 @@
         <v>2.43</v>
       </c>
       <c r="AD49">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE49">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF49">
         <v>1.5</v>
@@ -8369,7 +8369,7 @@
         <v>1.22</v>
       </c>
       <c r="AK49">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="O50">
         <v>3.9</v>
@@ -8468,49 +8468,49 @@
         <v>2.9</v>
       </c>
       <c r="Q50">
-        <v>2.43</v>
+        <v>2.48</v>
       </c>
       <c r="R50">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="S50">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="T50">
         <v>4.4</v>
       </c>
       <c r="U50">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="V50">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="W50">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="X50">
         <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Z50">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="AA50">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AB50">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="AC50">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AD50">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AE50">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AF50">
         <v>1.33</v>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK50">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,10 +8622,10 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="O51">
-        <v>5.22</v>
+        <v>5.1</v>
       </c>
       <c r="P51">
         <v>5</v>
@@ -8658,7 +8658,7 @@
         <v>1.13</v>
       </c>
       <c r="Z51">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AA51">
         <v>1.5</v>
@@ -8794,25 +8794,25 @@
         <v>2.5</v>
       </c>
       <c r="Q52">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="R52">
         <v>2.55</v>
       </c>
       <c r="S52">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T52">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="U52">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="V52">
         <v>1.7</v>
       </c>
       <c r="W52">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X52">
         <v>1.02</v>
@@ -8858,7 +8858,7 @@
         <v>1.38</v>
       </c>
       <c r="AK52">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AL52">
         <v>0</v>

--- a/jogos_2026-08-19.xlsx
+++ b/jogos_2026-08-19.xlsx
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q28">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R28">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="S28">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="T28">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U28">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V28">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="W28">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X28">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y28">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z28">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA28">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AB28">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AC28">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AD28">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE28">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF28">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG28">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK28">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="Q42">
         <v>0</v>

--- a/jogos_2026-08-19.xlsx
+++ b/jogos_2026-08-19.xlsx
@@ -638,7 +638,7 @@
         <v>1.91</v>
       </c>
       <c r="O2">
-        <v>3.5</v>
+        <v>3.76</v>
       </c>
       <c r="P2">
         <v>3.6</v>
@@ -1133,22 +1133,22 @@
         <v>4.55</v>
       </c>
       <c r="Q5">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="R5">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="S5">
         <v>1.43</v>
       </c>
       <c r="T5">
-        <v>2.73</v>
+        <v>2.59</v>
       </c>
       <c r="U5">
-        <v>3.18</v>
+        <v>3.05</v>
       </c>
       <c r="V5">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W5">
         <v>1.03</v>
@@ -1157,10 +1157,10 @@
         <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z5">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="AA5">
         <v>2.12</v>
@@ -1172,7 +1172,7 @@
         <v>3.68</v>
       </c>
       <c r="AD5">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE5">
         <v>1.04</v>
@@ -1779,61 +1779,61 @@
         <v>3.85</v>
       </c>
       <c r="O9">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P9">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q9">
         <v>5.2</v>
       </c>
       <c r="R9">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="S9">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="T9">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
       <c r="U9">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="V9">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="W9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X9">
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z9">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="AA9">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AB9">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AC9">
-        <v>3.83</v>
+        <v>3.7</v>
       </c>
       <c r="AD9">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AE9">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF9">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="AG9">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.29</v>
+        <v>2.05</v>
       </c>
       <c r="AK9">
         <v>1.18</v>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="O17">
-        <v>6.25</v>
+        <v>6.4</v>
       </c>
       <c r="P17">
         <v>9.5</v>
@@ -3092,10 +3092,10 @@
         <v>1.57</v>
       </c>
       <c r="R17">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="S17">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T17">
         <v>3.4</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AK17">
         <v>4</v>
@@ -3418,7 +3418,7 @@
         <v>2.44</v>
       </c>
       <c r="R19">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="S19">
         <v>1.5</v>
@@ -3445,13 +3445,13 @@
         <v>2.53</v>
       </c>
       <c r="AA19">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="AB19">
         <v>1.47</v>
       </c>
       <c r="AC19">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AD19">
         <v>1.11</v>
@@ -3919,7 +3919,7 @@
         <v>2.49</v>
       </c>
       <c r="V22">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W22">
         <v>1.06</v>
@@ -3952,7 +3952,7 @@
         <v>1.78</v>
       </c>
       <c r="AG22">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AK22">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,7 +4058,7 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="O23">
         <v>3.9</v>
@@ -4230,10 +4230,10 @@
         <v>2.5</v>
       </c>
       <c r="Q24">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="R24">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="S24">
         <v>1.2</v>
@@ -4260,7 +4260,7 @@
         <v>5.75</v>
       </c>
       <c r="AA24">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AB24">
         <v>2.7</v>
@@ -4269,7 +4269,7 @@
         <v>2</v>
       </c>
       <c r="AD24">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AE24">
         <v>1.3</v>
@@ -4278,7 +4278,7 @@
         <v>1.4</v>
       </c>
       <c r="AG24">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK24">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4387,10 +4387,10 @@
         <v>2.17</v>
       </c>
       <c r="O25">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="P25">
-        <v>3.1</v>
+        <v>2.77</v>
       </c>
       <c r="Q25">
         <v>2.85</v>
@@ -4426,7 +4426,7 @@
         <v>1.93</v>
       </c>
       <c r="AB25">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AC25">
         <v>3.3</v>
@@ -4457,7 +4457,7 @@
         <v>1.37</v>
       </c>
       <c r="AK25">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="O26">
         <v>5.65</v>
@@ -4565,7 +4565,7 @@
         <v>1.3</v>
       </c>
       <c r="T26">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="U26">
         <v>2.44</v>
@@ -4577,34 +4577,34 @@
         <v>1.09</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
         <v>1.19</v>
       </c>
       <c r="Z26">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AA26">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AB26">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AC26">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="AD26">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE26">
         <v>1.1</v>
       </c>
       <c r="AF26">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AG26">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4882,55 +4882,55 @@
         <v>2.25</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5045,10 +5045,10 @@
         <v>2.35</v>
       </c>
       <c r="Q29">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="R29">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S29">
         <v>1.47</v>
@@ -5066,7 +5066,7 @@
         <v>1.05</v>
       </c>
       <c r="X29">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y29">
         <v>1.33</v>
@@ -5090,7 +5090,7 @@
         <v>1.02</v>
       </c>
       <c r="AF29">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AG29">
         <v>1.86</v>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AK29">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5205,7 +5205,7 @@
         <v>3.4</v>
       </c>
       <c r="P30">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="Q30">
         <v>2.25</v>
@@ -5214,7 +5214,7 @@
         <v>2.19</v>
       </c>
       <c r="S30">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T30">
         <v>2.62</v>
@@ -5226,7 +5226,7 @@
         <v>1.32</v>
       </c>
       <c r="W30">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X30">
         <v>1.03</v>
@@ -5238,7 +5238,7 @@
         <v>2.99</v>
       </c>
       <c r="AA30">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="AB30">
         <v>1.68</v>
@@ -5272,7 +5272,7 @@
         <v>1.25</v>
       </c>
       <c r="AK30">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5691,10 +5691,10 @@
         <v>1.57</v>
       </c>
       <c r="O33">
-        <v>4.64</v>
+        <v>4.6</v>
       </c>
       <c r="P33">
-        <v>4.98</v>
+        <v>4.9</v>
       </c>
       <c r="Q33">
         <v>2</v>
@@ -5712,7 +5712,7 @@
         <v>2.2</v>
       </c>
       <c r="V33">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W33">
         <v>1.15</v>
@@ -5727,10 +5727,10 @@
         <v>5</v>
       </c>
       <c r="AA33">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AB33">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="AC33">
         <v>2.3</v>
@@ -5745,7 +5745,7 @@
         <v>1.56</v>
       </c>
       <c r="AG33">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
         <v>1.17</v>
       </c>
       <c r="AK33">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,31 +5851,31 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="O34">
         <v>3.94</v>
       </c>
       <c r="P34">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="Q34">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="R34">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S34">
         <v>1.3</v>
       </c>
       <c r="T34">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U34">
         <v>2.48</v>
       </c>
       <c r="V34">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W34">
         <v>1.12</v>
@@ -5884,16 +5884,16 @@
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z34">
         <v>4.15</v>
       </c>
       <c r="AA34">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB34">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AC34">
         <v>2.63</v>
@@ -5908,7 +5908,7 @@
         <v>1.53</v>
       </c>
       <c r="AG34">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AK34">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="O35">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="P35">
         <v>3</v>
@@ -6183,28 +6183,28 @@
         <v>3.75</v>
       </c>
       <c r="P36">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="Q36">
         <v>2.7</v>
       </c>
       <c r="R36">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S36">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T36">
-        <v>4</v>
+        <v>3.66</v>
       </c>
       <c r="U36">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="V36">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="W36">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X36">
         <v>1.01</v>
@@ -6216,10 +6216,10 @@
         <v>5.75</v>
       </c>
       <c r="AA36">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB36">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AC36">
         <v>2.05</v>
@@ -6228,7 +6228,7 @@
         <v>1.73</v>
       </c>
       <c r="AE36">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AF36">
         <v>1.36</v>
@@ -6340,19 +6340,19 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="O37">
-        <v>4.38</v>
+        <v>4.47</v>
       </c>
       <c r="P37">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="Q37">
         <v>3.13</v>
       </c>
       <c r="R37">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="S37">
         <v>1.2</v>
@@ -6361,7 +6361,7 @@
         <v>4.8</v>
       </c>
       <c r="U37">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="V37">
         <v>1.77</v>
@@ -6379,13 +6379,13 @@
         <v>6.5</v>
       </c>
       <c r="AA37">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB37">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AC37">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AD37">
         <v>1.83</v>
@@ -6503,19 +6503,19 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="O38">
-        <v>4.36</v>
+        <v>3.75</v>
       </c>
       <c r="P38">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="Q38">
         <v>2.32</v>
       </c>
       <c r="R38">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S38">
         <v>1.22</v>
@@ -6527,7 +6527,7 @@
         <v>2.07</v>
       </c>
       <c r="V38">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="W38">
         <v>1.18</v>
@@ -6539,28 +6539,28 @@
         <v>1.11</v>
       </c>
       <c r="Z38">
-        <v>5.55</v>
+        <v>5.7</v>
       </c>
       <c r="AA38">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AB38">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AC38">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AD38">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AE38">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AF38">
         <v>1.4</v>
       </c>
       <c r="AG38">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>1.36</v>
       </c>
       <c r="AK38">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6666,16 +6666,16 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="O39">
-        <v>3.6</v>
+        <v>4.17</v>
       </c>
       <c r="P39">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="Q39">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R39">
         <v>2.38</v>
@@ -6684,16 +6684,16 @@
         <v>1.2</v>
       </c>
       <c r="T39">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="U39">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="V39">
         <v>1.61</v>
       </c>
       <c r="W39">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X39">
         <v>1.03</v>
@@ -6705,13 +6705,13 @@
         <v>5.3</v>
       </c>
       <c r="AA39">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AB39">
         <v>2.4</v>
       </c>
       <c r="AC39">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AD39">
         <v>1.57</v>
@@ -6720,7 +6720,7 @@
         <v>1.23</v>
       </c>
       <c r="AF39">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG39">
         <v>2.6</v>
@@ -6838,19 +6838,19 @@
         <v>8.6</v>
       </c>
       <c r="Q40">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="R40">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="S40">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="T40">
-        <v>2.67</v>
+        <v>2.96</v>
       </c>
       <c r="U40">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="V40">
         <v>1.38</v>
@@ -6862,31 +6862,31 @@
         <v>1.05</v>
       </c>
       <c r="Y40">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z40">
         <v>3.4</v>
       </c>
       <c r="AA40">
-        <v>1.91</v>
+        <v>1.74</v>
       </c>
       <c r="AB40">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="AC40">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="AD40">
         <v>1.29</v>
       </c>
       <c r="AE40">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF40">
         <v>2.1</v>
       </c>
       <c r="AG40">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="AK40">
-        <v>3.1</v>
+        <v>2.68</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7001,7 +7001,7 @@
         <v>3.4</v>
       </c>
       <c r="Q41">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="R41">
         <v>1.91</v>
@@ -7031,10 +7031,10 @@
         <v>2.63</v>
       </c>
       <c r="AA41">
-        <v>2.43</v>
+        <v>2.69</v>
       </c>
       <c r="AB41">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AC41">
         <v>5.25</v>
@@ -7164,55 +7164,55 @@
         <v>4.37</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="O43">
         <v>3.7</v>
       </c>
       <c r="P43">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="Q43">
         <v>3.5</v>
@@ -7369,13 +7369,13 @@
         <v>1.62</v>
       </c>
       <c r="AE43">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AF43">
         <v>1.44</v>
       </c>
       <c r="AG43">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.22</v>
+        <v>1.75</v>
       </c>
       <c r="AK43">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7490,7 +7490,7 @@
         <v>4.14</v>
       </c>
       <c r="Q44">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="R44">
         <v>2.4</v>
@@ -7517,16 +7517,16 @@
         <v>1.2</v>
       </c>
       <c r="Z44">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AA44">
         <v>1.68</v>
       </c>
       <c r="AB44">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="AC44">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="AD44">
         <v>1.48</v>
@@ -7538,7 +7538,7 @@
         <v>1.61</v>
       </c>
       <c r="AG44">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK44">
         <v>2</v>
@@ -7695,7 +7695,7 @@
         <v>1.16</v>
       </c>
       <c r="AE45">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF45">
         <v>2.08</v>
@@ -7813,25 +7813,25 @@
         <v>3.9</v>
       </c>
       <c r="P46">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="Q46">
         <v>2.1</v>
       </c>
       <c r="R46">
-        <v>2.34</v>
+        <v>2.45</v>
       </c>
       <c r="S46">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T46">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U46">
         <v>2.25</v>
       </c>
       <c r="V46">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="W46">
         <v>1.11</v>
@@ -7840,7 +7840,7 @@
         <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z46">
         <v>4.5</v>
@@ -7849,10 +7849,10 @@
         <v>1.61</v>
       </c>
       <c r="AB46">
+        <v>2.3</v>
+      </c>
+      <c r="AC46">
         <v>2.25</v>
-      </c>
-      <c r="AC46">
-        <v>2.39</v>
       </c>
       <c r="AD46">
         <v>1.5</v>
@@ -7861,10 +7861,10 @@
         <v>1.18</v>
       </c>
       <c r="AF46">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AG46">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7970,10 +7970,10 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="O47">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P47">
         <v>2.3</v>
@@ -7991,7 +7991,7 @@
         <v>3.4</v>
       </c>
       <c r="U47">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="V47">
         <v>1.51</v>
@@ -8012,16 +8012,16 @@
         <v>1.66</v>
       </c>
       <c r="AB47">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC47">
-        <v>2.55</v>
+        <v>2.64</v>
       </c>
       <c r="AD47">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AE47">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AF47">
         <v>1.5</v>
@@ -8136,31 +8136,31 @@
         <v>1.85</v>
       </c>
       <c r="O48">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="P48">
-        <v>3.58</v>
+        <v>3.69</v>
       </c>
       <c r="Q48">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="R48">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="S48">
         <v>1.2</v>
       </c>
       <c r="T48">
-        <v>3.8</v>
+        <v>3.34</v>
       </c>
       <c r="U48">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="V48">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="W48">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X48">
         <v>1.01</v>
@@ -8172,10 +8172,10 @@
         <v>6.1</v>
       </c>
       <c r="AA48">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AB48">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AC48">
         <v>2.25</v>
@@ -8187,7 +8187,7 @@
         <v>1.25</v>
       </c>
       <c r="AF48">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AG48">
         <v>2.5</v>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK48">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8302,7 +8302,7 @@
         <v>3.35</v>
       </c>
       <c r="P49">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="Q49">
         <v>2.93</v>
@@ -8338,7 +8338,7 @@
         <v>1.75</v>
       </c>
       <c r="AB49">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="AC49">
         <v>2.43</v>
@@ -8350,10 +8350,10 @@
         <v>1.11</v>
       </c>
       <c r="AF49">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AG49">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8459,31 +8459,31 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="O50">
-        <v>3.9</v>
+        <v>4.42</v>
       </c>
       <c r="P50">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="Q50">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="R50">
-        <v>2.51</v>
+        <v>2.6</v>
       </c>
       <c r="S50">
         <v>1.16</v>
       </c>
       <c r="T50">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="U50">
         <v>1.95</v>
       </c>
       <c r="V50">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="W50">
         <v>1.19</v>
@@ -8501,22 +8501,22 @@
         <v>1.31</v>
       </c>
       <c r="AB50">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AC50">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AD50">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AE50">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AF50">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AG50">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8622,34 +8622,34 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="O51">
-        <v>5.1</v>
+        <v>4.82</v>
       </c>
       <c r="P51">
         <v>5</v>
       </c>
       <c r="Q51">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="R51">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="S51">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T51">
-        <v>3.66</v>
+        <v>3.9</v>
       </c>
       <c r="U51">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="V51">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="W51">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X51">
         <v>1.01</v>
@@ -8658,13 +8658,13 @@
         <v>1.13</v>
       </c>
       <c r="Z51">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AA51">
         <v>1.5</v>
       </c>
       <c r="AB51">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AC51">
         <v>2.2</v>
@@ -8676,7 +8676,7 @@
         <v>1.28</v>
       </c>
       <c r="AF51">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG51">
         <v>2.18</v>
@@ -8695,7 +8695,7 @@
         <v>1.18</v>
       </c>
       <c r="AK51">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8788,10 +8788,10 @@
         <v>2.2</v>
       </c>
       <c r="O52">
-        <v>3.7</v>
+        <v>4.24</v>
       </c>
       <c r="P52">
-        <v>2.5</v>
+        <v>2.72</v>
       </c>
       <c r="Q52">
         <v>2.67</v>
@@ -8836,7 +8836,7 @@
         <v>1.7</v>
       </c>
       <c r="AE52">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF52">
         <v>1.4</v>
@@ -8858,7 +8858,7 @@
         <v>1.38</v>
       </c>
       <c r="AK52">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AL52">
         <v>0</v>

--- a/jogos_2026-08-19.xlsx
+++ b/jogos_2026-08-19.xlsx
@@ -1160,10 +1160,10 @@
         <v>1.36</v>
       </c>
       <c r="Z5">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AA5">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AB5">
         <v>1.68</v>
@@ -1181,7 +1181,7 @@
         <v>1.97</v>
       </c>
       <c r="AG5">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1782,10 +1782,10 @@
         <v>3.5</v>
       </c>
       <c r="P9">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="Q9">
-        <v>5.2</v>
+        <v>5.28</v>
       </c>
       <c r="R9">
         <v>2.05</v>
@@ -1815,7 +1815,7 @@
         <v>2.97</v>
       </c>
       <c r="AA9">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AB9">
         <v>1.72</v>
@@ -1830,10 +1830,10 @@
         <v>1.03</v>
       </c>
       <c r="AF9">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AG9">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>2.05</v>
       </c>
       <c r="AK9">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AL9">
         <v>0</v>

--- a/jogos_2026-08-19.xlsx
+++ b/jogos_2026-08-19.xlsx
@@ -4882,13 +4882,13 @@
         <v>2.25</v>
       </c>
       <c r="Q28">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="R28">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="S28">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="T28">
         <v>3.28</v>
@@ -4897,7 +4897,7 @@
         <v>2.45</v>
       </c>
       <c r="V28">
-        <v>1.46</v>
+        <v>1.51</v>
       </c>
       <c r="W28">
         <v>1.11</v>
@@ -4906,13 +4906,13 @@
         <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z28">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AA28">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AB28">
         <v>2.12</v>
@@ -4924,7 +4924,7 @@
         <v>1.4</v>
       </c>
       <c r="AE28">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF28">
         <v>1.53</v>
@@ -4946,7 +4946,7 @@
         <v>1.25</v>
       </c>
       <c r="AK28">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,80 +6829,80 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.36</v>
+        <v>2.15</v>
       </c>
       <c r="O40">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="P40">
-        <v>8.6</v>
+        <v>3.4</v>
       </c>
       <c r="Q40">
-        <v>1.88</v>
+        <v>2.9</v>
       </c>
       <c r="R40">
-        <v>2.44</v>
+        <v>1.91</v>
       </c>
       <c r="S40">
-        <v>1.37</v>
+        <v>1.61</v>
       </c>
       <c r="T40">
-        <v>2.96</v>
+        <v>2.3</v>
       </c>
       <c r="U40">
-        <v>2.88</v>
+        <v>3.55</v>
       </c>
       <c r="V40">
+        <v>1.21</v>
+      </c>
+      <c r="W40">
+        <v>1.04</v>
+      </c>
+      <c r="X40">
+        <v>1.12</v>
+      </c>
+      <c r="Y40">
+        <v>1.46</v>
+      </c>
+      <c r="Z40">
+        <v>2.63</v>
+      </c>
+      <c r="AA40">
+        <v>2.69</v>
+      </c>
+      <c r="AB40">
+        <v>1.44</v>
+      </c>
+      <c r="AC40">
+        <v>5.25</v>
+      </c>
+      <c r="AD40">
+        <v>1.09</v>
+      </c>
+      <c r="AE40">
+        <v>1.03</v>
+      </c>
+      <c r="AF40">
+        <v>2.04</v>
+      </c>
+      <c r="AG40">
+        <v>1.68</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ40">
         <v>1.38</v>
       </c>
-      <c r="W40">
-        <v>1.06</v>
-      </c>
-      <c r="X40">
-        <v>1.05</v>
-      </c>
-      <c r="Y40">
-        <v>1.24</v>
-      </c>
-      <c r="Z40">
-        <v>3.4</v>
-      </c>
-      <c r="AA40">
-        <v>1.74</v>
-      </c>
-      <c r="AB40">
-        <v>2.02</v>
-      </c>
-      <c r="AC40">
-        <v>3.14</v>
-      </c>
-      <c r="AD40">
-        <v>1.29</v>
-      </c>
-      <c r="AE40">
-        <v>1.06</v>
-      </c>
-      <c r="AF40">
-        <v>2.1</v>
-      </c>
-      <c r="AG40">
+      <c r="AK40">
         <v>1.59</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ40">
-        <v>1.05</v>
-      </c>
-      <c r="AK40">
-        <v>2.68</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>2.15</v>
+        <v>1.36</v>
       </c>
       <c r="O41">
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="P41">
+        <v>8.6</v>
+      </c>
+      <c r="Q41">
+        <v>1.88</v>
+      </c>
+      <c r="R41">
+        <v>2.44</v>
+      </c>
+      <c r="S41">
+        <v>1.37</v>
+      </c>
+      <c r="T41">
+        <v>2.96</v>
+      </c>
+      <c r="U41">
+        <v>2.88</v>
+      </c>
+      <c r="V41">
+        <v>1.38</v>
+      </c>
+      <c r="W41">
+        <v>1.06</v>
+      </c>
+      <c r="X41">
+        <v>1.05</v>
+      </c>
+      <c r="Y41">
+        <v>1.24</v>
+      </c>
+      <c r="Z41">
         <v>3.4</v>
       </c>
-      <c r="Q41">
-        <v>2.9</v>
-      </c>
-      <c r="R41">
-        <v>1.91</v>
-      </c>
-      <c r="S41">
-        <v>1.61</v>
-      </c>
-      <c r="T41">
-        <v>2.3</v>
-      </c>
-      <c r="U41">
-        <v>3.55</v>
-      </c>
-      <c r="V41">
-        <v>1.21</v>
-      </c>
-      <c r="W41">
-        <v>1.04</v>
-      </c>
-      <c r="X41">
-        <v>1.12</v>
-      </c>
-      <c r="Y41">
-        <v>1.46</v>
-      </c>
-      <c r="Z41">
-        <v>2.63</v>
-      </c>
       <c r="AA41">
-        <v>2.69</v>
+        <v>1.74</v>
       </c>
       <c r="AB41">
-        <v>1.44</v>
+        <v>2.02</v>
       </c>
       <c r="AC41">
-        <v>5.25</v>
+        <v>3.14</v>
       </c>
       <c r="AD41">
-        <v>1.09</v>
+        <v>1.29</v>
       </c>
       <c r="AE41">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF41">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AG41">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.38</v>
+        <v>1.05</v>
       </c>
       <c r="AK41">
-        <v>1.59</v>
+        <v>2.68</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7164,7 +7164,7 @@
         <v>4.37</v>
       </c>
       <c r="Q42">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="R42">
         <v>2.25</v>
@@ -7173,34 +7173,34 @@
         <v>1.31</v>
       </c>
       <c r="T42">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="U42">
-        <v>2.12</v>
+        <v>2.47</v>
       </c>
       <c r="V42">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="W42">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X42">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z42">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="AA42">
         <v>1.75</v>
       </c>
       <c r="AB42">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AC42">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="AD42">
         <v>1.33</v>
@@ -7228,7 +7228,7 @@
         <v>1.18</v>
       </c>
       <c r="AK42">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AL42">
         <v>0</v>

--- a/jogos_2026-08-19.xlsx
+++ b/jogos_2026-08-19.xlsx
@@ -1133,10 +1133,10 @@
         <v>4.55</v>
       </c>
       <c r="Q5">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="R5">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="S5">
         <v>1.43</v>
@@ -1172,7 +1172,7 @@
         <v>3.68</v>
       </c>
       <c r="AD5">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AE5">
         <v>1.04</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK5">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1776,19 +1776,19 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.85</v>
+        <v>4.7</v>
       </c>
       <c r="O9">
         <v>3.5</v>
       </c>
       <c r="P9">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Q9">
-        <v>5.28</v>
+        <v>4.47</v>
       </c>
       <c r="R9">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="S9">
         <v>1.41</v>
@@ -1800,7 +1800,7 @@
         <v>2.99</v>
       </c>
       <c r="V9">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W9">
         <v>1.02</v>
@@ -1809,19 +1809,19 @@
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Z9">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="AA9">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AB9">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC9">
-        <v>3.7</v>
+        <v>3.69</v>
       </c>
       <c r="AD9">
         <v>1.25</v>
@@ -1830,10 +1830,10 @@
         <v>1.03</v>
       </c>
       <c r="AF9">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AG9">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AK9">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="O11">
-        <v>3.9</v>
+        <v>4.15</v>
       </c>
       <c r="P11">
-        <v>9.4</v>
+        <v>10.2</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -3080,25 +3080,25 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="O17">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="P17">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="Q17">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="R17">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="S17">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T17">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="U17">
         <v>2.3</v>
@@ -3107,7 +3107,7 @@
         <v>1.55</v>
       </c>
       <c r="W17">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X17">
         <v>1.03</v>
@@ -3119,25 +3119,25 @@
         <v>4.5</v>
       </c>
       <c r="AA17">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AB17">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AC17">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AD17">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AE17">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AF17">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AG17">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AK17">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -4547,25 +4547,25 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="O26">
-        <v>5.65</v>
+        <v>5.25</v>
       </c>
       <c r="P26">
         <v>10</v>
       </c>
       <c r="Q26">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="R26">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="S26">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T26">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="U26">
         <v>2.44</v>
@@ -4574,37 +4574,37 @@
         <v>1.47</v>
       </c>
       <c r="W26">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X26">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y26">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z26">
-        <v>4.33</v>
+        <v>3.55</v>
       </c>
       <c r="AA26">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AB26">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AC26">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="AD26">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE26">
         <v>1.1</v>
       </c>
       <c r="AF26">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AG26">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -5045,52 +5045,52 @@
         <v>2.35</v>
       </c>
       <c r="Q29">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R29">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="S29">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="T29">
-        <v>2.47</v>
+        <v>2.65</v>
       </c>
       <c r="U29">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="V29">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="W29">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X29">
         <v>1.03</v>
       </c>
       <c r="Y29">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z29">
         <v>2.83</v>
       </c>
       <c r="AA29">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AB29">
         <v>1.65</v>
       </c>
       <c r="AC29">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="AD29">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE29">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF29">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AG29">
         <v>1.86</v>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AK29">
         <v>1.4</v>
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="O30">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P30">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="Q30">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="R30">
-        <v>2.19</v>
+        <v>2.1</v>
       </c>
       <c r="S30">
         <v>1.44</v>
       </c>
       <c r="T30">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="U30">
-        <v>3.21</v>
+        <v>3.18</v>
       </c>
       <c r="V30">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W30">
         <v>1.04</v>
       </c>
       <c r="X30">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y30">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z30">
-        <v>2.99</v>
+        <v>3.3</v>
       </c>
       <c r="AA30">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="AB30">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC30">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="AD30">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE30">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF30">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG30">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK30">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O40">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="P40">
         <v>3.4</v>
       </c>
       <c r="Q40">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="R40">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="S40">
         <v>1.61</v>
       </c>
       <c r="T40">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="U40">
-        <v>3.55</v>
+        <v>3.68</v>
       </c>
       <c r="V40">
         <v>1.21</v>
       </c>
       <c r="W40">
+        <v>1.02</v>
+      </c>
+      <c r="X40">
+        <v>1.07</v>
+      </c>
+      <c r="Y40">
+        <v>1.49</v>
+      </c>
+      <c r="Z40">
+        <v>2.3</v>
+      </c>
+      <c r="AA40">
+        <v>2.63</v>
+      </c>
+      <c r="AB40">
+        <v>1.4</v>
+      </c>
+      <c r="AC40">
+        <v>5.5</v>
+      </c>
+      <c r="AD40">
+        <v>1.13</v>
+      </c>
+      <c r="AE40">
         <v>1.04</v>
       </c>
-      <c r="X40">
-        <v>1.12</v>
-      </c>
-      <c r="Y40">
-        <v>1.46</v>
-      </c>
-      <c r="Z40">
-        <v>2.63</v>
-      </c>
-      <c r="AA40">
-        <v>2.69</v>
-      </c>
-      <c r="AB40">
-        <v>1.44</v>
-      </c>
-      <c r="AC40">
-        <v>5.25</v>
-      </c>
-      <c r="AD40">
-        <v>1.09</v>
-      </c>
-      <c r="AE40">
-        <v>1.03</v>
-      </c>
       <c r="AF40">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="AG40">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>1.38</v>
       </c>
       <c r="AK40">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7001,34 +7001,34 @@
         <v>8.6</v>
       </c>
       <c r="Q41">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="R41">
-        <v>2.44</v>
+        <v>2.23</v>
       </c>
       <c r="S41">
         <v>1.37</v>
       </c>
       <c r="T41">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="U41">
-        <v>2.88</v>
+        <v>2.55</v>
       </c>
       <c r="V41">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="W41">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X41">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y41">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Z41">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AA41">
         <v>1.74</v>
@@ -7040,7 +7040,7 @@
         <v>3.14</v>
       </c>
       <c r="AD41">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AE41">
         <v>1.06</v>
@@ -7049,7 +7049,7 @@
         <v>2.1</v>
       </c>
       <c r="AG41">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         <v>1.05</v>
       </c>
       <c r="AK41">
-        <v>2.68</v>
+        <v>2.9</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7653,52 +7653,52 @@
         <v>2.66</v>
       </c>
       <c r="Q45">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R45">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="S45">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="T45">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="U45">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="V45">
         <v>1.22</v>
       </c>
       <c r="W45">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X45">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Y45">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="Z45">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="AA45">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AB45">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AC45">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AD45">
         <v>1.16</v>
       </c>
       <c r="AE45">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF45">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AG45">
         <v>1.67</v>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AK45">
         <v>1.4</v>
@@ -8296,31 +8296,31 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="O49">
         <v>3.35</v>
       </c>
       <c r="P49">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="Q49">
-        <v>2.93</v>
+        <v>3.05</v>
       </c>
       <c r="R49">
         <v>2.15</v>
       </c>
       <c r="S49">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T49">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="U49">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="V49">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W49">
         <v>1.11</v>
@@ -8338,10 +8338,10 @@
         <v>1.75</v>
       </c>
       <c r="AB49">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AC49">
-        <v>2.43</v>
+        <v>2.66</v>
       </c>
       <c r="AD49">
         <v>1.4</v>
@@ -8353,7 +8353,7 @@
         <v>1.57</v>
       </c>
       <c r="AG49">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AK49">
         <v>1.46</v>

--- a/jogos_2026-08-19.xlsx
+++ b/jogos_2026-08-19.xlsx
@@ -635,80 +635,80 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="O2">
-        <v>3.76</v>
+        <v>3.65</v>
       </c>
       <c r="P2">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="Q2">
-        <v>2.5</v>
+        <v>1.87</v>
       </c>
       <c r="R2">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="S2">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T2">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U2">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="V2">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="W2">
         <v>1.13</v>
       </c>
       <c r="X2">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="Z2">
-        <v>6.98</v>
+        <v>5.65</v>
       </c>
       <c r="AA2">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AB2">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="AC2">
-        <v>2.38</v>
+        <v>2.13</v>
       </c>
       <c r="AD2">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AE2">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AF2">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="AG2">
+        <v>2.25</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ2">
+        <v>1.15</v>
+      </c>
+      <c r="AK2">
         <v>2.4</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ2">
-        <v>1.25</v>
-      </c>
-      <c r="AK2">
-        <v>1.8</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -3412,28 +3412,28 @@
         <v>2.65</v>
       </c>
       <c r="P19">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="Q19">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="R19">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="S19">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="T19">
         <v>2.3</v>
       </c>
       <c r="U19">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="V19">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="W19">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X19">
         <v>1.1</v>
@@ -3445,19 +3445,19 @@
         <v>2.53</v>
       </c>
       <c r="AA19">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="AB19">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AC19">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AD19">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AE19">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF19">
         <v>2.23</v>
@@ -3895,46 +3895,46 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="O22">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P22">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="Q22">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="R22">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S22">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T22">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="U22">
         <v>2.49</v>
       </c>
       <c r="V22">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W22">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X22">
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z22">
         <v>3.9</v>
       </c>
       <c r="AA22">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AB22">
         <v>2</v>
@@ -3946,13 +3946,13 @@
         <v>1.4</v>
       </c>
       <c r="AE22">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF22">
         <v>1.78</v>
       </c>
       <c r="AG22">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AK22">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,25 +4058,25 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="O23">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P23">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="Q23">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="R23">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="S23">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T23">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="U23">
         <v>2.56</v>
@@ -4091,16 +4091,16 @@
         <v>1.04</v>
       </c>
       <c r="Y23">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z23">
-        <v>3.84</v>
+        <v>3.7</v>
       </c>
       <c r="AA23">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AB23">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AC23">
         <v>2.9</v>
@@ -4109,13 +4109,13 @@
         <v>1.36</v>
       </c>
       <c r="AE23">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF23">
         <v>1.73</v>
       </c>
       <c r="AG23">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK23">
         <v>2</v>
@@ -4230,49 +4230,49 @@
         <v>2.5</v>
       </c>
       <c r="Q24">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="R24">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="S24">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T24">
-        <v>4</v>
+        <v>3.66</v>
       </c>
       <c r="U24">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="V24">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="W24">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X24">
         <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z24">
         <v>5.75</v>
       </c>
       <c r="AA24">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AB24">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AC24">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AD24">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AE24">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AF24">
         <v>1.4</v>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="AK24">
         <v>1.5</v>
@@ -4384,43 +4384,43 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.17</v>
+        <v>2.4</v>
       </c>
       <c r="O25">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="P25">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="Q25">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="R25">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="S25">
+        <v>1.36</v>
+      </c>
+      <c r="T25">
+        <v>2.88</v>
+      </c>
+      <c r="U25">
+        <v>2.7</v>
+      </c>
+      <c r="V25">
         <v>1.42</v>
       </c>
-      <c r="T25">
-        <v>2.66</v>
-      </c>
-      <c r="U25">
-        <v>2.85</v>
-      </c>
-      <c r="V25">
-        <v>1.37</v>
-      </c>
       <c r="W25">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X25">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y25">
         <v>1.33</v>
       </c>
       <c r="Z25">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="AA25">
         <v>1.93</v>
@@ -4429,19 +4429,19 @@
         <v>1.87</v>
       </c>
       <c r="AC25">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AD25">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE25">
         <v>1.06</v>
       </c>
       <c r="AF25">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG25">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="AK25">
         <v>1.53</v>
@@ -4882,13 +4882,13 @@
         <v>2.25</v>
       </c>
       <c r="Q28">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="R28">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="S28">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="T28">
         <v>3.28</v>
@@ -4909,13 +4909,13 @@
         <v>1.15</v>
       </c>
       <c r="Z28">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AA28">
         <v>1.64</v>
       </c>
       <c r="AB28">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="AC28">
         <v>2.56</v>
@@ -4927,7 +4927,7 @@
         <v>1.17</v>
       </c>
       <c r="AF28">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AG28">
         <v>2.3</v>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK28">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="O31">
-        <v>3.92</v>
+        <v>3.96</v>
       </c>
       <c r="P31">
-        <v>5.55</v>
+        <v>6.09</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5401,10 +5401,10 @@
         <v>0</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC31">
         <v>0</v>
@@ -5528,10 +5528,10 @@
         <v>2.64</v>
       </c>
       <c r="O32">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="P32">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5564,10 +5564,10 @@
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC32">
         <v>0</v>
@@ -5688,28 +5688,28 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="O33">
-        <v>4.6</v>
+        <v>4.05</v>
       </c>
       <c r="P33">
-        <v>4.9</v>
+        <v>4.65</v>
       </c>
       <c r="Q33">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="R33">
         <v>2.45</v>
       </c>
       <c r="S33">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T33">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="U33">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="V33">
         <v>1.6</v>
@@ -5718,19 +5718,19 @@
         <v>1.15</v>
       </c>
       <c r="X33">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="Z33">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AA33">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AB33">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="AC33">
         <v>2.3</v>
@@ -5742,10 +5742,10 @@
         <v>1.22</v>
       </c>
       <c r="AF33">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AG33">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AK33">
         <v>2.25</v>
@@ -5851,22 +5851,22 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="O34">
-        <v>3.94</v>
+        <v>3.55</v>
       </c>
       <c r="P34">
         <v>2.8</v>
       </c>
       <c r="Q34">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="R34">
         <v>2.3</v>
       </c>
       <c r="S34">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T34">
         <v>3.4</v>
@@ -5875,7 +5875,7 @@
         <v>2.48</v>
       </c>
       <c r="V34">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="W34">
         <v>1.12</v>
@@ -5887,28 +5887,28 @@
         <v>1.16</v>
       </c>
       <c r="Z34">
-        <v>4.15</v>
+        <v>4.8</v>
       </c>
       <c r="AA34">
         <v>1.66</v>
       </c>
       <c r="AB34">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AC34">
         <v>2.63</v>
       </c>
       <c r="AD34">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="AE34">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AF34">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AG34">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AK34">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6017,10 +6017,10 @@
         <v>2.16</v>
       </c>
       <c r="O35">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="P35">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6053,10 +6053,10 @@
         <v>0</v>
       </c>
       <c r="AA35">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB35">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC35">
         <v>0</v>
@@ -6177,40 +6177,40 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="O36">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P36">
+        <v>2.6</v>
+      </c>
+      <c r="Q36">
         <v>2.5</v>
       </c>
-      <c r="Q36">
-        <v>2.7</v>
-      </c>
       <c r="R36">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S36">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="T36">
-        <v>3.66</v>
+        <v>4</v>
       </c>
       <c r="U36">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="V36">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="W36">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X36">
         <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z36">
         <v>5.75</v>
@@ -6219,19 +6219,19 @@
         <v>1.44</v>
       </c>
       <c r="AB36">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AC36">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AD36">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AE36">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AF36">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AG36">
         <v>2.76</v>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK36">
         <v>1.55</v>
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="O37">
-        <v>4.47</v>
+        <v>3.6</v>
       </c>
       <c r="P37">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="Q37">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="R37">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="S37">
+        <v>1.14</v>
+      </c>
+      <c r="T37">
+        <v>4.33</v>
+      </c>
+      <c r="U37">
+        <v>1.96</v>
+      </c>
+      <c r="V37">
+        <v>1.75</v>
+      </c>
+      <c r="W37">
         <v>1.2</v>
-      </c>
-      <c r="T37">
-        <v>4.8</v>
-      </c>
-      <c r="U37">
-        <v>1.91</v>
-      </c>
-      <c r="V37">
-        <v>1.77</v>
-      </c>
-      <c r="W37">
-        <v>1.22</v>
       </c>
       <c r="X37">
         <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z37">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="AA37">
         <v>1.33</v>
       </c>
       <c r="AB37">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="AC37">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AD37">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AE37">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AF37">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AG37">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK37">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,19 +6503,19 @@
         </is>
       </c>
       <c r="N38">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="O38">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P38">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="Q38">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="R38">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S38">
         <v>1.22</v>
@@ -6524,28 +6524,28 @@
         <v>4.1</v>
       </c>
       <c r="U38">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="V38">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="W38">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="X38">
         <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z38">
         <v>5.7</v>
       </c>
       <c r="AA38">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AB38">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AC38">
         <v>2.1</v>
@@ -6554,13 +6554,13 @@
         <v>1.71</v>
       </c>
       <c r="AE38">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AF38">
         <v>1.4</v>
       </c>
       <c r="AG38">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK38">
         <v>1.8</v>
@@ -6666,31 +6666,31 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="O39">
-        <v>4.17</v>
+        <v>4.08</v>
       </c>
       <c r="P39">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="Q39">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R39">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="S39">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T39">
         <v>3.75</v>
       </c>
       <c r="U39">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="V39">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W39">
         <v>1.14</v>
@@ -6699,31 +6699,31 @@
         <v>1.03</v>
       </c>
       <c r="Y39">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z39">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AA39">
         <v>1.52</v>
       </c>
       <c r="AB39">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="AC39">
         <v>2.25</v>
       </c>
       <c r="AD39">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AE39">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AF39">
         <v>1.44</v>
       </c>
       <c r="AG39">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.6</v>
+        <v>1.26</v>
       </c>
       <c r="AK39">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,16 +6829,16 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="O40">
-        <v>2.87</v>
+        <v>2.85</v>
       </c>
       <c r="P40">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="Q40">
-        <v>3.08</v>
+        <v>3.01</v>
       </c>
       <c r="R40">
         <v>1.79</v>
@@ -6871,7 +6871,7 @@
         <v>2.63</v>
       </c>
       <c r="AB40">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AC40">
         <v>5.5</v>
@@ -7022,7 +7022,7 @@
         <v>1.08</v>
       </c>
       <c r="X41">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
         <v>1.3</v>
@@ -7043,7 +7043,7 @@
         <v>1.27</v>
       </c>
       <c r="AE41">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF41">
         <v>2.1</v>
@@ -7167,13 +7167,13 @@
         <v>2.22</v>
       </c>
       <c r="R42">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="S42">
         <v>1.31</v>
       </c>
       <c r="T42">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="U42">
         <v>2.47</v>
@@ -7194,10 +7194,10 @@
         <v>3.58</v>
       </c>
       <c r="AA42">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AB42">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AC42">
         <v>2.74</v>
@@ -7206,13 +7206,13 @@
         <v>1.33</v>
       </c>
       <c r="AE42">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF42">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AG42">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK42">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>3.1</v>
+        <v>3.41</v>
       </c>
       <c r="O43">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="P43">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="Q43">
         <v>3.5</v>
@@ -7342,40 +7342,40 @@
         <v>2.15</v>
       </c>
       <c r="V43">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="W43">
         <v>1.18</v>
       </c>
       <c r="X43">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z43">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AA43">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AB43">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AC43">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AD43">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AE43">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF43">
         <v>1.44</v>
       </c>
       <c r="AG43">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AK43">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,19 +7481,19 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="O44">
         <v>3.6</v>
       </c>
       <c r="P44">
-        <v>4.14</v>
+        <v>3.8</v>
       </c>
       <c r="Q44">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="R44">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S44">
         <v>1.3</v>
@@ -7505,40 +7505,40 @@
         <v>2.41</v>
       </c>
       <c r="V44">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W44">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X44">
         <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z44">
-        <v>4.33</v>
+        <v>4.31</v>
       </c>
       <c r="AA44">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AB44">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AC44">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="AD44">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AE44">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF44">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AG44">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK44">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7677,7 +7677,7 @@
         <v>1.11</v>
       </c>
       <c r="Y45">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Z45">
         <v>2.31</v>
@@ -7695,7 +7695,7 @@
         <v>1.16</v>
       </c>
       <c r="AE45">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF45">
         <v>2.05</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.6</v>
+        <v>2.64</v>
       </c>
       <c r="O46">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="P46">
-        <v>4.4</v>
+        <v>2.39</v>
       </c>
       <c r="Q46">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="R46">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="S46">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="T46">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="U46">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="V46">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="W46">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X46">
         <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z46">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA46">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB46">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AC46">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="AD46">
+        <v>1.44</v>
+      </c>
+      <c r="AE46">
+        <v>1.19</v>
+      </c>
+      <c r="AF46">
         <v>1.5</v>
       </c>
-      <c r="AE46">
-        <v>1.18</v>
-      </c>
-      <c r="AF46">
-        <v>1.53</v>
-      </c>
       <c r="AG46">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.18</v>
+        <v>1.5</v>
       </c>
       <c r="AK46">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.6</v>
+        <v>1.92</v>
       </c>
       <c r="O47">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P47">
-        <v>2.3</v>
+        <v>3.68</v>
       </c>
       <c r="Q47">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="R47">
-        <v>2.35</v>
+        <v>2.57</v>
       </c>
       <c r="S47">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T47">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U47">
-        <v>2.39</v>
+        <v>2.1</v>
       </c>
       <c r="V47">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="W47">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X47">
         <v>1.03</v>
       </c>
       <c r="Y47">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z47">
-        <v>4.2</v>
+        <v>5.31</v>
       </c>
       <c r="AA47">
-        <v>1.66</v>
+        <v>1.46</v>
       </c>
       <c r="AB47">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="AC47">
-        <v>2.64</v>
+        <v>2.25</v>
       </c>
       <c r="AD47">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="AE47">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF47">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AG47">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.53</v>
+        <v>1.2</v>
       </c>
       <c r="AK47">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="O48">
-        <v>3.8</v>
+        <v>4.62</v>
       </c>
       <c r="P48">
-        <v>3.69</v>
+        <v>4.88</v>
       </c>
       <c r="Q48">
+        <v>2.1</v>
+      </c>
+      <c r="R48">
+        <v>2.5</v>
+      </c>
+      <c r="S48">
+        <v>1.22</v>
+      </c>
+      <c r="T48">
+        <v>3.5</v>
+      </c>
+      <c r="U48">
         <v>2.15</v>
       </c>
-      <c r="R48">
-        <v>2.57</v>
-      </c>
-      <c r="S48">
-        <v>1.2</v>
-      </c>
-      <c r="T48">
-        <v>3.34</v>
-      </c>
-      <c r="U48">
-        <v>2.21</v>
-      </c>
       <c r="V48">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="W48">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X48">
         <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="Z48">
-        <v>6.1</v>
+        <v>5</v>
       </c>
       <c r="AA48">
+        <v>1.52</v>
+      </c>
+      <c r="AB48">
+        <v>2.55</v>
+      </c>
+      <c r="AC48">
+        <v>2.29</v>
+      </c>
+      <c r="AD48">
         <v>1.5</v>
       </c>
-      <c r="AB48">
-        <v>2.45</v>
-      </c>
-      <c r="AC48">
-        <v>2.25</v>
-      </c>
-      <c r="AD48">
-        <v>1.6</v>
-      </c>
       <c r="AE48">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF48">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AG48">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK48">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,34 +8296,34 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="O49">
         <v>3.35</v>
       </c>
       <c r="P49">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q49">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="R49">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="S49">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T49">
-        <v>3.2</v>
+        <v>3.26</v>
       </c>
       <c r="U49">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="V49">
         <v>1.47</v>
       </c>
       <c r="W49">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X49">
         <v>1.01</v>
@@ -8335,13 +8335,13 @@
         <v>3.74</v>
       </c>
       <c r="AA49">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AB49">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AC49">
-        <v>2.66</v>
+        <v>2.82</v>
       </c>
       <c r="AD49">
         <v>1.4</v>
@@ -8350,10 +8350,10 @@
         <v>1.11</v>
       </c>
       <c r="AF49">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG49">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AK49">
         <v>1.46</v>
@@ -8462,55 +8462,55 @@
         <v>2.04</v>
       </c>
       <c r="O50">
-        <v>4.42</v>
+        <v>4.4</v>
       </c>
       <c r="P50">
-        <v>2.8</v>
+        <v>2.97</v>
       </c>
       <c r="Q50">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="R50">
-        <v>2.6</v>
+        <v>2.49</v>
       </c>
       <c r="S50">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="T50">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="U50">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V50">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="W50">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X50">
         <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Z50">
-        <v>6.5</v>
+        <v>6.56</v>
       </c>
       <c r="AA50">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AB50">
-        <v>2.9</v>
+        <v>3.01</v>
       </c>
       <c r="AC50">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="AD50">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AE50">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AF50">
         <v>1.36</v>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK50">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,31 +8622,31 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="O51">
-        <v>4.82</v>
+        <v>4.72</v>
       </c>
       <c r="P51">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="Q51">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="R51">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="S51">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T51">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="U51">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="V51">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="W51">
         <v>1.15</v>
@@ -8655,31 +8655,31 @@
         <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z51">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AA51">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB51">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AC51">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="AD51">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AE51">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AF51">
         <v>1.57</v>
       </c>
       <c r="AG51">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>1.18</v>
       </c>
       <c r="AK51">
-        <v>2.66</v>
+        <v>2.43</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O52">
         <v>4.24</v>
       </c>
       <c r="P52">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="Q52">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="R52">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="S52">
         <v>1.22</v>
       </c>
       <c r="T52">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="U52">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="V52">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="W52">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X52">
         <v>1.02</v>
       </c>
       <c r="Y52">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="Z52">
-        <v>5.5</v>
+        <v>6.25</v>
       </c>
       <c r="AA52">
         <v>1.4</v>
       </c>
       <c r="AB52">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="AC52">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AD52">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AE52">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AF52">
         <v>1.4</v>
       </c>
       <c r="AG52">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AK52">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AL52">
         <v>0</v>

--- a/jogos_2026-08-19.xlsx
+++ b/jogos_2026-08-19.xlsx
@@ -1948,40 +1948,40 @@
         <v>3.73</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W10">
         <v>0</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC10">
         <v>0</v>
@@ -1993,10 +1993,10 @@
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="O11">
-        <v>4.15</v>
+        <v>4.33</v>
       </c>
       <c r="P11">
-        <v>10.2</v>
+        <v>8</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -4882,7 +4882,7 @@
         <v>2.25</v>
       </c>
       <c r="Q28">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="R28">
         <v>2.28</v>
@@ -4906,7 +4906,7 @@
         <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z28">
         <v>3.8</v>
@@ -4921,13 +4921,13 @@
         <v>2.56</v>
       </c>
       <c r="AD28">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE28">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF28">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AG28">
         <v>2.3</v>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK28">
         <v>1.4</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="O31">
-        <v>3.96</v>
+        <v>4.1</v>
       </c>
       <c r="P31">
-        <v>6.09</v>
+        <v>5.5</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5525,10 +5525,10 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="O32">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="P32">
         <v>2.26</v>
@@ -5712,7 +5712,7 @@
         <v>2.3</v>
       </c>
       <c r="V33">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W33">
         <v>1.15</v>
@@ -5851,16 +5851,16 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="O34">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P34">
         <v>2.8</v>
       </c>
       <c r="Q34">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="R34">
         <v>2.3</v>
@@ -5890,7 +5890,7 @@
         <v>4.8</v>
       </c>
       <c r="AA34">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AB34">
         <v>2.2</v>
@@ -6195,7 +6195,7 @@
         <v>1.22</v>
       </c>
       <c r="T36">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U36">
         <v>2</v>
@@ -6340,7 +6340,7 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="O37">
         <v>3.6</v>
@@ -6385,16 +6385,16 @@
         <v>3.1</v>
       </c>
       <c r="AC37">
+        <v>1.85</v>
+      </c>
+      <c r="AD37">
         <v>1.9</v>
-      </c>
-      <c r="AD37">
-        <v>1.85</v>
       </c>
       <c r="AE37">
         <v>1.37</v>
       </c>
       <c r="AF37">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AG37">
         <v>3.13</v>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="O38">
         <v>3.7</v>
@@ -6705,13 +6705,13 @@
         <v>5.2</v>
       </c>
       <c r="AA39">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AB39">
         <v>2.63</v>
       </c>
       <c r="AC39">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AD39">
         <v>1.56</v>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK39">
         <v>1.4</v>
@@ -7164,19 +7164,19 @@
         <v>4.37</v>
       </c>
       <c r="Q42">
-        <v>2.22</v>
+        <v>2.13</v>
       </c>
       <c r="R42">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="S42">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T42">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="U42">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="V42">
         <v>1.44</v>
@@ -7185,28 +7185,28 @@
         <v>1.1</v>
       </c>
       <c r="X42">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y42">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z42">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="AA42">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AB42">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AC42">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AD42">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE42">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF42">
         <v>1.57</v>
@@ -7228,7 +7228,7 @@
         <v>1.25</v>
       </c>
       <c r="AK42">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7321,13 +7321,13 @@
         <v>3.41</v>
       </c>
       <c r="O43">
-        <v>3.67</v>
+        <v>3.8</v>
       </c>
       <c r="P43">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="Q43">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="R43">
         <v>2.5</v>
@@ -7810,10 +7810,10 @@
         <v>2.64</v>
       </c>
       <c r="O46">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P46">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="Q46">
         <v>3.3</v>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="AK46">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.92</v>
+        <v>1.61</v>
       </c>
       <c r="O47">
-        <v>3.7</v>
+        <v>4.15</v>
       </c>
       <c r="P47">
-        <v>3.68</v>
+        <v>4.55</v>
       </c>
       <c r="Q47">
+        <v>1.95</v>
+      </c>
+      <c r="R47">
+        <v>2.5</v>
+      </c>
+      <c r="S47">
+        <v>1.22</v>
+      </c>
+      <c r="T47">
+        <v>3.5</v>
+      </c>
+      <c r="U47">
         <v>2.15</v>
       </c>
-      <c r="R47">
-        <v>2.57</v>
-      </c>
-      <c r="S47">
-        <v>1.2</v>
-      </c>
-      <c r="T47">
-        <v>3.6</v>
-      </c>
-      <c r="U47">
-        <v>2.1</v>
-      </c>
       <c r="V47">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="W47">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X47">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y47">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z47">
-        <v>5.31</v>
+        <v>5</v>
       </c>
       <c r="AA47">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AB47">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AC47">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AD47">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AE47">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF47">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AG47">
-        <v>2.55</v>
+        <v>2.26</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK47">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,65 +8133,65 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.57</v>
+        <v>1.87</v>
       </c>
       <c r="O48">
-        <v>4.62</v>
+        <v>3.7</v>
       </c>
       <c r="P48">
-        <v>4.88</v>
+        <v>3.68</v>
       </c>
       <c r="Q48">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="R48">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="S48">
         <v>1.22</v>
       </c>
       <c r="T48">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="U48">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="V48">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="W48">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X48">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y48">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="Z48">
-        <v>5</v>
+        <v>5.31</v>
       </c>
       <c r="AA48">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="AB48">
+        <v>2.63</v>
+      </c>
+      <c r="AC48">
+        <v>2.35</v>
+      </c>
+      <c r="AD48">
+        <v>1.58</v>
+      </c>
+      <c r="AE48">
+        <v>1.2</v>
+      </c>
+      <c r="AF48">
+        <v>1.44</v>
+      </c>
+      <c r="AG48">
         <v>2.55</v>
       </c>
-      <c r="AC48">
-        <v>2.29</v>
-      </c>
-      <c r="AD48">
-        <v>1.5</v>
-      </c>
-      <c r="AE48">
-        <v>1.22</v>
-      </c>
-      <c r="AF48">
-        <v>1.55</v>
-      </c>
-      <c r="AG48">
-        <v>2.26</v>
-      </c>
       <c r="AH48" t="inlineStr">
         <is>
           <t>[]</t>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK48">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="O50">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="P50">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="Q50">
         <v>2.3</v>
@@ -8486,7 +8486,7 @@
         <v>1.77</v>
       </c>
       <c r="W50">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X50">
         <v>1.01</v>
@@ -8510,7 +8510,7 @@
         <v>1.86</v>
       </c>
       <c r="AE50">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AF50">
         <v>1.36</v>
@@ -8625,10 +8625,10 @@
         <v>1.59</v>
       </c>
       <c r="O51">
-        <v>4.72</v>
+        <v>4.82</v>
       </c>
       <c r="P51">
-        <v>5.3</v>
+        <v>5.46</v>
       </c>
       <c r="Q51">
         <v>2</v>
@@ -8646,7 +8646,7 @@
         <v>2.2</v>
       </c>
       <c r="V51">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W51">
         <v>1.15</v>
@@ -8661,25 +8661,25 @@
         <v>5.4</v>
       </c>
       <c r="AA51">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AB51">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AC51">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="AD51">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AE51">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AF51">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG51">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="O52">
         <v>4.24</v>

--- a/jogos_2026-08-19.xlsx
+++ b/jogos_2026-08-19.xlsx
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Sanat Naft</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.33</v>
+        <v>2.51</v>
       </c>
       <c r="O11">
-        <v>4.33</v>
+        <v>2.61</v>
       </c>
       <c r="P11">
-        <v>8</v>
+        <v>3.04</v>
       </c>
       <c r="Q11">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="R11">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S11">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="V11">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X11">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y11">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z11">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA11">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC11">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AD11">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF11">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="AG11">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK11">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Mes Shahr-e Babak</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sanat Naft</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,49 +2265,49 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="O12">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="P12">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W12">
         <v>0</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC12">
         <v>0</v>
@@ -2319,10 +2319,10 @@
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mes Shahr-e Babak</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -5709,10 +5709,10 @@
         <v>3.7</v>
       </c>
       <c r="U33">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="V33">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W33">
         <v>1.15</v>
@@ -5721,16 +5721,16 @@
         <v>1.03</v>
       </c>
       <c r="Y33">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z33">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AA33">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AB33">
-        <v>2.44</v>
+        <v>2.35</v>
       </c>
       <c r="AC33">
         <v>2.3</v>
@@ -5902,7 +5902,7 @@
         <v>1.52</v>
       </c>
       <c r="AE34">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AF34">
         <v>1.48</v>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK34">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6186,16 +6186,16 @@
         <v>2.6</v>
       </c>
       <c r="Q36">
-        <v>2.5</v>
+        <v>2.82</v>
       </c>
       <c r="R36">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="S36">
         <v>1.22</v>
       </c>
       <c r="T36">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U36">
         <v>2</v>
@@ -6222,7 +6222,7 @@
         <v>2.75</v>
       </c>
       <c r="AC36">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="AD36">
         <v>1.7</v>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK36">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6343,13 +6343,13 @@
         <v>2.7</v>
       </c>
       <c r="O37">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P37">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="Q37">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R37">
         <v>2.62</v>
@@ -6367,31 +6367,31 @@
         <v>1.75</v>
       </c>
       <c r="W37">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X37">
         <v>1.01</v>
       </c>
       <c r="Y37">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z37">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="AA37">
+        <v>1.36</v>
+      </c>
+      <c r="AB37">
+        <v>2.9</v>
+      </c>
+      <c r="AC37">
+        <v>1.98</v>
+      </c>
+      <c r="AD37">
+        <v>1.86</v>
+      </c>
+      <c r="AE37">
         <v>1.33</v>
-      </c>
-      <c r="AB37">
-        <v>3.1</v>
-      </c>
-      <c r="AC37">
-        <v>1.85</v>
-      </c>
-      <c r="AD37">
-        <v>1.9</v>
-      </c>
-      <c r="AE37">
-        <v>1.37</v>
       </c>
       <c r="AF37">
         <v>1.3</v>
@@ -6503,7 +6503,7 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="O38">
         <v>3.7</v>
@@ -6515,10 +6515,10 @@
         <v>2.4</v>
       </c>
       <c r="R38">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="S38">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T38">
         <v>4.1</v>
@@ -6530,13 +6530,13 @@
         <v>1.69</v>
       </c>
       <c r="W38">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X38">
         <v>1.02</v>
       </c>
       <c r="Y38">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Z38">
         <v>5.7</v>
@@ -6560,7 +6560,7 @@
         <v>1.4</v>
       </c>
       <c r="AG38">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="O39">
-        <v>4.08</v>
+        <v>3.61</v>
       </c>
       <c r="P39">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q39">
         <v>3.1</v>
@@ -6681,10 +6681,10 @@
         <v>2.35</v>
       </c>
       <c r="S39">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T39">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U39">
         <v>2.2</v>
@@ -6708,13 +6708,13 @@
         <v>1.53</v>
       </c>
       <c r="AB39">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="AC39">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="AD39">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AE39">
         <v>1.24</v>
@@ -7321,19 +7321,19 @@
         <v>3.41</v>
       </c>
       <c r="O43">
-        <v>3.8</v>
+        <v>4.34</v>
       </c>
       <c r="P43">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="Q43">
-        <v>3.8</v>
+        <v>3.88</v>
       </c>
       <c r="R43">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="S43">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T43">
         <v>3.8</v>
@@ -7354,7 +7354,7 @@
         <v>1.13</v>
       </c>
       <c r="Z43">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="AA43">
         <v>1.52</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="O44">
         <v>3.6</v>
@@ -7490,7 +7490,7 @@
         <v>3.8</v>
       </c>
       <c r="Q44">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="R44">
         <v>2.3</v>
@@ -7517,22 +7517,22 @@
         <v>1.22</v>
       </c>
       <c r="Z44">
-        <v>4.31</v>
+        <v>4.15</v>
       </c>
       <c r="AA44">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB44">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="AC44">
-        <v>2.71</v>
+        <v>2.57</v>
       </c>
       <c r="AD44">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AE44">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF44">
         <v>1.67</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK44">
         <v>1.91</v>
@@ -7810,19 +7810,19 @@
         <v>2.64</v>
       </c>
       <c r="O46">
-        <v>3.4</v>
+        <v>3.88</v>
       </c>
       <c r="P46">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="Q46">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R46">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="S46">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T46">
         <v>3.28</v>
@@ -7831,7 +7831,7 @@
         <v>2.3</v>
       </c>
       <c r="V46">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W46">
         <v>1.12</v>
@@ -7840,13 +7840,13 @@
         <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z46">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="AA46">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AB46">
         <v>2.15</v>
@@ -7858,7 +7858,7 @@
         <v>1.44</v>
       </c>
       <c r="AE46">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AF46">
         <v>1.5</v>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AK46">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7994,13 +7994,13 @@
         <v>2.15</v>
       </c>
       <c r="V47">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="W47">
         <v>1.17</v>
       </c>
       <c r="X47">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y47">
         <v>1.15</v>
@@ -8012,10 +8012,10 @@
         <v>1.5</v>
       </c>
       <c r="AB47">
-        <v>2.55</v>
+        <v>2.36</v>
       </c>
       <c r="AC47">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="AD47">
         <v>1.5</v>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AK47">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="O48">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P48">
-        <v>3.68</v>
+        <v>3.6</v>
       </c>
       <c r="Q48">
         <v>2.15</v>
@@ -8175,7 +8175,7 @@
         <v>1.46</v>
       </c>
       <c r="AB48">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="AC48">
         <v>2.35</v>
@@ -8184,7 +8184,7 @@
         <v>1.58</v>
       </c>
       <c r="AE48">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF48">
         <v>1.44</v>
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="O50">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="P50">
-        <v>3.04</v>
+        <v>2.97</v>
       </c>
       <c r="Q50">
         <v>2.3</v>
@@ -8483,10 +8483,10 @@
         <v>1.96</v>
       </c>
       <c r="V50">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="W50">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X50">
         <v>1.01</v>
@@ -8510,7 +8510,7 @@
         <v>1.86</v>
       </c>
       <c r="AE50">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AF50">
         <v>1.36</v>
@@ -8622,16 +8622,16 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="O51">
-        <v>4.82</v>
+        <v>4.2</v>
       </c>
       <c r="P51">
-        <v>5.46</v>
+        <v>5.6</v>
       </c>
       <c r="Q51">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="R51">
         <v>2.5</v>
@@ -8646,7 +8646,7 @@
         <v>2.2</v>
       </c>
       <c r="V51">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W51">
         <v>1.15</v>
@@ -8667,10 +8667,10 @@
         <v>2.4</v>
       </c>
       <c r="AC51">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AD51">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AE51">
         <v>1.23</v>

--- a/jogos_2026-08-19.xlsx
+++ b/jogos_2026-08-19.xlsx
@@ -635,16 +635,16 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="O2">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P2">
         <v>3.25</v>
       </c>
       <c r="Q2">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="R2">
         <v>2.4</v>
@@ -653,13 +653,13 @@
         <v>1.2</v>
       </c>
       <c r="T2">
-        <v>4</v>
+        <v>3.68</v>
       </c>
       <c r="U2">
         <v>2.05</v>
       </c>
       <c r="V2">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="W2">
         <v>1.13</v>
@@ -668,7 +668,7 @@
         <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z2">
         <v>5.65</v>
@@ -677,22 +677,22 @@
         <v>1.44</v>
       </c>
       <c r="AB2">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AC2">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="AD2">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AE2">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AF2">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG2">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AK2">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1130,7 +1130,7 @@
         <v>3.4</v>
       </c>
       <c r="P5">
-        <v>4.55</v>
+        <v>3.85</v>
       </c>
       <c r="Q5">
         <v>2.37</v>
@@ -1157,7 +1157,7 @@
         <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z5">
         <v>2.83</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK5">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1776,16 +1776,16 @@
         </is>
       </c>
       <c r="N9">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="O9">
         <v>3.5</v>
       </c>
       <c r="P9">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="Q9">
-        <v>4.47</v>
+        <v>5.25</v>
       </c>
       <c r="R9">
         <v>2.19</v>
@@ -1809,7 +1809,7 @@
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="Z9">
         <v>3.04</v>
@@ -1824,16 +1824,16 @@
         <v>3.69</v>
       </c>
       <c r="AD9">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE9">
         <v>1.03</v>
       </c>
       <c r="AF9">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AG9">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="AK9">
         <v>1.15</v>
@@ -3083,37 +3083,37 @@
         <v>1.25</v>
       </c>
       <c r="O17">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="P17">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="Q17">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="R17">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="S17">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T17">
         <v>3.18</v>
       </c>
       <c r="U17">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="V17">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W17">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X17">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z17">
         <v>4.5</v>
@@ -3153,7 +3153,7 @@
         <v>1.13</v>
       </c>
       <c r="AK17">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3412,10 +3412,10 @@
         <v>2.65</v>
       </c>
       <c r="P19">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="Q19">
-        <v>2.3</v>
+        <v>2.49</v>
       </c>
       <c r="R19">
         <v>1.89</v>
@@ -3424,19 +3424,19 @@
         <v>1.52</v>
       </c>
       <c r="T19">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="U19">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="V19">
         <v>1.25</v>
       </c>
       <c r="W19">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X19">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Y19">
         <v>1.5</v>
@@ -3445,7 +3445,7 @@
         <v>2.53</v>
       </c>
       <c r="AA19">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="AB19">
         <v>1.5</v>
@@ -3479,7 +3479,7 @@
         <v>1.27</v>
       </c>
       <c r="AK19">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3898,25 +3898,25 @@
         <v>1.58</v>
       </c>
       <c r="O22">
-        <v>4.1</v>
+        <v>3.91</v>
       </c>
       <c r="P22">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="Q22">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="R22">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="S22">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T22">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="U22">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="V22">
         <v>1.5</v>
@@ -3934,22 +3934,22 @@
         <v>3.9</v>
       </c>
       <c r="AA22">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AB22">
         <v>2</v>
       </c>
       <c r="AC22">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AD22">
         <v>1.4</v>
       </c>
       <c r="AE22">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF22">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG22">
         <v>1.95</v>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AK22">
         <v>2.3</v>
@@ -4058,19 +4058,19 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="O23">
+        <v>3.9</v>
+      </c>
+      <c r="P23">
         <v>3.8</v>
       </c>
-      <c r="P23">
-        <v>4.2</v>
-      </c>
       <c r="Q23">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="R23">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="S23">
         <v>1.33</v>
@@ -4079,28 +4079,28 @@
         <v>3.1</v>
       </c>
       <c r="U23">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="V23">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W23">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X23">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y23">
         <v>1.2</v>
       </c>
       <c r="Z23">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="AA23">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AB23">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AC23">
         <v>2.9</v>
@@ -4109,13 +4109,13 @@
         <v>1.36</v>
       </c>
       <c r="AE23">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF23">
         <v>1.73</v>
       </c>
       <c r="AG23">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK23">
         <v>2</v>
@@ -4224,28 +4224,28 @@
         <v>2.5</v>
       </c>
       <c r="O24">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="P24">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q24">
-        <v>3.02</v>
+        <v>2.8</v>
       </c>
       <c r="R24">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="S24">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T24">
-        <v>3.66</v>
+        <v>3.75</v>
       </c>
       <c r="U24">
         <v>2.1</v>
       </c>
       <c r="V24">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="W24">
         <v>1.14</v>
@@ -4260,19 +4260,19 @@
         <v>5.75</v>
       </c>
       <c r="AA24">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AB24">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AC24">
         <v>2.05</v>
       </c>
       <c r="AD24">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AE24">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AF24">
         <v>1.4</v>
@@ -4294,7 +4294,7 @@
         <v>1.5</v>
       </c>
       <c r="AK24">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,61 +4384,61 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="O25">
-        <v>3.4</v>
+        <v>3.32</v>
       </c>
       <c r="P25">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="Q25">
-        <v>2.87</v>
+        <v>2.82</v>
       </c>
       <c r="R25">
         <v>2.02</v>
       </c>
       <c r="S25">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="T25">
-        <v>2.88</v>
+        <v>2.68</v>
       </c>
       <c r="U25">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="V25">
         <v>1.42</v>
       </c>
       <c r="W25">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X25">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y25">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z25">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AA25">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AB25">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AC25">
         <v>3.5</v>
       </c>
       <c r="AD25">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE25">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF25">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AG25">
         <v>2</v>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AK25">
         <v>1.53</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="O26">
-        <v>5.25</v>
+        <v>5.6</v>
       </c>
       <c r="P26">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="Q26">
         <v>1.73</v>
@@ -4562,10 +4562,10 @@
         <v>2.45</v>
       </c>
       <c r="S26">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T26">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U26">
         <v>2.44</v>
@@ -4574,10 +4574,10 @@
         <v>1.47</v>
       </c>
       <c r="W26">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X26">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
         <v>1.22</v>
@@ -4586,7 +4586,7 @@
         <v>3.55</v>
       </c>
       <c r="AA26">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AB26">
         <v>2</v>
@@ -4604,7 +4604,7 @@
         <v>2.2</v>
       </c>
       <c r="AG26">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         <v>1.15</v>
       </c>
       <c r="AF28">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AG28">
         <v>2.3</v>
@@ -5045,16 +5045,16 @@
         <v>2.35</v>
       </c>
       <c r="Q29">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R29">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="S29">
         <v>1.4</v>
       </c>
       <c r="T29">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="U29">
         <v>3</v>
@@ -5066,7 +5066,7 @@
         <v>1.07</v>
       </c>
       <c r="X29">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y29">
         <v>1.4</v>
@@ -5084,7 +5084,7 @@
         <v>3.75</v>
       </c>
       <c r="AD29">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE29">
         <v>1.07</v>
@@ -5093,7 +5093,7 @@
         <v>1.85</v>
       </c>
       <c r="AG29">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="AK29">
         <v>1.4</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="O30">
-        <v>3.5</v>
+        <v>3.17</v>
       </c>
       <c r="P30">
-        <v>6.2</v>
+        <v>4.6</v>
       </c>
       <c r="Q30">
         <v>2.17</v>
@@ -5223,7 +5223,7 @@
         <v>3.18</v>
       </c>
       <c r="V30">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W30">
         <v>1.04</v>
@@ -5235,7 +5235,7 @@
         <v>1.36</v>
       </c>
       <c r="Z30">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="AA30">
         <v>2.09</v>
@@ -5253,7 +5253,7 @@
         <v>1.06</v>
       </c>
       <c r="AF30">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AG30">
         <v>1.65</v>
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="O31">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="P31">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA31">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AB31">
         <v>2.1</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK31">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="O32">
         <v>3.5</v>
       </c>
       <c r="P32">
-        <v>2.26</v>
+        <v>2.35</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA32">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AB32">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -6832,10 +6832,10 @@
         <v>2.09</v>
       </c>
       <c r="O40">
-        <v>2.85</v>
+        <v>2.87</v>
       </c>
       <c r="P40">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="Q40">
         <v>3.01</v>
@@ -6859,13 +6859,13 @@
         <v>1.02</v>
       </c>
       <c r="X40">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Y40">
         <v>1.49</v>
       </c>
       <c r="Z40">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AA40">
         <v>2.63</v>
@@ -6883,7 +6883,7 @@
         <v>1.04</v>
       </c>
       <c r="AF40">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AG40">
         <v>1.62</v>
@@ -6902,7 +6902,7 @@
         <v>1.38</v>
       </c>
       <c r="AK40">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7004,43 +7004,43 @@
         <v>1.85</v>
       </c>
       <c r="R41">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="S41">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T41">
         <v>2.9</v>
       </c>
       <c r="U41">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="V41">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W41">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X41">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y41">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z41">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="AA41">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AB41">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AC41">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="AD41">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE41">
         <v>1.11</v>
@@ -7049,7 +7049,7 @@
         <v>2.1</v>
       </c>
       <c r="AG41">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AK41">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7164,71 +7164,71 @@
         <v>4.37</v>
       </c>
       <c r="Q42">
-        <v>2.13</v>
+        <v>1.97</v>
       </c>
       <c r="R42">
-        <v>2.26</v>
+        <v>2.52</v>
       </c>
       <c r="S42">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T42">
-        <v>3.04</v>
+        <v>4.2</v>
       </c>
       <c r="U42">
-        <v>2.46</v>
+        <v>1.82</v>
       </c>
       <c r="V42">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="W42">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="X42">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y42">
+        <v>1.13</v>
+      </c>
+      <c r="Z42">
+        <v>4.5</v>
+      </c>
+      <c r="AA42">
+        <v>1.4</v>
+      </c>
+      <c r="AB42">
+        <v>2.42</v>
+      </c>
+      <c r="AC42">
+        <v>2.06</v>
+      </c>
+      <c r="AD42">
+        <v>1.65</v>
+      </c>
+      <c r="AE42">
+        <v>1.25</v>
+      </c>
+      <c r="AF42">
+        <v>1.4</v>
+      </c>
+      <c r="AG42">
+        <v>2.3</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ42">
         <v>1.2</v>
       </c>
-      <c r="Z42">
-        <v>3.7</v>
-      </c>
-      <c r="AA42">
-        <v>1.72</v>
-      </c>
-      <c r="AB42">
-        <v>1.98</v>
-      </c>
-      <c r="AC42">
-        <v>2.7</v>
-      </c>
-      <c r="AD42">
-        <v>1.36</v>
-      </c>
-      <c r="AE42">
-        <v>1.11</v>
-      </c>
-      <c r="AF42">
-        <v>1.57</v>
-      </c>
-      <c r="AG42">
-        <v>2</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ42">
-        <v>1.25</v>
-      </c>
       <c r="AK42">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7653,10 +7653,10 @@
         <v>2.66</v>
       </c>
       <c r="Q45">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R45">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="S45">
         <v>1.5</v>
@@ -7677,16 +7677,16 @@
         <v>1.11</v>
       </c>
       <c r="Y45">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="Z45">
         <v>2.31</v>
       </c>
       <c r="AA45">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AB45">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AC45">
         <v>4.8</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.64</v>
+        <v>1.61</v>
       </c>
       <c r="O46">
-        <v>3.88</v>
+        <v>4.15</v>
       </c>
       <c r="P46">
-        <v>2.44</v>
+        <v>4.55</v>
       </c>
       <c r="Q46">
-        <v>3.1</v>
+        <v>1.95</v>
       </c>
       <c r="R46">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="S46">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="T46">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="U46">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="V46">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="W46">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="X46">
         <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z46">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="AA46">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="AB46">
-        <v>2.15</v>
+        <v>2.36</v>
       </c>
       <c r="AC46">
-        <v>2.63</v>
+        <v>2.32</v>
       </c>
       <c r="AD46">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AE46">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AF46">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AG46">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.5</v>
+        <v>1.13</v>
       </c>
       <c r="AK46">
-        <v>1.4</v>
+        <v>2.25</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.61</v>
+        <v>1.86</v>
       </c>
       <c r="O47">
-        <v>4.15</v>
+        <v>3.5</v>
       </c>
       <c r="P47">
-        <v>4.55</v>
+        <v>3.6</v>
       </c>
       <c r="Q47">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="R47">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="S47">
         <v>1.22</v>
       </c>
       <c r="T47">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="U47">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="V47">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W47">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X47">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y47">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z47">
-        <v>5</v>
+        <v>5.31</v>
       </c>
       <c r="AA47">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AB47">
-        <v>2.36</v>
+        <v>2.65</v>
       </c>
       <c r="AC47">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AD47">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AE47">
         <v>1.22</v>
       </c>
       <c r="AF47">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AG47">
-        <v>2.26</v>
+        <v>2.55</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AK47">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.86</v>
+        <v>2.64</v>
       </c>
       <c r="O48">
-        <v>3.5</v>
+        <v>3.88</v>
       </c>
       <c r="P48">
-        <v>3.6</v>
+        <v>2.44</v>
       </c>
       <c r="Q48">
+        <v>3.1</v>
+      </c>
+      <c r="R48">
+        <v>2.28</v>
+      </c>
+      <c r="S48">
+        <v>1.29</v>
+      </c>
+      <c r="T48">
+        <v>3.28</v>
+      </c>
+      <c r="U48">
+        <v>2.3</v>
+      </c>
+      <c r="V48">
+        <v>1.53</v>
+      </c>
+      <c r="W48">
+        <v>1.12</v>
+      </c>
+      <c r="X48">
+        <v>1.01</v>
+      </c>
+      <c r="Y48">
+        <v>1.18</v>
+      </c>
+      <c r="Z48">
+        <v>4.25</v>
+      </c>
+      <c r="AA48">
+        <v>1.68</v>
+      </c>
+      <c r="AB48">
         <v>2.15</v>
       </c>
-      <c r="R48">
-        <v>2.57</v>
-      </c>
-      <c r="S48">
-        <v>1.22</v>
-      </c>
-      <c r="T48">
-        <v>3.65</v>
-      </c>
-      <c r="U48">
-        <v>2.2</v>
-      </c>
-      <c r="V48">
-        <v>1.6</v>
-      </c>
-      <c r="W48">
-        <v>1.13</v>
-      </c>
-      <c r="X48">
-        <v>1.03</v>
-      </c>
-      <c r="Y48">
-        <v>1.13</v>
-      </c>
-      <c r="Z48">
-        <v>5.31</v>
-      </c>
-      <c r="AA48">
-        <v>1.46</v>
-      </c>
-      <c r="AB48">
-        <v>2.65</v>
-      </c>
       <c r="AC48">
-        <v>2.35</v>
+        <v>2.63</v>
       </c>
       <c r="AD48">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AE48">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AF48">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG48">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AK48">
-        <v>1.83</v>
+        <v>1.4</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.55</v>
+        <v>2.49</v>
       </c>
       <c r="O49">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P49">
         <v>2.5</v>
       </c>
       <c r="Q49">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="R49">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="S49">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="T49">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="U49">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V49">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W49">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X49">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y49">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="Z49">
-        <v>3.74</v>
+        <v>3.42</v>
       </c>
       <c r="AA49">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="AB49">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AC49">
-        <v>2.82</v>
+        <v>3.08</v>
       </c>
       <c r="AD49">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AE49">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF49">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AG49">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8369,7 +8369,7 @@
         <v>1.44</v>
       </c>
       <c r="AK49">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="AL49">
         <v>0</v>

--- a/jogos_2026-08-19.xlsx
+++ b/jogos_2026-08-19.xlsx
@@ -631,65 +631,65 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N2">
-        <v>1.95</v>
+        <v>1.4</v>
       </c>
       <c r="O2">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="P2">
-        <v>3.25</v>
+        <v>6.32</v>
       </c>
       <c r="Q2">
         <v>1.83</v>
       </c>
       <c r="R2">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S2">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T2">
         <v>3.68</v>
       </c>
       <c r="U2">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="V2">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="W2">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X2">
         <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z2">
         <v>5.65</v>
       </c>
       <c r="AA2">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AB2">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AC2">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AD2">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AE2">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AF2">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AG2">
         <v>2.28</v>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AK2">
-        <v>2.17</v>
+        <v>2.74</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -1729,12 +1729,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Veles</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>3.95</v>
+        <v>2.16</v>
       </c>
       <c r="O9">
-        <v>3.5</v>
+        <v>2.64</v>
       </c>
       <c r="P9">
-        <v>1.71</v>
+        <v>3.73</v>
       </c>
       <c r="Q9">
-        <v>5.25</v>
+        <v>3</v>
       </c>
       <c r="R9">
-        <v>2.19</v>
+        <v>1.73</v>
       </c>
       <c r="S9">
-        <v>1.41</v>
+        <v>1.75</v>
       </c>
       <c r="T9">
-        <v>2.66</v>
+        <v>1.93</v>
       </c>
       <c r="U9">
-        <v>2.99</v>
+        <v>4.5</v>
       </c>
       <c r="V9">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="W9">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X9">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="Y9">
-        <v>1.29</v>
+        <v>1.85</v>
       </c>
       <c r="Z9">
-        <v>3.04</v>
+        <v>1.85</v>
       </c>
       <c r="AA9">
-        <v>2.08</v>
+        <v>3.65</v>
       </c>
       <c r="AB9">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="AC9">
-        <v>3.69</v>
+        <v>0</v>
       </c>
       <c r="AD9">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE9">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>1.94</v>
+        <v>2.75</v>
       </c>
       <c r="AG9">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.95</v>
+        <v>1.36</v>
       </c>
       <c r="AK9">
-        <v>1.15</v>
+        <v>1.62</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-08-19 13:30:00</t>
+          <t>2026-08-19 13:00:00</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Sanat Naft</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,49 +1939,49 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.16</v>
+        <v>2.51</v>
       </c>
       <c r="O10">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="P10">
-        <v>3.73</v>
+        <v>3.04</v>
       </c>
       <c r="Q10">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R10">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S10">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="T10">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U10">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="V10">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W10">
         <v>0</v>
       </c>
       <c r="X10">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Y10">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z10">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA10">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AB10">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC10">
         <v>0</v>
@@ -1993,10 +1993,10 @@
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AG10">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK10">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-08-19 13:30:00</t>
+          <t>2026-08-19 13:00:00</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Mes Shahr-e Babak</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sanat Naft</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,49 +2102,49 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.51</v>
+        <v>4.99</v>
       </c>
       <c r="O11">
-        <v>2.61</v>
+        <v>3.04</v>
       </c>
       <c r="P11">
-        <v>3.04</v>
+        <v>1.72</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W11">
         <v>0</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC11">
         <v>0</v>
@@ -2156,10 +2156,10 @@
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-08-19 13:30:00</t>
+          <t>2026-08-19 13:00:00</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mes Shahr-e Babak</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q12">
-        <v>5.25</v>
+        <v>1.85</v>
       </c>
       <c r="R12">
-        <v>1.85</v>
+        <v>2.14</v>
       </c>
       <c r="S12">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="T12">
-        <v>2.2</v>
+        <v>2.53</v>
       </c>
       <c r="U12">
-        <v>3.7</v>
+        <v>3.18</v>
       </c>
       <c r="V12">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X12">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="Z12">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="AA12">
-        <v>2.85</v>
+        <v>2.23</v>
       </c>
       <c r="AB12">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF12">
-        <v>2.4</v>
+        <v>2.84</v>
       </c>
       <c r="AG12">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.28</v>
+        <v>1.02</v>
       </c>
       <c r="AK12">
-        <v>1.11</v>
+        <v>3.05</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2026-08-19 13:30:00</t>
+          <t>2026-08-19 13:00:00</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Veles</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,80 +2428,80 @@
         </is>
       </c>
       <c r="N13">
+        <v>3.95</v>
+      </c>
+      <c r="O13">
+        <v>3.5</v>
+      </c>
+      <c r="P13">
+        <v>1.71</v>
+      </c>
+      <c r="Q13">
+        <v>5.25</v>
+      </c>
+      <c r="R13">
+        <v>2.19</v>
+      </c>
+      <c r="S13">
+        <v>1.41</v>
+      </c>
+      <c r="T13">
+        <v>2.66</v>
+      </c>
+      <c r="U13">
+        <v>2.99</v>
+      </c>
+      <c r="V13">
         <v>1.33</v>
       </c>
-      <c r="O13">
-        <v>4.33</v>
-      </c>
-      <c r="P13">
-        <v>8</v>
-      </c>
-      <c r="Q13">
-        <v>1.84</v>
-      </c>
-      <c r="R13">
-        <v>2.15</v>
-      </c>
-      <c r="S13">
-        <v>1.43</v>
-      </c>
-      <c r="T13">
-        <v>2.53</v>
-      </c>
-      <c r="U13">
-        <v>3.18</v>
-      </c>
-      <c r="V13">
-        <v>1.28</v>
-      </c>
       <c r="W13">
+        <v>1.02</v>
+      </c>
+      <c r="X13">
         <v>1.01</v>
       </c>
-      <c r="X13">
-        <v>1.02</v>
-      </c>
       <c r="Y13">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="Z13">
-        <v>2.7</v>
+        <v>3.04</v>
       </c>
       <c r="AA13">
-        <v>2.23</v>
+        <v>2.08</v>
       </c>
       <c r="AB13">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AC13">
-        <v>4.2</v>
+        <v>3.69</v>
       </c>
       <c r="AD13">
+        <v>1.21</v>
+      </c>
+      <c r="AE13">
+        <v>1.03</v>
+      </c>
+      <c r="AF13">
+        <v>1.94</v>
+      </c>
+      <c r="AG13">
+        <v>1.75</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13">
+        <v>1.95</v>
+      </c>
+      <c r="AK13">
         <v>1.15</v>
-      </c>
-      <c r="AE13">
-        <v>1.01</v>
-      </c>
-      <c r="AF13">
-        <v>2.84</v>
-      </c>
-      <c r="AG13">
-        <v>1.35</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13">
-        <v>1.13</v>
-      </c>
-      <c r="AK13">
-        <v>3.12</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G16">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mamelodi Sundowns</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Marumo Gallants</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Q17">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="R17">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S17">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T17">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="V17">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W17">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X17">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y17">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Z17">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AA17">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AB17">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC17">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD17">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AE17">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF17">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG17">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK17">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2026-08-19 14:30:00</t>
+          <t>2026-08-19 14:00:00</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Mamelodi Sundowns</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Marumo Gallants</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,65 +5036,65 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.94</v>
+        <v>1.55</v>
       </c>
       <c r="O29">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="P29">
-        <v>2.35</v>
+        <v>4.6</v>
       </c>
       <c r="Q29">
-        <v>3.4</v>
+        <v>2.17</v>
       </c>
       <c r="R29">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S29">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T29">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="U29">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="V29">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W29">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X29">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y29">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z29">
-        <v>2.83</v>
+        <v>3.08</v>
       </c>
       <c r="AA29">
+        <v>2.09</v>
+      </c>
+      <c r="AB29">
+        <v>1.7</v>
+      </c>
+      <c r="AC29">
+        <v>4</v>
+      </c>
+      <c r="AD29">
+        <v>1.22</v>
+      </c>
+      <c r="AE29">
+        <v>1.06</v>
+      </c>
+      <c r="AF29">
         <v>2.15</v>
       </c>
-      <c r="AB29">
+      <c r="AG29">
         <v>1.65</v>
       </c>
-      <c r="AC29">
-        <v>3.75</v>
-      </c>
-      <c r="AD29">
-        <v>1.19</v>
-      </c>
-      <c r="AE29">
-        <v>1.07</v>
-      </c>
-      <c r="AF29">
-        <v>1.85</v>
-      </c>
-      <c r="AG29">
-        <v>1.85</v>
-      </c>
       <c r="AH29" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.52</v>
+        <v>1.14</v>
       </c>
       <c r="AK29">
-        <v>1.4</v>
+        <v>2.21</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.55</v>
+        <v>2.94</v>
       </c>
       <c r="O30">
-        <v>3.17</v>
+        <v>3.25</v>
       </c>
       <c r="P30">
-        <v>4.6</v>
+        <v>2.35</v>
       </c>
       <c r="Q30">
-        <v>2.17</v>
+        <v>3.4</v>
       </c>
       <c r="R30">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S30">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T30">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="U30">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="V30">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W30">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X30">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y30">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z30">
-        <v>3.08</v>
+        <v>2.83</v>
       </c>
       <c r="AA30">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="AB30">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AC30">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="AD30">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE30">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF30">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AG30">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.14</v>
+        <v>1.52</v>
       </c>
       <c r="AK30">
-        <v>2.21</v>
+        <v>1.4</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5688,16 +5688,16 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="O33">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="P33">
-        <v>4.65</v>
+        <v>5.15</v>
       </c>
       <c r="Q33">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="R33">
         <v>2.45</v>
@@ -5706,16 +5706,16 @@
         <v>1.25</v>
       </c>
       <c r="T33">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="U33">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="V33">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="W33">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X33">
         <v>1.03</v>
@@ -5724,22 +5724,22 @@
         <v>1.14</v>
       </c>
       <c r="Z33">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA33">
         <v>1.57</v>
       </c>
       <c r="AB33">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AC33">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="AD33">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AE33">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF33">
         <v>1.6</v>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AK33">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5854,22 +5854,22 @@
         <v>2.1</v>
       </c>
       <c r="O34">
-        <v>3.5</v>
+        <v>3.92</v>
       </c>
       <c r="P34">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="Q34">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="R34">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="S34">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T34">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="U34">
         <v>2.48</v>
@@ -5878,31 +5878,31 @@
         <v>1.52</v>
       </c>
       <c r="W34">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X34">
         <v>1.01</v>
       </c>
       <c r="Y34">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="Z34">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AA34">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AB34">
         <v>2.2</v>
       </c>
       <c r="AC34">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="AD34">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="AE34">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AF34">
         <v>1.48</v>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK34">
         <v>1.61</v>
@@ -6014,43 +6014,43 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="O35">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P35">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA35">
         <v>1.75</v>
@@ -6059,19 +6059,19 @@
         <v>2.05</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,19 +6177,19 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="O36">
-        <v>3.7</v>
+        <v>3.71</v>
       </c>
       <c r="P36">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="Q36">
-        <v>2.82</v>
+        <v>2.5</v>
       </c>
       <c r="R36">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="S36">
         <v>1.22</v>
@@ -6219,7 +6219,7 @@
         <v>1.44</v>
       </c>
       <c r="AB36">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AC36">
         <v>2.08</v>
@@ -6234,7 +6234,7 @@
         <v>1.35</v>
       </c>
       <c r="AG36">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="AK36">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6349,10 +6349,10 @@
         <v>2.13</v>
       </c>
       <c r="Q37">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="R37">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="S37">
         <v>1.14</v>
@@ -6361,13 +6361,13 @@
         <v>4.33</v>
       </c>
       <c r="U37">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V37">
         <v>1.75</v>
       </c>
       <c r="W37">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X37">
         <v>1.01</v>
@@ -6379,16 +6379,16 @@
         <v>6.5</v>
       </c>
       <c r="AA37">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AB37">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="AC37">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AD37">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AE37">
         <v>1.33</v>
@@ -6397,7 +6397,7 @@
         <v>1.3</v>
       </c>
       <c r="AG37">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.24</v>
+        <v>1.63</v>
       </c>
       <c r="AK37">
         <v>1.4</v>
@@ -6503,34 +6503,34 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="O38">
         <v>3.7</v>
       </c>
       <c r="P38">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="Q38">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="R38">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S38">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T38">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="U38">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="V38">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="W38">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X38">
         <v>1.02</v>
@@ -6545,7 +6545,7 @@
         <v>1.4</v>
       </c>
       <c r="AB38">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AC38">
         <v>2.1</v>
@@ -6554,13 +6554,13 @@
         <v>1.71</v>
       </c>
       <c r="AE38">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AF38">
         <v>1.4</v>
       </c>
       <c r="AG38">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK38">
         <v>1.8</v>
@@ -6672,16 +6672,16 @@
         <v>3.61</v>
       </c>
       <c r="P39">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q39">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="R39">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="S39">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T39">
         <v>4</v>
@@ -6723,7 +6723,7 @@
         <v>1.44</v>
       </c>
       <c r="AG39">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK39">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7318,49 +7318,49 @@
         </is>
       </c>
       <c r="N43">
-        <v>3.41</v>
+        <v>2.95</v>
       </c>
       <c r="O43">
-        <v>4.34</v>
+        <v>3.6</v>
       </c>
       <c r="P43">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="Q43">
-        <v>3.88</v>
+        <v>3.36</v>
       </c>
       <c r="R43">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="S43">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T43">
         <v>3.8</v>
       </c>
       <c r="U43">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="V43">
         <v>1.65</v>
       </c>
       <c r="W43">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X43">
         <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z43">
         <v>5</v>
       </c>
       <c r="AA43">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AB43">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AC43">
         <v>2.25</v>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="AK43">
         <v>1.3</v>
@@ -7484,16 +7484,16 @@
         <v>1.73</v>
       </c>
       <c r="O44">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P44">
         <v>3.8</v>
       </c>
       <c r="Q44">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="R44">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="S44">
         <v>1.3</v>
@@ -7502,7 +7502,7 @@
         <v>3.3</v>
       </c>
       <c r="U44">
-        <v>2.41</v>
+        <v>2.34</v>
       </c>
       <c r="V44">
         <v>1.5</v>
@@ -7514,22 +7514,22 @@
         <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z44">
         <v>4.15</v>
       </c>
       <c r="AA44">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB44">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AC44">
         <v>2.57</v>
       </c>
       <c r="AD44">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AE44">
         <v>1.17</v>
@@ -7538,7 +7538,7 @@
         <v>1.67</v>
       </c>
       <c r="AG44">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK44">
         <v>1.91</v>
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="O46">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="P46">
-        <v>4.55</v>
+        <v>4.33</v>
       </c>
       <c r="Q46">
         <v>1.95</v>
       </c>
       <c r="R46">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="S46">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T46">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U46">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="V46">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="W46">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X46">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y46">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z46">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AA46">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB46">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AC46">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="AD46">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AE46">
         <v>1.22</v>
       </c>
       <c r="AF46">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG46">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AK46">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="O47">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P47">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="Q47">
         <v>2.15</v>
@@ -8015,13 +8015,13 @@
         <v>2.65</v>
       </c>
       <c r="AC47">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AD47">
         <v>1.58</v>
       </c>
       <c r="AE47">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF47">
         <v>1.44</v>
@@ -8139,16 +8139,16 @@
         <v>3.88</v>
       </c>
       <c r="P48">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="Q48">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R48">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="S48">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T48">
         <v>3.28</v>
@@ -8160,22 +8160,22 @@
         <v>1.53</v>
       </c>
       <c r="W48">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X48">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z48">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="AA48">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AB48">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AC48">
         <v>2.63</v>
@@ -8184,13 +8184,13 @@
         <v>1.44</v>
       </c>
       <c r="AE48">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AF48">
         <v>1.5</v>
       </c>
       <c r="AG48">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AK48">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8305,10 +8305,10 @@
         <v>2.5</v>
       </c>
       <c r="Q49">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="R49">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="S49">
         <v>1.34</v>
@@ -8317,43 +8317,43 @@
         <v>3.2</v>
       </c>
       <c r="U49">
-        <v>2.63</v>
+        <v>2.76</v>
       </c>
       <c r="V49">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W49">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X49">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y49">
         <v>1.26</v>
       </c>
       <c r="Z49">
-        <v>3.42</v>
+        <v>3.65</v>
       </c>
       <c r="AA49">
         <v>1.87</v>
       </c>
       <c r="AB49">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AC49">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AD49">
         <v>1.34</v>
       </c>
       <c r="AE49">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF49">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AG49">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="AK49">
         <v>1.41</v>
@@ -8459,34 +8459,34 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="O50">
-        <v>4.4</v>
+        <v>3.93</v>
       </c>
       <c r="P50">
-        <v>2.97</v>
+        <v>2.87</v>
       </c>
       <c r="Q50">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="R50">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="S50">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T50">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="U50">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V50">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="W50">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X50">
         <v>1.01</v>
@@ -8498,22 +8498,22 @@
         <v>6.56</v>
       </c>
       <c r="AA50">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AB50">
         <v>3.01</v>
       </c>
       <c r="AC50">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AD50">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AE50">
         <v>1.33</v>
       </c>
       <c r="AF50">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AG50">
         <v>2.9</v>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK50">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,34 +8622,34 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="O51">
         <v>4.2</v>
       </c>
       <c r="P51">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="Q51">
         <v>1.95</v>
       </c>
       <c r="R51">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S51">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T51">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U51">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="V51">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="W51">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X51">
         <v>1.01</v>
@@ -8658,13 +8658,13 @@
         <v>1.11</v>
       </c>
       <c r="Z51">
-        <v>5.4</v>
+        <v>5.02</v>
       </c>
       <c r="AA51">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AB51">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AC51">
         <v>2.33</v>
@@ -8679,7 +8679,7 @@
         <v>1.6</v>
       </c>
       <c r="AG51">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AK51">
-        <v>2.43</v>
+        <v>2.37</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,34 +8785,34 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.21</v>
+        <v>2.12</v>
       </c>
       <c r="O52">
-        <v>4.24</v>
+        <v>3.83</v>
       </c>
       <c r="P52">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="Q52">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="R52">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S52">
         <v>1.22</v>
       </c>
       <c r="T52">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="U52">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="V52">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W52">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X52">
         <v>1.02</v>
@@ -8821,25 +8821,25 @@
         <v>1.13</v>
       </c>
       <c r="Z52">
-        <v>6.25</v>
+        <v>5.93</v>
       </c>
       <c r="AA52">
         <v>1.4</v>
       </c>
       <c r="AB52">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="AC52">
         <v>2.02</v>
       </c>
       <c r="AD52">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AE52">
         <v>1.3</v>
       </c>
       <c r="AF52">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG52">
         <v>2.75</v>
@@ -8858,7 +8858,7 @@
         <v>1.22</v>
       </c>
       <c r="AK52">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AL52">
         <v>0</v>

--- a/jogos_2026-08-19.xlsx
+++ b/jogos_2026-08-19.xlsx
@@ -3402,7 +3402,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N19">
@@ -3415,13 +3415,13 @@
         <v>4.5</v>
       </c>
       <c r="Q19">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="R19">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="S19">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="T19">
         <v>2.32</v>
@@ -3433,19 +3433,19 @@
         <v>1.25</v>
       </c>
       <c r="W19">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X19">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="Y19">
         <v>1.5</v>
       </c>
       <c r="Z19">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="AA19">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="AB19">
         <v>1.5</v>
@@ -3479,7 +3479,7 @@
         <v>1.27</v>
       </c>
       <c r="AK19">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,80 +7970,80 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.83</v>
+        <v>2.64</v>
       </c>
       <c r="O47">
-        <v>3.6</v>
+        <v>3.88</v>
       </c>
       <c r="P47">
-        <v>3.4</v>
+        <v>2.39</v>
       </c>
       <c r="Q47">
-        <v>2.15</v>
+        <v>3.2</v>
       </c>
       <c r="R47">
-        <v>2.57</v>
+        <v>2.33</v>
       </c>
       <c r="S47">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T47">
-        <v>3.65</v>
+        <v>3.28</v>
       </c>
       <c r="U47">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="V47">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="W47">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="X47">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y47">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="Z47">
-        <v>5.31</v>
+        <v>4.2</v>
       </c>
       <c r="AA47">
-        <v>1.46</v>
+        <v>1.66</v>
       </c>
       <c r="AB47">
-        <v>2.65</v>
+        <v>2.08</v>
       </c>
       <c r="AC47">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="AD47">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AE47">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AF47">
+        <v>1.5</v>
+      </c>
+      <c r="AG47">
+        <v>2.38</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ47">
+        <v>1.57</v>
+      </c>
+      <c r="AK47">
         <v>1.44</v>
-      </c>
-      <c r="AG47">
-        <v>2.55</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ47">
-        <v>1.2</v>
-      </c>
-      <c r="AK47">
-        <v>1.83</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.64</v>
+        <v>1.83</v>
       </c>
       <c r="O48">
-        <v>3.88</v>
+        <v>3.6</v>
       </c>
       <c r="P48">
-        <v>2.39</v>
+        <v>3.4</v>
       </c>
       <c r="Q48">
-        <v>3.2</v>
+        <v>2.15</v>
       </c>
       <c r="R48">
-        <v>2.33</v>
+        <v>2.57</v>
       </c>
       <c r="S48">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T48">
-        <v>3.28</v>
+        <v>3.65</v>
       </c>
       <c r="U48">
+        <v>2.2</v>
+      </c>
+      <c r="V48">
+        <v>1.6</v>
+      </c>
+      <c r="W48">
+        <v>1.13</v>
+      </c>
+      <c r="X48">
+        <v>1.03</v>
+      </c>
+      <c r="Y48">
+        <v>1.13</v>
+      </c>
+      <c r="Z48">
+        <v>5.31</v>
+      </c>
+      <c r="AA48">
+        <v>1.46</v>
+      </c>
+      <c r="AB48">
+        <v>2.65</v>
+      </c>
+      <c r="AC48">
         <v>2.3</v>
       </c>
-      <c r="V48">
-        <v>1.53</v>
-      </c>
-      <c r="W48">
-        <v>1.1</v>
-      </c>
-      <c r="X48">
-        <v>1.02</v>
-      </c>
-      <c r="Y48">
+      <c r="AD48">
+        <v>1.58</v>
+      </c>
+      <c r="AE48">
         <v>1.2</v>
       </c>
-      <c r="Z48">
-        <v>4.2</v>
-      </c>
-      <c r="AA48">
-        <v>1.66</v>
-      </c>
-      <c r="AB48">
-        <v>2.08</v>
-      </c>
-      <c r="AC48">
-        <v>2.63</v>
-      </c>
-      <c r="AD48">
+      <c r="AF48">
         <v>1.44</v>
       </c>
-      <c r="AE48">
-        <v>1.19</v>
-      </c>
-      <c r="AF48">
-        <v>1.5</v>
-      </c>
       <c r="AG48">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.57</v>
+        <v>1.2</v>
       </c>
       <c r="AK48">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AL48">
         <v>0</v>

--- a/jogos_2026-08-19.xlsx
+++ b/jogos_2026-08-19.xlsx
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.4</v>
+        <v>1.96</v>
       </c>
       <c r="O2">
-        <v>4.5</v>
+        <v>3.76</v>
       </c>
       <c r="P2">
-        <v>6.32</v>
+        <v>2.95</v>
       </c>
       <c r="Q2">
         <v>1.83</v>
       </c>
       <c r="R2">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S2">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T2">
         <v>3.68</v>
@@ -659,40 +659,40 @@
         <v>2.08</v>
       </c>
       <c r="V2">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="W2">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X2">
         <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z2">
-        <v>5.65</v>
+        <v>6</v>
       </c>
       <c r="AA2">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AB2">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AC2">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AD2">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AE2">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AF2">
         <v>1.56</v>
       </c>
       <c r="AG2">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AK2">
-        <v>2.74</v>
+        <v>2.17</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -970,55 +970,55 @@
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="O10">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="P10">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2111,7 +2111,7 @@
         <v>1.72</v>
       </c>
       <c r="Q11">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="R11">
         <v>1.85</v>
@@ -2123,7 +2123,7 @@
         <v>2.2</v>
       </c>
       <c r="U11">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="V11">
         <v>1.22</v>
@@ -2141,10 +2141,10 @@
         <v>2.2</v>
       </c>
       <c r="AA11">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="AB11">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AC11">
         <v>0</v>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.28</v>
+        <v>1.95</v>
       </c>
       <c r="AK11">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,25 +2265,25 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="O12">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="P12">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="R12">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="S12">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="T12">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="U12">
         <v>3.18</v>
@@ -2295,7 +2295,7 @@
         <v>1.01</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y12">
         <v>1.36</v>
@@ -2304,38 +2304,38 @@
         <v>2.7</v>
       </c>
       <c r="AA12">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AB12">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AC12">
-        <v>4.2</v>
+        <v>3.94</v>
       </c>
       <c r="AD12">
+        <v>1.17</v>
+      </c>
+      <c r="AE12">
+        <v>1.02</v>
+      </c>
+      <c r="AF12">
+        <v>2.88</v>
+      </c>
+      <c r="AG12">
+        <v>1.34</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12">
         <v>1.15</v>
-      </c>
-      <c r="AE12">
-        <v>1.01</v>
-      </c>
-      <c r="AF12">
-        <v>2.84</v>
-      </c>
-      <c r="AG12">
-        <v>1.36</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12">
-        <v>1.02</v>
       </c>
       <c r="AK12">
         <v>3.05</v>
@@ -2600,40 +2600,40 @@
         <v>4.46</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W14">
         <v>0</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC14">
         <v>0</v>
@@ -2645,10 +2645,10 @@
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3243,31 +3243,31 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="O18">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="P18">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="Q18">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="R18">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="S18">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T18">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="U18">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="V18">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W18">
         <v>1.11</v>
@@ -3276,31 +3276,31 @@
         <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z18">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA18">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AB18">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AC18">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AD18">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AE18">
         <v>1.16</v>
       </c>
       <c r="AF18">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="AG18">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK18">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AL18">
         <v>0</v>

--- a/jogos_2026-08-19.xlsx
+++ b/jogos_2026-08-19.xlsx
@@ -644,7 +644,7 @@
         <v>2.95</v>
       </c>
       <c r="Q2">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R2">
         <v>2.4</v>
@@ -659,7 +659,7 @@
         <v>2.08</v>
       </c>
       <c r="V2">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W2">
         <v>1.13</v>
@@ -686,7 +686,7 @@
         <v>1.67</v>
       </c>
       <c r="AE2">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AF2">
         <v>1.56</v>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK2">
         <v>2.17</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Q4">
         <v>3.8</v>
@@ -1124,25 +1124,25 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="O5">
         <v>3.4</v>
       </c>
       <c r="P5">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="Q5">
-        <v>2.37</v>
+        <v>2.31</v>
       </c>
       <c r="R5">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="S5">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T5">
-        <v>2.59</v>
+        <v>2.72</v>
       </c>
       <c r="U5">
         <v>3.05</v>
@@ -1157,19 +1157,19 @@
         <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z5">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="AA5">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AB5">
         <v>1.68</v>
       </c>
       <c r="AC5">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="AD5">
         <v>1.24</v>
@@ -1178,10 +1178,10 @@
         <v>1.04</v>
       </c>
       <c r="AF5">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AG5">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>3.95</v>
+        <v>4.26</v>
       </c>
       <c r="O13">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P13">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q13">
         <v>5.25</v>
       </c>
       <c r="R13">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="S13">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T13">
-        <v>2.66</v>
+        <v>2.85</v>
       </c>
       <c r="U13">
-        <v>2.99</v>
+        <v>3.04</v>
       </c>
       <c r="V13">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W13">
         <v>1.02</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y13">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z13">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="AA13">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AB13">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AC13">
-        <v>3.69</v>
+        <v>3.48</v>
       </c>
       <c r="AD13">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE13">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF13">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AG13">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.95</v>
+        <v>1.28</v>
       </c>
       <c r="AK13">
         <v>1.15</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="G20">
@@ -3578,55 +3578,55 @@
         <v>0</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,34 +3895,34 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="O22">
-        <v>3.91</v>
+        <v>4.1</v>
       </c>
       <c r="P22">
-        <v>5.5</v>
+        <v>4.85</v>
       </c>
       <c r="Q22">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R22">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="S22">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T22">
-        <v>2.96</v>
+        <v>3.3</v>
       </c>
       <c r="U22">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="V22">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W22">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X22">
         <v>1.02</v>
@@ -3931,28 +3931,28 @@
         <v>1.23</v>
       </c>
       <c r="Z22">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="AA22">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AB22">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC22">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="AD22">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE22">
         <v>1.12</v>
       </c>
       <c r="AF22">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AG22">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK22">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,25 +4058,25 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="O23">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="P23">
-        <v>3.8</v>
+        <v>4.35</v>
       </c>
       <c r="Q23">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="R23">
         <v>2.3</v>
       </c>
       <c r="S23">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T23">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U23">
         <v>2.45</v>
@@ -4085,10 +4085,10 @@
         <v>1.5</v>
       </c>
       <c r="W23">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X23">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y23">
         <v>1.2</v>
@@ -4097,16 +4097,16 @@
         <v>3.74</v>
       </c>
       <c r="AA23">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AB23">
-        <v>2.01</v>
+        <v>2.08</v>
       </c>
       <c r="AC23">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="AD23">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE23">
         <v>1.14</v>
@@ -4115,7 +4115,7 @@
         <v>1.73</v>
       </c>
       <c r="AG23">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4131,7 +4131,7 @@
         <v>1.22</v>
       </c>
       <c r="AK23">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4224,7 +4224,7 @@
         <v>2.5</v>
       </c>
       <c r="O24">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="P24">
         <v>2.4</v>
@@ -4233,46 +4233,46 @@
         <v>2.8</v>
       </c>
       <c r="R24">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="S24">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T24">
         <v>3.75</v>
       </c>
       <c r="U24">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="V24">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="W24">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X24">
         <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z24">
-        <v>5.75</v>
+        <v>6.26</v>
       </c>
       <c r="AA24">
         <v>1.43</v>
       </c>
       <c r="AB24">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AC24">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="AD24">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AE24">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AF24">
         <v>1.4</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
+        <v>1.2</v>
+      </c>
+      <c r="AK24">
         <v>1.5</v>
-      </c>
-      <c r="AK24">
-        <v>1.47</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O25">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="P25">
-        <v>2.77</v>
+        <v>2.95</v>
       </c>
       <c r="Q25">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="R25">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="S25">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T25">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="U25">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="V25">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W25">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X25">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y25">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z25">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AA25">
+        <v>1.88</v>
+      </c>
+      <c r="AB25">
         <v>1.9</v>
       </c>
-      <c r="AB25">
-        <v>1.75</v>
-      </c>
       <c r="AC25">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="AD25">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AE25">
         <v>1.08</v>
       </c>
       <c r="AF25">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG25">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4457,7 +4457,7 @@
         <v>1.33</v>
       </c>
       <c r="AK25">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="O26">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="P26">
-        <v>9.5</v>
+        <v>9.85</v>
       </c>
       <c r="Q26">
         <v>1.73</v>
@@ -4562,46 +4562,46 @@
         <v>2.45</v>
       </c>
       <c r="S26">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T26">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="U26">
-        <v>2.44</v>
+        <v>2.63</v>
       </c>
       <c r="V26">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W26">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X26">
         <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z26">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="AA26">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB26">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AC26">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="AD26">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE26">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF26">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AG26">
         <v>1.62</v>
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,25 +4873,25 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.71</v>
+        <v>2.55</v>
       </c>
       <c r="O28">
-        <v>3.46</v>
+        <v>3.6</v>
       </c>
       <c r="P28">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q28">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="R28">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="S28">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="T28">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="U28">
         <v>2.45</v>
@@ -4909,25 +4909,25 @@
         <v>1.16</v>
       </c>
       <c r="Z28">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AA28">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AB28">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="AC28">
         <v>2.56</v>
       </c>
       <c r="AD28">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE28">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF28">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AG28">
         <v>2.3</v>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.22</v>
+        <v>1.49</v>
       </c>
       <c r="AK28">
         <v>1.4</v>
@@ -5036,34 +5036,34 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="O29">
-        <v>3.17</v>
+        <v>3.5</v>
       </c>
       <c r="P29">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="Q29">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="R29">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="S29">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T29">
-        <v>2.65</v>
+        <v>2.79</v>
       </c>
       <c r="U29">
-        <v>3.18</v>
+        <v>2.9</v>
       </c>
       <c r="V29">
         <v>1.33</v>
       </c>
       <c r="W29">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X29">
         <v>1.06</v>
@@ -5072,10 +5072,10 @@
         <v>1.36</v>
       </c>
       <c r="Z29">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="AA29">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="AB29">
         <v>1.7</v>
@@ -5093,7 +5093,7 @@
         <v>2.15</v>
       </c>
       <c r="AG29">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AK29">
-        <v>2.21</v>
+        <v>2.07</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,43 +5199,43 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.94</v>
+        <v>2.6</v>
       </c>
       <c r="O30">
-        <v>3.25</v>
+        <v>2.85</v>
       </c>
       <c r="P30">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="Q30">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="R30">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S30">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T30">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="U30">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="V30">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W30">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X30">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y30">
         <v>1.4</v>
       </c>
       <c r="Z30">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="AA30">
         <v>2.15</v>
@@ -5244,19 +5244,19 @@
         <v>1.65</v>
       </c>
       <c r="AC30">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="AD30">
         <v>1.19</v>
       </c>
       <c r="AE30">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF30">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AG30">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="AK30">
         <v>1.4</v>
@@ -5365,10 +5365,10 @@
         <v>1.65</v>
       </c>
       <c r="O31">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P31">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="Q31">
         <v>2.05</v>
@@ -5377,25 +5377,25 @@
         <v>2.3</v>
       </c>
       <c r="S31">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="T31">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="U31">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="V31">
         <v>1.44</v>
       </c>
       <c r="W31">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X31">
         <v>1.04</v>
       </c>
       <c r="Y31">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z31">
         <v>3.75</v>
@@ -5404,22 +5404,22 @@
         <v>1.73</v>
       </c>
       <c r="AB31">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AC31">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="AD31">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AE31">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF31">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AG31">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AK31">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="O32">
         <v>3.5</v>
       </c>
       <c r="P32">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="Q32">
         <v>2.88</v>
       </c>
       <c r="R32">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="S32">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T32">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U32">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="V32">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="W32">
         <v>1.14</v>
       </c>
       <c r="X32">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z32">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AA32">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB32">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="AC32">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="AD32">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AE32">
         <v>1.2</v>
       </c>
       <c r="AF32">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AG32">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK32">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,65 +6014,65 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="O35">
-        <v>3.5</v>
+        <v>3.71</v>
       </c>
       <c r="P35">
-        <v>2.88</v>
+        <v>2.48</v>
       </c>
       <c r="Q35">
         <v>2.5</v>
       </c>
       <c r="R35">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S35">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="T35">
-        <v>3.23</v>
+        <v>4</v>
       </c>
       <c r="U35">
-        <v>2.65</v>
+        <v>2</v>
       </c>
       <c r="V35">
-        <v>1.46</v>
+        <v>1.71</v>
       </c>
       <c r="W35">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="X35">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="Z35">
-        <v>3.8</v>
+        <v>5.75</v>
       </c>
       <c r="AA35">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AB35">
-        <v>2.05</v>
+        <v>2.7</v>
       </c>
       <c r="AC35">
+        <v>2.08</v>
+      </c>
+      <c r="AD35">
+        <v>1.7</v>
+      </c>
+      <c r="AE35">
+        <v>1.26</v>
+      </c>
+      <c r="AF35">
+        <v>1.35</v>
+      </c>
+      <c r="AG35">
         <v>2.9</v>
       </c>
-      <c r="AD35">
-        <v>1.36</v>
-      </c>
-      <c r="AE35">
-        <v>1.13</v>
-      </c>
-      <c r="AF35">
-        <v>1.62</v>
-      </c>
-      <c r="AG35">
-        <v>2.2</v>
-      </c>
       <c r="AH35" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AK35">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Orlando City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.22</v>
+        <v>2.7</v>
       </c>
       <c r="O36">
-        <v>3.71</v>
+        <v>3.8</v>
       </c>
       <c r="P36">
-        <v>2.48</v>
+        <v>2.13</v>
       </c>
       <c r="Q36">
-        <v>2.5</v>
+        <v>2.89</v>
       </c>
       <c r="R36">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S36">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="T36">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="U36">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="V36">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="W36">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X36">
         <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z36">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="AA36">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB36">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="AC36">
-        <v>2.08</v>
+        <v>1.91</v>
       </c>
       <c r="AD36">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="AE36">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AF36">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AG36">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AK36">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Orlando City</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>2.7</v>
+        <v>1.92</v>
       </c>
       <c r="O37">
+        <v>3.7</v>
+      </c>
+      <c r="P37">
+        <v>3.1</v>
+      </c>
+      <c r="Q37">
+        <v>2.3</v>
+      </c>
+      <c r="R37">
+        <v>2.5</v>
+      </c>
+      <c r="S37">
+        <v>1.22</v>
+      </c>
+      <c r="T37">
         <v>3.8</v>
       </c>
-      <c r="P37">
-        <v>2.13</v>
-      </c>
-      <c r="Q37">
-        <v>2.89</v>
-      </c>
-      <c r="R37">
-        <v>2.45</v>
-      </c>
-      <c r="S37">
+      <c r="U37">
+        <v>2.08</v>
+      </c>
+      <c r="V37">
+        <v>1.67</v>
+      </c>
+      <c r="W37">
+        <v>1.18</v>
+      </c>
+      <c r="X37">
+        <v>1.02</v>
+      </c>
+      <c r="Y37">
         <v>1.14</v>
       </c>
-      <c r="T37">
-        <v>4.33</v>
-      </c>
-      <c r="U37">
-        <v>1.97</v>
-      </c>
-      <c r="V37">
-        <v>1.75</v>
-      </c>
-      <c r="W37">
-        <v>1.2</v>
-      </c>
-      <c r="X37">
-        <v>1.01</v>
-      </c>
-      <c r="Y37">
-        <v>1.1</v>
-      </c>
       <c r="Z37">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="AA37">
         <v>1.4</v>
       </c>
       <c r="AB37">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="AC37">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AD37">
-        <v>1.88</v>
+        <v>1.71</v>
       </c>
       <c r="AE37">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AF37">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AG37">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.63</v>
+        <v>1.2</v>
       </c>
       <c r="AK37">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,65 +6503,65 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.92</v>
+        <v>2.63</v>
       </c>
       <c r="O38">
-        <v>3.7</v>
+        <v>3.61</v>
       </c>
       <c r="P38">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q38">
+        <v>3.34</v>
+      </c>
+      <c r="R38">
+        <v>2.32</v>
+      </c>
+      <c r="S38">
+        <v>1.25</v>
+      </c>
+      <c r="T38">
+        <v>4</v>
+      </c>
+      <c r="U38">
+        <v>2.2</v>
+      </c>
+      <c r="V38">
+        <v>1.6</v>
+      </c>
+      <c r="W38">
+        <v>1.14</v>
+      </c>
+      <c r="X38">
+        <v>1.03</v>
+      </c>
+      <c r="Y38">
+        <v>1.17</v>
+      </c>
+      <c r="Z38">
+        <v>5.2</v>
+      </c>
+      <c r="AA38">
+        <v>1.53</v>
+      </c>
+      <c r="AB38">
+        <v>2.4</v>
+      </c>
+      <c r="AC38">
         <v>2.3</v>
       </c>
-      <c r="R38">
-        <v>2.5</v>
-      </c>
-      <c r="S38">
-        <v>1.22</v>
-      </c>
-      <c r="T38">
-        <v>3.8</v>
-      </c>
-      <c r="U38">
-        <v>2.08</v>
-      </c>
-      <c r="V38">
-        <v>1.67</v>
-      </c>
-      <c r="W38">
-        <v>1.18</v>
-      </c>
-      <c r="X38">
-        <v>1.02</v>
-      </c>
-      <c r="Y38">
-        <v>1.14</v>
-      </c>
-      <c r="Z38">
-        <v>5.7</v>
-      </c>
-      <c r="AA38">
-        <v>1.4</v>
-      </c>
-      <c r="AB38">
+      <c r="AD38">
+        <v>1.57</v>
+      </c>
+      <c r="AE38">
+        <v>1.24</v>
+      </c>
+      <c r="AF38">
+        <v>1.44</v>
+      </c>
+      <c r="AG38">
         <v>2.7</v>
       </c>
-      <c r="AC38">
-        <v>2.1</v>
-      </c>
-      <c r="AD38">
-        <v>1.71</v>
-      </c>
-      <c r="AE38">
-        <v>1.29</v>
-      </c>
-      <c r="AF38">
-        <v>1.4</v>
-      </c>
-      <c r="AG38">
-        <v>2.88</v>
-      </c>
       <c r="AH38" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AK38">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,65 +6666,65 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.63</v>
+        <v>2.12</v>
       </c>
       <c r="O39">
-        <v>3.61</v>
+        <v>3.5</v>
       </c>
       <c r="P39">
-        <v>2.15</v>
+        <v>2.88</v>
       </c>
       <c r="Q39">
-        <v>3.34</v>
+        <v>2.5</v>
       </c>
       <c r="R39">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="S39">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="T39">
-        <v>4</v>
+        <v>3.23</v>
       </c>
       <c r="U39">
+        <v>2.65</v>
+      </c>
+      <c r="V39">
+        <v>1.46</v>
+      </c>
+      <c r="W39">
+        <v>1.08</v>
+      </c>
+      <c r="X39">
+        <v>1.04</v>
+      </c>
+      <c r="Y39">
+        <v>1.22</v>
+      </c>
+      <c r="Z39">
+        <v>3.8</v>
+      </c>
+      <c r="AA39">
+        <v>1.75</v>
+      </c>
+      <c r="AB39">
+        <v>2.05</v>
+      </c>
+      <c r="AC39">
+        <v>2.9</v>
+      </c>
+      <c r="AD39">
+        <v>1.36</v>
+      </c>
+      <c r="AE39">
+        <v>1.13</v>
+      </c>
+      <c r="AF39">
+        <v>1.62</v>
+      </c>
+      <c r="AG39">
         <v>2.2</v>
       </c>
-      <c r="V39">
-        <v>1.6</v>
-      </c>
-      <c r="W39">
-        <v>1.14</v>
-      </c>
-      <c r="X39">
-        <v>1.03</v>
-      </c>
-      <c r="Y39">
-        <v>1.17</v>
-      </c>
-      <c r="Z39">
-        <v>5.2</v>
-      </c>
-      <c r="AA39">
-        <v>1.53</v>
-      </c>
-      <c r="AB39">
-        <v>2.4</v>
-      </c>
-      <c r="AC39">
-        <v>2.3</v>
-      </c>
-      <c r="AD39">
-        <v>1.57</v>
-      </c>
-      <c r="AE39">
-        <v>1.24</v>
-      </c>
-      <c r="AF39">
-        <v>1.44</v>
-      </c>
-      <c r="AG39">
-        <v>2.7</v>
-      </c>
       <c r="AH39" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK39">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,22 +6829,22 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="O40">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="P40">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="Q40">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="R40">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="S40">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="T40">
         <v>2.21</v>
@@ -6856,37 +6856,37 @@
         <v>1.21</v>
       </c>
       <c r="W40">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X40">
         <v>1.13</v>
       </c>
       <c r="Y40">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="Z40">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AA40">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="AB40">
         <v>1.44</v>
       </c>
       <c r="AC40">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AD40">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AE40">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF40">
         <v>2.15</v>
       </c>
       <c r="AG40">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AK40">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,22 +6992,22 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="O41">
         <v>4.5</v>
       </c>
       <c r="P41">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="Q41">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="R41">
-        <v>2.24</v>
+        <v>2.46</v>
       </c>
       <c r="S41">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T41">
         <v>2.9</v>
@@ -7019,37 +7019,37 @@
         <v>1.44</v>
       </c>
       <c r="W41">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X41">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y41">
         <v>1.29</v>
       </c>
       <c r="Z41">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AA41">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="AB41">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AC41">
-        <v>3.08</v>
+        <v>3.36</v>
       </c>
       <c r="AD41">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AE41">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF41">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AG41">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.06</v>
+        <v>1.2</v>
       </c>
       <c r="AK41">
-        <v>3.1</v>
+        <v>2.68</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7164,28 +7164,28 @@
         <v>4.37</v>
       </c>
       <c r="Q42">
-        <v>1.97</v>
+        <v>2.07</v>
       </c>
       <c r="R42">
-        <v>2.52</v>
+        <v>2.15</v>
       </c>
       <c r="S42">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T42">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="U42">
-        <v>1.82</v>
+        <v>2.31</v>
       </c>
       <c r="V42">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="W42">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="X42">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y42">
         <v>1.13</v>
@@ -7194,25 +7194,25 @@
         <v>4.5</v>
       </c>
       <c r="AA42">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AB42">
-        <v>2.42</v>
+        <v>2.18</v>
       </c>
       <c r="AC42">
-        <v>2.06</v>
+        <v>2.55</v>
       </c>
       <c r="AD42">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AE42">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AF42">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AG42">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK42">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7653,10 +7653,10 @@
         <v>2.66</v>
       </c>
       <c r="Q45">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="R45">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="S45">
         <v>1.5</v>
@@ -7665,7 +7665,7 @@
         <v>2.4</v>
       </c>
       <c r="U45">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="V45">
         <v>1.22</v>
@@ -7674,7 +7674,7 @@
         <v>1.02</v>
       </c>
       <c r="X45">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Y45">
         <v>1.52</v>
@@ -7689,10 +7689,10 @@
         <v>1.47</v>
       </c>
       <c r="AC45">
-        <v>4.8</v>
+        <v>5.36</v>
       </c>
       <c r="AD45">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AE45">
         <v>1.01</v>
@@ -7701,7 +7701,7 @@
         <v>2.05</v>
       </c>
       <c r="AG45">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AK45">
         <v>1.4</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,80 +7807,80 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.57</v>
+        <v>2.64</v>
       </c>
       <c r="O46">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="P46">
-        <v>4.33</v>
+        <v>2.39</v>
       </c>
       <c r="Q46">
-        <v>1.95</v>
+        <v>3.2</v>
       </c>
       <c r="R46">
-        <v>2.42</v>
+        <v>2.33</v>
       </c>
       <c r="S46">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T46">
-        <v>3.75</v>
+        <v>3.28</v>
       </c>
       <c r="U46">
         <v>2.3</v>
       </c>
       <c r="V46">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="W46">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X46">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y46">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z46">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="AA46">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AB46">
-        <v>2.33</v>
+        <v>2.08</v>
       </c>
       <c r="AC46">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="AD46">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AE46">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AF46">
+        <v>1.5</v>
+      </c>
+      <c r="AG46">
+        <v>2.38</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ46">
         <v>1.57</v>
       </c>
-      <c r="AG46">
-        <v>2.25</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ46">
-        <v>1.17</v>
-      </c>
       <c r="AK46">
-        <v>2.2</v>
+        <v>1.44</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.64</v>
+        <v>1.83</v>
       </c>
       <c r="O47">
-        <v>3.88</v>
+        <v>3.6</v>
       </c>
       <c r="P47">
-        <v>2.39</v>
+        <v>3.4</v>
       </c>
       <c r="Q47">
-        <v>3.2</v>
+        <v>2.15</v>
       </c>
       <c r="R47">
-        <v>2.33</v>
+        <v>2.57</v>
       </c>
       <c r="S47">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T47">
-        <v>3.28</v>
+        <v>3.65</v>
       </c>
       <c r="U47">
+        <v>2.2</v>
+      </c>
+      <c r="V47">
+        <v>1.6</v>
+      </c>
+      <c r="W47">
+        <v>1.13</v>
+      </c>
+      <c r="X47">
+        <v>1.03</v>
+      </c>
+      <c r="Y47">
+        <v>1.13</v>
+      </c>
+      <c r="Z47">
+        <v>5.31</v>
+      </c>
+      <c r="AA47">
+        <v>1.46</v>
+      </c>
+      <c r="AB47">
+        <v>2.65</v>
+      </c>
+      <c r="AC47">
         <v>2.3</v>
       </c>
-      <c r="V47">
-        <v>1.53</v>
-      </c>
-      <c r="W47">
-        <v>1.1</v>
-      </c>
-      <c r="X47">
-        <v>1.02</v>
-      </c>
-      <c r="Y47">
+      <c r="AD47">
+        <v>1.58</v>
+      </c>
+      <c r="AE47">
         <v>1.2</v>
       </c>
-      <c r="Z47">
-        <v>4.2</v>
-      </c>
-      <c r="AA47">
-        <v>1.66</v>
-      </c>
-      <c r="AB47">
-        <v>2.08</v>
-      </c>
-      <c r="AC47">
-        <v>2.63</v>
-      </c>
-      <c r="AD47">
+      <c r="AF47">
         <v>1.44</v>
       </c>
-      <c r="AE47">
-        <v>1.19</v>
-      </c>
-      <c r="AF47">
-        <v>1.5</v>
-      </c>
       <c r="AG47">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.57</v>
+        <v>1.2</v>
       </c>
       <c r="AK47">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="O48">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="P48">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="Q48">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="R48">
-        <v>2.57</v>
+        <v>2.42</v>
       </c>
       <c r="S48">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T48">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="U48">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="V48">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="W48">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X48">
         <v>1.03</v>
       </c>
       <c r="Y48">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z48">
-        <v>5.31</v>
+        <v>5.4</v>
       </c>
       <c r="AA48">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AB48">
-        <v>2.65</v>
+        <v>2.33</v>
       </c>
       <c r="AC48">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AD48">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="AE48">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF48">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AG48">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK48">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AL48">
         <v>0</v>

--- a/jogos_2026-08-19.xlsx
+++ b/jogos_2026-08-19.xlsx
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>14.7</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1652,10 +1652,10 @@
         <v>0</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AC8">
         <v>0</v>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Mes Shahr-e Babak</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sanat Naft</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,64 +1939,64 @@
         </is>
       </c>
       <c r="N10">
-        <v>2.5</v>
+        <v>4.99</v>
       </c>
       <c r="O10">
-        <v>2.5</v>
+        <v>3.04</v>
       </c>
       <c r="P10">
-        <v>3.1</v>
+        <v>1.72</v>
       </c>
       <c r="Q10">
-        <v>3.57</v>
+        <v>5.5</v>
       </c>
       <c r="R10">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="S10">
-        <v>1.76</v>
+        <v>1.57</v>
       </c>
       <c r="T10">
-        <v>1.94</v>
+        <v>2.2</v>
       </c>
       <c r="U10">
-        <v>4.75</v>
+        <v>3.65</v>
       </c>
       <c r="V10">
+        <v>1.22</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
         <v>1.12</v>
       </c>
-      <c r="W10">
-        <v>1.02</v>
-      </c>
-      <c r="X10">
-        <v>1.13</v>
-      </c>
       <c r="Y10">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="Z10">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="AA10">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="AB10">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AC10">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AD10">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AE10">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF10">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AG10">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="AK10">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mes Shahr-e Babak</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>4.99</v>
+        <v>1.3</v>
       </c>
       <c r="O11">
-        <v>3.04</v>
+        <v>4.2</v>
       </c>
       <c r="P11">
-        <v>1.72</v>
+        <v>10</v>
       </c>
       <c r="Q11">
-        <v>5.5</v>
+        <v>1.87</v>
       </c>
       <c r="R11">
-        <v>1.85</v>
+        <v>2.07</v>
       </c>
       <c r="S11">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="T11">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="U11">
-        <v>3.65</v>
+        <v>3.18</v>
       </c>
       <c r="V11">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X11">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="Z11">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="AA11">
-        <v>2.8</v>
+        <v>2.19</v>
       </c>
       <c r="AB11">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF11">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="AG11">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.95</v>
+        <v>1.15</v>
       </c>
       <c r="AK11">
-        <v>1.1</v>
+        <v>3.05</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Sanat Naft</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="O12">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="P12">
-        <v>10</v>
+        <v>3.1</v>
       </c>
       <c r="Q12">
-        <v>1.87</v>
+        <v>3.57</v>
       </c>
       <c r="R12">
-        <v>2.07</v>
+        <v>1.66</v>
       </c>
       <c r="S12">
-        <v>1.47</v>
+        <v>1.76</v>
       </c>
       <c r="T12">
-        <v>2.62</v>
+        <v>1.94</v>
       </c>
       <c r="U12">
-        <v>3.18</v>
+        <v>4.75</v>
       </c>
       <c r="V12">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="W12">
+        <v>1.02</v>
+      </c>
+      <c r="X12">
+        <v>1.13</v>
+      </c>
+      <c r="Y12">
+        <v>1.81</v>
+      </c>
+      <c r="Z12">
+        <v>1.89</v>
+      </c>
+      <c r="AA12">
+        <v>3.5</v>
+      </c>
+      <c r="AB12">
+        <v>1.22</v>
+      </c>
+      <c r="AC12">
+        <v>8</v>
+      </c>
+      <c r="AD12">
+        <v>1.02</v>
+      </c>
+      <c r="AE12">
         <v>1.01</v>
       </c>
-      <c r="X12">
-        <v>1.03</v>
-      </c>
-      <c r="Y12">
-        <v>1.36</v>
-      </c>
-      <c r="Z12">
-        <v>2.7</v>
-      </c>
-      <c r="AA12">
-        <v>2.19</v>
-      </c>
-      <c r="AB12">
-        <v>1.6</v>
-      </c>
-      <c r="AC12">
-        <v>3.94</v>
-      </c>
-      <c r="AD12">
-        <v>1.17</v>
-      </c>
-      <c r="AE12">
-        <v>1.02</v>
-      </c>
       <c r="AF12">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="AG12">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.15</v>
+        <v>1.4</v>
       </c>
       <c r="AK12">
-        <v>3.05</v>
+        <v>1.4</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -3421,28 +3421,28 @@
         <v>1.95</v>
       </c>
       <c r="S19">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="T19">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="U19">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="V19">
         <v>1.25</v>
       </c>
       <c r="W19">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X19">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Y19">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Z19">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="AA19">
         <v>2.63</v>
@@ -3457,10 +3457,10 @@
         <v>1.15</v>
       </c>
       <c r="AE19">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF19">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="AG19">
         <v>1.6</v>
@@ -3901,7 +3901,7 @@
         <v>4.1</v>
       </c>
       <c r="P22">
-        <v>4.85</v>
+        <v>5</v>
       </c>
       <c r="Q22">
         <v>2.02</v>
@@ -3910,19 +3910,19 @@
         <v>2.38</v>
       </c>
       <c r="S22">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T22">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U22">
         <v>2.36</v>
       </c>
       <c r="V22">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="W22">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X22">
         <v>1.02</v>
@@ -3937,22 +3937,22 @@
         <v>1.68</v>
       </c>
       <c r="AB22">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC22">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AD22">
         <v>1.41</v>
       </c>
       <c r="AE22">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF22">
         <v>1.76</v>
       </c>
       <c r="AG22">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -4058,19 +4058,19 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="O23">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="P23">
-        <v>4.35</v>
+        <v>4.8</v>
       </c>
       <c r="Q23">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="R23">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="S23">
         <v>1.3</v>
@@ -4079,7 +4079,7 @@
         <v>3.2</v>
       </c>
       <c r="U23">
-        <v>2.45</v>
+        <v>2.53</v>
       </c>
       <c r="V23">
         <v>1.5</v>
@@ -4088,34 +4088,34 @@
         <v>1.1</v>
       </c>
       <c r="X23">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y23">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z23">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="AA23">
         <v>1.77</v>
       </c>
       <c r="AB23">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AC23">
-        <v>2.83</v>
+        <v>2.76</v>
       </c>
       <c r="AD23">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE23">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF23">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AG23">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK23">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4224,7 +4224,7 @@
         <v>2.5</v>
       </c>
       <c r="O24">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="P24">
         <v>2.4</v>
@@ -4233,7 +4233,7 @@
         <v>2.8</v>
       </c>
       <c r="R24">
-        <v>2.43</v>
+        <v>2.55</v>
       </c>
       <c r="S24">
         <v>1.21</v>
@@ -4242,37 +4242,37 @@
         <v>3.75</v>
       </c>
       <c r="U24">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="V24">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="W24">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X24">
         <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z24">
-        <v>6.26</v>
+        <v>6.41</v>
       </c>
       <c r="AA24">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AB24">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AC24">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="AD24">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AE24">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AF24">
         <v>1.4</v>
@@ -4294,7 +4294,7 @@
         <v>1.2</v>
       </c>
       <c r="AK24">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,28 +4384,28 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="O25">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P25">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="Q25">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="R25">
         <v>2.25</v>
       </c>
       <c r="S25">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T25">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="U25">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="V25">
         <v>1.43</v>
@@ -4414,16 +4414,16 @@
         <v>1.06</v>
       </c>
       <c r="X25">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y25">
         <v>1.28</v>
       </c>
       <c r="Z25">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AA25">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AB25">
         <v>1.9</v>
@@ -4432,7 +4432,7 @@
         <v>3.25</v>
       </c>
       <c r="AD25">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE25">
         <v>1.08</v>
@@ -4441,7 +4441,7 @@
         <v>1.74</v>
       </c>
       <c r="AG25">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="O26">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="P26">
-        <v>9.85</v>
+        <v>9.5</v>
       </c>
       <c r="Q26">
         <v>1.73</v>
@@ -4562,13 +4562,13 @@
         <v>2.45</v>
       </c>
       <c r="S26">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T26">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="U26">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="V26">
         <v>1.48</v>
@@ -4583,16 +4583,16 @@
         <v>1.25</v>
       </c>
       <c r="Z26">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AA26">
         <v>1.75</v>
       </c>
       <c r="AB26">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AC26">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AD26">
         <v>1.36</v>
@@ -4601,10 +4601,10 @@
         <v>1.14</v>
       </c>
       <c r="AF26">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="AG26">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>1.06</v>
       </c>
       <c r="AK26">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,80 +5362,80 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.65</v>
+        <v>2.37</v>
       </c>
       <c r="O31">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P31">
-        <v>4.2</v>
+        <v>2.45</v>
       </c>
       <c r="Q31">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="R31">
+        <v>2.35</v>
+      </c>
+      <c r="S31">
+        <v>1.22</v>
+      </c>
+      <c r="T31">
+        <v>3.5</v>
+      </c>
+      <c r="U31">
+        <v>2.25</v>
+      </c>
+      <c r="V31">
+        <v>1.57</v>
+      </c>
+      <c r="W31">
+        <v>1.14</v>
+      </c>
+      <c r="X31">
+        <v>1.01</v>
+      </c>
+      <c r="Y31">
+        <v>1.13</v>
+      </c>
+      <c r="Z31">
+        <v>4.8</v>
+      </c>
+      <c r="AA31">
+        <v>1.57</v>
+      </c>
+      <c r="AB31">
+        <v>2.36</v>
+      </c>
+      <c r="AC31">
+        <v>2.42</v>
+      </c>
+      <c r="AD31">
+        <v>1.51</v>
+      </c>
+      <c r="AE31">
+        <v>1.2</v>
+      </c>
+      <c r="AF31">
+        <v>1.5</v>
+      </c>
+      <c r="AG31">
         <v>2.3</v>
       </c>
-      <c r="S31">
-        <v>1.29</v>
-      </c>
-      <c r="T31">
-        <v>3.1</v>
-      </c>
-      <c r="U31">
-        <v>2.45</v>
-      </c>
-      <c r="V31">
-        <v>1.44</v>
-      </c>
-      <c r="W31">
-        <v>1.09</v>
-      </c>
-      <c r="X31">
-        <v>1.04</v>
-      </c>
-      <c r="Y31">
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31">
         <v>1.2</v>
       </c>
-      <c r="Z31">
-        <v>3.75</v>
-      </c>
-      <c r="AA31">
-        <v>1.73</v>
-      </c>
-      <c r="AB31">
-        <v>2.07</v>
-      </c>
-      <c r="AC31">
-        <v>2.81</v>
-      </c>
-      <c r="AD31">
-        <v>1.39</v>
-      </c>
-      <c r="AE31">
-        <v>1.11</v>
-      </c>
-      <c r="AF31">
-        <v>1.69</v>
-      </c>
-      <c r="AG31">
-        <v>2</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ31">
-        <v>1.14</v>
-      </c>
       <c r="AK31">
-        <v>2.06</v>
+        <v>1.48</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,80 +5525,80 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.37</v>
+        <v>1.65</v>
       </c>
       <c r="O32">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P32">
+        <v>4.2</v>
+      </c>
+      <c r="Q32">
+        <v>2.05</v>
+      </c>
+      <c r="R32">
+        <v>2.3</v>
+      </c>
+      <c r="S32">
+        <v>1.29</v>
+      </c>
+      <c r="T32">
+        <v>3.1</v>
+      </c>
+      <c r="U32">
         <v>2.45</v>
       </c>
-      <c r="Q32">
-        <v>2.88</v>
-      </c>
-      <c r="R32">
-        <v>2.35</v>
-      </c>
-      <c r="S32">
-        <v>1.22</v>
-      </c>
-      <c r="T32">
-        <v>3.5</v>
-      </c>
-      <c r="U32">
-        <v>2.25</v>
-      </c>
       <c r="V32">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="W32">
+        <v>1.09</v>
+      </c>
+      <c r="X32">
+        <v>1.04</v>
+      </c>
+      <c r="Y32">
+        <v>1.2</v>
+      </c>
+      <c r="Z32">
+        <v>3.75</v>
+      </c>
+      <c r="AA32">
+        <v>1.73</v>
+      </c>
+      <c r="AB32">
+        <v>2.07</v>
+      </c>
+      <c r="AC32">
+        <v>2.81</v>
+      </c>
+      <c r="AD32">
+        <v>1.39</v>
+      </c>
+      <c r="AE32">
+        <v>1.11</v>
+      </c>
+      <c r="AF32">
+        <v>1.69</v>
+      </c>
+      <c r="AG32">
+        <v>2</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ32">
         <v>1.14</v>
       </c>
-      <c r="X32">
-        <v>1.01</v>
-      </c>
-      <c r="Y32">
-        <v>1.13</v>
-      </c>
-      <c r="Z32">
-        <v>4.8</v>
-      </c>
-      <c r="AA32">
-        <v>1.57</v>
-      </c>
-      <c r="AB32">
-        <v>2.36</v>
-      </c>
-      <c r="AC32">
-        <v>2.42</v>
-      </c>
-      <c r="AD32">
-        <v>1.51</v>
-      </c>
-      <c r="AE32">
-        <v>1.2</v>
-      </c>
-      <c r="AF32">
-        <v>1.5</v>
-      </c>
-      <c r="AG32">
-        <v>2.3</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ32">
-        <v>1.2</v>
-      </c>
       <c r="AK32">
-        <v>1.48</v>
+        <v>2.06</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,58 +5688,58 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="O33">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="P33">
-        <v>5.15</v>
+        <v>4.6</v>
       </c>
       <c r="Q33">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="R33">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="S33">
         <v>1.25</v>
       </c>
       <c r="T33">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="U33">
         <v>2.25</v>
       </c>
       <c r="V33">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W33">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X33">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z33">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AA33">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB33">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="AC33">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="AD33">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="AE33">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AF33">
         <v>1.6</v>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AK33">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="O34">
-        <v>3.92</v>
+        <v>3.5</v>
       </c>
       <c r="P34">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="Q34">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="R34">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="S34">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T34">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U34">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="V34">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="W34">
         <v>1.11</v>
       </c>
       <c r="X34">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y34">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z34">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA34">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB34">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AC34">
-        <v>2.51</v>
+        <v>2.8</v>
       </c>
       <c r="AD34">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE34">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AF34">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="AG34">
-        <v>2.48</v>
+        <v>2.25</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK34">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6014,22 +6014,22 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.22</v>
+        <v>2.37</v>
       </c>
       <c r="O35">
-        <v>3.71</v>
+        <v>4.24</v>
       </c>
       <c r="P35">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="Q35">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="R35">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="S35">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T35">
         <v>4</v>
@@ -6038,40 +6038,40 @@
         <v>2</v>
       </c>
       <c r="V35">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="W35">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X35">
         <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z35">
-        <v>5.75</v>
+        <v>5.55</v>
       </c>
       <c r="AA35">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB35">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="AC35">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AD35">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AE35">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AF35">
         <v>1.35</v>
       </c>
       <c r="AG35">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
+        <v>1.21</v>
+      </c>
+      <c r="AK35">
         <v>1.5</v>
-      </c>
-      <c r="AK35">
-        <v>1.53</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,34 +6177,34 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="O36">
         <v>3.8</v>
       </c>
       <c r="P36">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="Q36">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="R36">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S36">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="T36">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="U36">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="V36">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="W36">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X36">
         <v>1.01</v>
@@ -6213,28 +6213,28 @@
         <v>1.1</v>
       </c>
       <c r="Z36">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="AA36">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AB36">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="AC36">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AD36">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AE36">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AF36">
         <v>1.3</v>
       </c>
       <c r="AG36">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.63</v>
+        <v>1.24</v>
       </c>
       <c r="AK36">
         <v>1.4</v>
@@ -6340,46 +6340,46 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="O37">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="P37">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="Q37">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="R37">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="S37">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="T37">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="U37">
-        <v>2.08</v>
+        <v>2.01</v>
       </c>
       <c r="V37">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W37">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X37">
         <v>1.02</v>
       </c>
       <c r="Y37">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z37">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AA37">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB37">
         <v>2.7</v>
@@ -6391,13 +6391,13 @@
         <v>1.71</v>
       </c>
       <c r="AE37">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AF37">
         <v>1.4</v>
       </c>
       <c r="AG37">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>1.2</v>
       </c>
       <c r="AK37">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,80 +6503,80 @@
         </is>
       </c>
       <c r="N38">
+        <v>2.15</v>
+      </c>
+      <c r="O38">
+        <v>3.5</v>
+      </c>
+      <c r="P38">
+        <v>2.9</v>
+      </c>
+      <c r="Q38">
         <v>2.63</v>
       </c>
-      <c r="O38">
-        <v>3.61</v>
-      </c>
-      <c r="P38">
-        <v>2.15</v>
-      </c>
-      <c r="Q38">
-        <v>3.34</v>
-      </c>
       <c r="R38">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="S38">
+        <v>1.3</v>
+      </c>
+      <c r="T38">
+        <v>3.05</v>
+      </c>
+      <c r="U38">
+        <v>2.46</v>
+      </c>
+      <c r="V38">
+        <v>1.46</v>
+      </c>
+      <c r="W38">
+        <v>1.08</v>
+      </c>
+      <c r="X38">
+        <v>1.04</v>
+      </c>
+      <c r="Y38">
+        <v>1.26</v>
+      </c>
+      <c r="Z38">
+        <v>4</v>
+      </c>
+      <c r="AA38">
+        <v>1.7</v>
+      </c>
+      <c r="AB38">
+        <v>2.1</v>
+      </c>
+      <c r="AC38">
+        <v>2.8</v>
+      </c>
+      <c r="AD38">
+        <v>1.42</v>
+      </c>
+      <c r="AE38">
+        <v>1.11</v>
+      </c>
+      <c r="AF38">
+        <v>1.61</v>
+      </c>
+      <c r="AG38">
+        <v>2.2</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38">
         <v>1.25</v>
       </c>
-      <c r="T38">
-        <v>4</v>
-      </c>
-      <c r="U38">
-        <v>2.2</v>
-      </c>
-      <c r="V38">
-        <v>1.6</v>
-      </c>
-      <c r="W38">
-        <v>1.14</v>
-      </c>
-      <c r="X38">
-        <v>1.03</v>
-      </c>
-      <c r="Y38">
-        <v>1.17</v>
-      </c>
-      <c r="Z38">
-        <v>5.2</v>
-      </c>
-      <c r="AA38">
-        <v>1.53</v>
-      </c>
-      <c r="AB38">
-        <v>2.4</v>
-      </c>
-      <c r="AC38">
-        <v>2.3</v>
-      </c>
-      <c r="AD38">
-        <v>1.57</v>
-      </c>
-      <c r="AE38">
-        <v>1.24</v>
-      </c>
-      <c r="AF38">
-        <v>1.44</v>
-      </c>
-      <c r="AG38">
-        <v>2.7</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ38">
-        <v>1.23</v>
-      </c>
       <c r="AK38">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.12</v>
+        <v>2.62</v>
       </c>
       <c r="O39">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="P39">
-        <v>2.88</v>
+        <v>2.23</v>
       </c>
       <c r="Q39">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="R39">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="S39">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="T39">
-        <v>3.23</v>
+        <v>4</v>
       </c>
       <c r="U39">
-        <v>2.65</v>
+        <v>2.2</v>
       </c>
       <c r="V39">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="W39">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X39">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y39">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="Z39">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="AA39">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AB39">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="AC39">
-        <v>2.9</v>
+        <v>2.31</v>
       </c>
       <c r="AD39">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="AE39">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AF39">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AG39">
-        <v>2.2</v>
+        <v>2.53</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7318,22 +7318,22 @@
         </is>
       </c>
       <c r="N43">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="O43">
         <v>3.6</v>
       </c>
       <c r="P43">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="Q43">
-        <v>3.36</v>
+        <v>3.54</v>
       </c>
       <c r="R43">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="S43">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T43">
         <v>3.8</v>
@@ -7345,28 +7345,28 @@
         <v>1.65</v>
       </c>
       <c r="W43">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X43">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z43">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AA43">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AB43">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AC43">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AD43">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AE43">
         <v>1.22</v>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK43">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,19 +7481,19 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="O44">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P44">
         <v>3.8</v>
       </c>
       <c r="Q44">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="R44">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="S44">
         <v>1.3</v>
@@ -7502,40 +7502,40 @@
         <v>3.3</v>
       </c>
       <c r="U44">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="V44">
         <v>1.5</v>
       </c>
       <c r="W44">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X44">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y44">
         <v>1.17</v>
       </c>
       <c r="Z44">
-        <v>4.15</v>
+        <v>4.05</v>
       </c>
       <c r="AA44">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB44">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="AC44">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="AD44">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AE44">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF44">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AG44">
         <v>2.1</v>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK44">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.64</v>
+        <v>2.73</v>
       </c>
       <c r="O46">
-        <v>3.88</v>
+        <v>3.4</v>
       </c>
       <c r="P46">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="Q46">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R46">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="S46">
         <v>1.3</v>
       </c>
       <c r="T46">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="U46">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="V46">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="W46">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X46">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y46">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z46">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AA46">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AB46">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AC46">
-        <v>2.63</v>
+        <v>2.7</v>
       </c>
       <c r="AD46">
         <v>1.44</v>
       </c>
       <c r="AE46">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AF46">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AG46">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.57</v>
+        <v>1.24</v>
       </c>
       <c r="AK46">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7970,19 +7970,19 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="O47">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P47">
         <v>3.4</v>
       </c>
       <c r="Q47">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="R47">
-        <v>2.57</v>
+        <v>2.36</v>
       </c>
       <c r="S47">
         <v>1.22</v>
@@ -7991,10 +7991,10 @@
         <v>3.65</v>
       </c>
       <c r="U47">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="V47">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="W47">
         <v>1.13</v>
@@ -8006,7 +8006,7 @@
         <v>1.13</v>
       </c>
       <c r="Z47">
-        <v>5.31</v>
+        <v>5.5</v>
       </c>
       <c r="AA47">
         <v>1.46</v>
@@ -8015,19 +8015,19 @@
         <v>2.65</v>
       </c>
       <c r="AC47">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AD47">
         <v>1.58</v>
       </c>
       <c r="AE47">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF47">
         <v>1.44</v>
       </c>
       <c r="AG47">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
+        <v>1.65</v>
+      </c>
+      <c r="O48">
+        <v>3.8</v>
+      </c>
+      <c r="P48">
+        <v>4.53</v>
+      </c>
+      <c r="Q48">
+        <v>2.05</v>
+      </c>
+      <c r="R48">
+        <v>2.4</v>
+      </c>
+      <c r="S48">
+        <v>1.22</v>
+      </c>
+      <c r="T48">
+        <v>3.34</v>
+      </c>
+      <c r="U48">
+        <v>2.25</v>
+      </c>
+      <c r="V48">
         <v>1.57</v>
       </c>
-      <c r="O48">
-        <v>4</v>
-      </c>
-      <c r="P48">
-        <v>4.33</v>
-      </c>
-      <c r="Q48">
-        <v>1.95</v>
-      </c>
-      <c r="R48">
-        <v>2.42</v>
-      </c>
-      <c r="S48">
-        <v>1.25</v>
-      </c>
-      <c r="T48">
-        <v>3.75</v>
-      </c>
-      <c r="U48">
-        <v>2.3</v>
-      </c>
-      <c r="V48">
+      <c r="W48">
+        <v>1.11</v>
+      </c>
+      <c r="X48">
+        <v>1.04</v>
+      </c>
+      <c r="Y48">
+        <v>1.15</v>
+      </c>
+      <c r="Z48">
+        <v>5</v>
+      </c>
+      <c r="AA48">
         <v>1.55</v>
       </c>
-      <c r="W48">
-        <v>1.14</v>
-      </c>
-      <c r="X48">
-        <v>1.03</v>
-      </c>
-      <c r="Y48">
-        <v>1.14</v>
-      </c>
-      <c r="Z48">
-        <v>5.4</v>
-      </c>
-      <c r="AA48">
+      <c r="AB48">
+        <v>2.45</v>
+      </c>
+      <c r="AC48">
+        <v>2.48</v>
+      </c>
+      <c r="AD48">
         <v>1.53</v>
       </c>
-      <c r="AB48">
-        <v>2.33</v>
-      </c>
-      <c r="AC48">
-        <v>2.25</v>
-      </c>
-      <c r="AD48">
-        <v>1.52</v>
-      </c>
       <c r="AE48">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF48">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG48">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK48">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="O49">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P49">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="Q49">
         <v>2.95</v>
       </c>
       <c r="R49">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="S49">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="T49">
         <v>3.2</v>
       </c>
       <c r="U49">
-        <v>2.76</v>
+        <v>2.63</v>
       </c>
       <c r="V49">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W49">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X49">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="Z49">
-        <v>3.65</v>
+        <v>3.42</v>
       </c>
       <c r="AA49">
         <v>1.87</v>
       </c>
       <c r="AB49">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AC49">
         <v>3.1</v>
       </c>
       <c r="AD49">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AE49">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AF49">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="AG49">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O50">
-        <v>3.93</v>
+        <v>4</v>
       </c>
       <c r="P50">
-        <v>2.87</v>
+        <v>2.71</v>
       </c>
       <c r="Q50">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R50">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="S50">
         <v>1.2</v>
       </c>
       <c r="T50">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="U50">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="V50">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="W50">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X50">
         <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z50">
-        <v>6.56</v>
+        <v>6.5</v>
       </c>
       <c r="AA50">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AB50">
-        <v>3.01</v>
+        <v>2.88</v>
       </c>
       <c r="AC50">
         <v>1.95</v>
       </c>
       <c r="AD50">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AE50">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AF50">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AG50">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AK50">
         <v>1.72</v>
@@ -8622,31 +8622,31 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="O51">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="P51">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Q51">
         <v>1.95</v>
       </c>
       <c r="R51">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="S51">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T51">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U51">
-        <v>2.23</v>
+        <v>2.15</v>
       </c>
       <c r="V51">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W51">
         <v>1.13</v>
@@ -8655,16 +8655,16 @@
         <v>1.01</v>
       </c>
       <c r="Y51">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="Z51">
-        <v>5.02</v>
+        <v>5.25</v>
       </c>
       <c r="AA51">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AB51">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AC51">
         <v>2.33</v>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AK51">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,19 +8785,19 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="O52">
-        <v>3.83</v>
+        <v>3.6</v>
       </c>
       <c r="P52">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="Q52">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="R52">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="S52">
         <v>1.22</v>
@@ -8806,13 +8806,13 @@
         <v>3.95</v>
       </c>
       <c r="U52">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="V52">
         <v>1.68</v>
       </c>
       <c r="W52">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="X52">
         <v>1.02</v>
@@ -8821,28 +8821,28 @@
         <v>1.13</v>
       </c>
       <c r="Z52">
-        <v>5.93</v>
+        <v>6</v>
       </c>
       <c r="AA52">
+        <v>1.41</v>
+      </c>
+      <c r="AB52">
+        <v>2.9</v>
+      </c>
+      <c r="AC52">
+        <v>2.12</v>
+      </c>
+      <c r="AD52">
+        <v>1.75</v>
+      </c>
+      <c r="AE52">
+        <v>1.33</v>
+      </c>
+      <c r="AF52">
         <v>1.4</v>
       </c>
-      <c r="AB52">
-        <v>2.75</v>
-      </c>
-      <c r="AC52">
-        <v>2.02</v>
-      </c>
-      <c r="AD52">
-        <v>1.7</v>
-      </c>
-      <c r="AE52">
-        <v>1.3</v>
-      </c>
-      <c r="AF52">
-        <v>1.36</v>
-      </c>
       <c r="AG52">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AK52">
         <v>1.57</v>

--- a/jogos_2026-08-19.xlsx
+++ b/jogos_2026-08-19.xlsx
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.58</v>
+        <v>2.72</v>
       </c>
       <c r="O29">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P29">
-        <v>4.9</v>
+        <v>2.5</v>
       </c>
       <c r="Q29">
-        <v>2.12</v>
+        <v>3.25</v>
       </c>
       <c r="R29">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="S29">
         <v>1.42</v>
       </c>
       <c r="T29">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="U29">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="V29">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W29">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X29">
         <v>1.06</v>
       </c>
       <c r="Y29">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z29">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AA29">
         <v>2.15</v>
       </c>
       <c r="AB29">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AC29">
-        <v>4</v>
+        <v>3.82</v>
       </c>
       <c r="AD29">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE29">
         <v>1.06</v>
       </c>
       <c r="AF29">
-        <v>2.15</v>
+        <v>1.77</v>
       </c>
       <c r="AG29">
-        <v>1.68</v>
+        <v>1.91</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK29">
-        <v>2.07</v>
+        <v>1.44</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.6</v>
+        <v>1.57</v>
       </c>
       <c r="O30">
-        <v>2.85</v>
+        <v>3.5</v>
       </c>
       <c r="P30">
-        <v>2.5</v>
+        <v>6.35</v>
       </c>
       <c r="Q30">
-        <v>3.35</v>
+        <v>2.2</v>
       </c>
       <c r="R30">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="S30">
         <v>1.42</v>
       </c>
       <c r="T30">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="U30">
         <v>2.9</v>
       </c>
       <c r="V30">
+        <v>1.34</v>
+      </c>
+      <c r="W30">
+        <v>1.05</v>
+      </c>
+      <c r="X30">
+        <v>1.03</v>
+      </c>
+      <c r="Y30">
         <v>1.36</v>
       </c>
-      <c r="W30">
-        <v>1.06</v>
-      </c>
-      <c r="X30">
-        <v>1.06</v>
-      </c>
-      <c r="Y30">
-        <v>1.4</v>
-      </c>
       <c r="Z30">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AA30">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="AB30">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AC30">
-        <v>4.33</v>
+        <v>3.85</v>
       </c>
       <c r="AD30">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE30">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF30">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="AG30">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK30">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,80 +5362,80 @@
         </is>
       </c>
       <c r="N31">
-        <v>2.37</v>
+        <v>1.65</v>
       </c>
       <c r="O31">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P31">
+        <v>4.2</v>
+      </c>
+      <c r="Q31">
+        <v>2.05</v>
+      </c>
+      <c r="R31">
+        <v>2.3</v>
+      </c>
+      <c r="S31">
+        <v>1.29</v>
+      </c>
+      <c r="T31">
+        <v>3.1</v>
+      </c>
+      <c r="U31">
         <v>2.45</v>
       </c>
-      <c r="Q31">
-        <v>2.88</v>
-      </c>
-      <c r="R31">
-        <v>2.35</v>
-      </c>
-      <c r="S31">
-        <v>1.22</v>
-      </c>
-      <c r="T31">
-        <v>3.5</v>
-      </c>
-      <c r="U31">
-        <v>2.25</v>
-      </c>
       <c r="V31">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="W31">
+        <v>1.09</v>
+      </c>
+      <c r="X31">
+        <v>1.04</v>
+      </c>
+      <c r="Y31">
+        <v>1.2</v>
+      </c>
+      <c r="Z31">
+        <v>3.75</v>
+      </c>
+      <c r="AA31">
+        <v>1.73</v>
+      </c>
+      <c r="AB31">
+        <v>2.07</v>
+      </c>
+      <c r="AC31">
+        <v>2.81</v>
+      </c>
+      <c r="AD31">
+        <v>1.39</v>
+      </c>
+      <c r="AE31">
+        <v>1.11</v>
+      </c>
+      <c r="AF31">
+        <v>1.69</v>
+      </c>
+      <c r="AG31">
+        <v>2</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31">
         <v>1.14</v>
       </c>
-      <c r="X31">
-        <v>1.01</v>
-      </c>
-      <c r="Y31">
-        <v>1.13</v>
-      </c>
-      <c r="Z31">
-        <v>4.8</v>
-      </c>
-      <c r="AA31">
-        <v>1.57</v>
-      </c>
-      <c r="AB31">
-        <v>2.36</v>
-      </c>
-      <c r="AC31">
-        <v>2.42</v>
-      </c>
-      <c r="AD31">
-        <v>1.51</v>
-      </c>
-      <c r="AE31">
-        <v>1.2</v>
-      </c>
-      <c r="AF31">
-        <v>1.5</v>
-      </c>
-      <c r="AG31">
-        <v>2.3</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ31">
-        <v>1.2</v>
-      </c>
       <c r="AK31">
-        <v>1.48</v>
+        <v>2.06</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,80 +5525,80 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.65</v>
+        <v>2.37</v>
       </c>
       <c r="O32">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P32">
-        <v>4.2</v>
+        <v>2.45</v>
       </c>
       <c r="Q32">
-        <v>2.05</v>
+        <v>2.88</v>
       </c>
       <c r="R32">
+        <v>2.35</v>
+      </c>
+      <c r="S32">
+        <v>1.22</v>
+      </c>
+      <c r="T32">
+        <v>3.5</v>
+      </c>
+      <c r="U32">
+        <v>2.25</v>
+      </c>
+      <c r="V32">
+        <v>1.57</v>
+      </c>
+      <c r="W32">
+        <v>1.14</v>
+      </c>
+      <c r="X32">
+        <v>1.01</v>
+      </c>
+      <c r="Y32">
+        <v>1.13</v>
+      </c>
+      <c r="Z32">
+        <v>4.8</v>
+      </c>
+      <c r="AA32">
+        <v>1.57</v>
+      </c>
+      <c r="AB32">
+        <v>2.36</v>
+      </c>
+      <c r="AC32">
+        <v>2.42</v>
+      </c>
+      <c r="AD32">
+        <v>1.51</v>
+      </c>
+      <c r="AE32">
+        <v>1.2</v>
+      </c>
+      <c r="AF32">
+        <v>1.5</v>
+      </c>
+      <c r="AG32">
         <v>2.3</v>
       </c>
-      <c r="S32">
-        <v>1.29</v>
-      </c>
-      <c r="T32">
-        <v>3.1</v>
-      </c>
-      <c r="U32">
-        <v>2.45</v>
-      </c>
-      <c r="V32">
-        <v>1.44</v>
-      </c>
-      <c r="W32">
-        <v>1.09</v>
-      </c>
-      <c r="X32">
-        <v>1.04</v>
-      </c>
-      <c r="Y32">
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ32">
         <v>1.2</v>
       </c>
-      <c r="Z32">
-        <v>3.75</v>
-      </c>
-      <c r="AA32">
-        <v>1.73</v>
-      </c>
-      <c r="AB32">
-        <v>2.07</v>
-      </c>
-      <c r="AC32">
-        <v>2.81</v>
-      </c>
-      <c r="AD32">
-        <v>1.39</v>
-      </c>
-      <c r="AE32">
-        <v>1.11</v>
-      </c>
-      <c r="AF32">
-        <v>1.69</v>
-      </c>
-      <c r="AG32">
-        <v>2</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ32">
-        <v>1.14</v>
-      </c>
       <c r="AK32">
-        <v>2.06</v>
+        <v>1.48</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -6829,25 +6829,25 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="O40">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="P40">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="Q40">
-        <v>2.98</v>
+        <v>2.93</v>
       </c>
       <c r="R40">
         <v>1.94</v>
       </c>
       <c r="S40">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="T40">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="U40">
         <v>3.68</v>
@@ -6859,31 +6859,31 @@
         <v>1.04</v>
       </c>
       <c r="X40">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="Y40">
         <v>1.57</v>
       </c>
       <c r="Z40">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AA40">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AB40">
         <v>1.44</v>
       </c>
       <c r="AC40">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AD40">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AE40">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF40">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AG40">
         <v>1.6</v>
@@ -7001,13 +7001,13 @@
         <v>7</v>
       </c>
       <c r="Q41">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="R41">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="S41">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T41">
         <v>2.9</v>
@@ -7019,16 +7019,16 @@
         <v>1.44</v>
       </c>
       <c r="W41">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X41">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y41">
         <v>1.29</v>
       </c>
       <c r="Z41">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AA41">
         <v>1.99</v>
@@ -7043,10 +7043,10 @@
         <v>1.32</v>
       </c>
       <c r="AE41">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF41">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AG41">
         <v>1.62</v>
@@ -7065,7 +7065,7 @@
         <v>1.2</v>
       </c>
       <c r="AK41">
-        <v>2.68</v>
+        <v>3</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7674,31 +7674,31 @@
         <v>1.02</v>
       </c>
       <c r="X45">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y45">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="Z45">
-        <v>2.31</v>
+        <v>2.55</v>
       </c>
       <c r="AA45">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="AB45">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AC45">
-        <v>5.36</v>
+        <v>4.9</v>
       </c>
       <c r="AD45">
         <v>1.15</v>
       </c>
       <c r="AE45">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF45">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AG45">
         <v>1.7</v>
@@ -7717,7 +7717,7 @@
         <v>1.4</v>
       </c>
       <c r="AK45">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AL45">
         <v>0</v>

--- a/jogos_2026-08-19.xlsx
+++ b/jogos_2026-08-19.xlsx
@@ -1127,10 +1127,10 @@
         <v>1.79</v>
       </c>
       <c r="O5">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P5">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="Q5">
         <v>2.31</v>
@@ -1142,7 +1142,7 @@
         <v>1.44</v>
       </c>
       <c r="T5">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="U5">
         <v>3.05</v>
@@ -1163,16 +1163,16 @@
         <v>2.78</v>
       </c>
       <c r="AA5">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AB5">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AC5">
         <v>3.7</v>
       </c>
       <c r="AD5">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE5">
         <v>1.04</v>
@@ -1181,7 +1181,7 @@
         <v>1.95</v>
       </c>
       <c r="AG5">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK5">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,19 +1287,19 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="O6">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P6">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="Q6">
         <v>2.34</v>
       </c>
       <c r="R6">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="S6">
         <v>1.45</v>
@@ -1320,10 +1320,10 @@
         <v>1.05</v>
       </c>
       <c r="Y6">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="Z6">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="AA6">
         <v>2.3</v>
@@ -1341,10 +1341,10 @@
         <v>1.03</v>
       </c>
       <c r="AF6">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AG6">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="O7">
         <v>2.9</v>
       </c>
       <c r="P7">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="Q7">
         <v>2.72</v>
@@ -1504,7 +1504,7 @@
         <v>1.01</v>
       </c>
       <c r="AF7">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AG7">
         <v>1.6</v>
@@ -2102,28 +2102,28 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="O11">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="P11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q11">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="R11">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="S11">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="T11">
         <v>2.62</v>
       </c>
       <c r="U11">
-        <v>3.18</v>
+        <v>2.88</v>
       </c>
       <c r="V11">
         <v>1.28</v>
@@ -2147,10 +2147,10 @@
         <v>1.6</v>
       </c>
       <c r="AC11">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="AD11">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE11">
         <v>1.02</v>
@@ -2159,7 +2159,7 @@
         <v>2.88</v>
       </c>
       <c r="AG11">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2268,19 +2268,19 @@
         <v>2.5</v>
       </c>
       <c r="O12">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="P12">
         <v>3.1</v>
       </c>
       <c r="Q12">
-        <v>3.57</v>
+        <v>3.6</v>
       </c>
       <c r="R12">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="S12">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="T12">
         <v>1.94</v>
@@ -2289,25 +2289,25 @@
         <v>4.75</v>
       </c>
       <c r="V12">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="W12">
         <v>1.02</v>
       </c>
       <c r="X12">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Y12">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Z12">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AA12">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AB12">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AC12">
         <v>8</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AK12">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2431,61 +2431,61 @@
         <v>4.26</v>
       </c>
       <c r="O13">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P13">
         <v>1.72</v>
       </c>
       <c r="Q13">
-        <v>5.25</v>
+        <v>4.47</v>
       </c>
       <c r="R13">
-        <v>2.21</v>
+        <v>2.09</v>
       </c>
       <c r="S13">
         <v>1.4</v>
       </c>
       <c r="T13">
-        <v>2.85</v>
+        <v>2.73</v>
       </c>
       <c r="U13">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="V13">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="W13">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X13">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y13">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z13">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AA13">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AB13">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AC13">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="AD13">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE13">
         <v>1.04</v>
       </c>
       <c r="AF13">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AG13">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>1.28</v>
       </c>
       <c r="AK13">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="O14">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="P14">
-        <v>4.46</v>
+        <v>4.4</v>
       </c>
       <c r="Q14">
         <v>2.7</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>3.75</v>
+        <v>3.82</v>
       </c>
       <c r="O15">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P15">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="Q15">
         <v>4.92</v>
@@ -2769,7 +2769,7 @@
         <v>2.02</v>
       </c>
       <c r="S15">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T15">
         <v>2.55</v>
@@ -2796,7 +2796,7 @@
         <v>2.25</v>
       </c>
       <c r="AB15">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC15">
         <v>4.2</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="O16">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P16">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="Q16">
         <v>2.12</v>
@@ -2935,7 +2935,7 @@
         <v>1.37</v>
       </c>
       <c r="T16">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="U16">
         <v>2.8</v>
@@ -2956,7 +2956,7 @@
         <v>3</v>
       </c>
       <c r="AA16">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB16">
         <v>1.72</v>
@@ -2971,10 +2971,10 @@
         <v>1.06</v>
       </c>
       <c r="AF16">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AG16">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK16">
         <v>2.3</v>
@@ -3080,10 +3080,10 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O17">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P17">
         <v>1.91</v>
@@ -3113,10 +3113,10 @@
         <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z17">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA17">
         <v>1.95</v>
@@ -3134,7 +3134,7 @@
         <v>1.07</v>
       </c>
       <c r="AF17">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG17">
         <v>1.89</v>
@@ -3243,61 +3243,61 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="O18">
         <v>5.5</v>
       </c>
       <c r="P18">
-        <v>9.5</v>
+        <v>13</v>
       </c>
       <c r="Q18">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="R18">
-        <v>2.59</v>
+        <v>2.75</v>
       </c>
       <c r="S18">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T18">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U18">
-        <v>2.28</v>
+        <v>2.39</v>
       </c>
       <c r="V18">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="W18">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X18">
         <v>1.02</v>
       </c>
       <c r="Y18">
+        <v>1.2</v>
+      </c>
+      <c r="Z18">
+        <v>4.5</v>
+      </c>
+      <c r="AA18">
+        <v>1.61</v>
+      </c>
+      <c r="AB18">
+        <v>2.12</v>
+      </c>
+      <c r="AC18">
+        <v>2.42</v>
+      </c>
+      <c r="AD18">
+        <v>1.5</v>
+      </c>
+      <c r="AE18">
         <v>1.15</v>
       </c>
-      <c r="Z18">
-        <v>4.2</v>
-      </c>
-      <c r="AA18">
-        <v>1.58</v>
-      </c>
-      <c r="AB18">
-        <v>2.25</v>
-      </c>
-      <c r="AC18">
-        <v>2.35</v>
-      </c>
-      <c r="AD18">
-        <v>1.47</v>
-      </c>
-      <c r="AE18">
-        <v>1.16</v>
-      </c>
       <c r="AF18">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="AG18">
         <v>1.55</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AK18">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>5.03</v>
       </c>
       <c r="Q20">
         <v>2.22</v>
@@ -3584,16 +3584,16 @@
         <v>2.13</v>
       </c>
       <c r="S20">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T20">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="U20">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="V20">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W20">
         <v>1.05</v>
@@ -3608,10 +3608,10 @@
         <v>3</v>
       </c>
       <c r="AA20">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AB20">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AC20">
         <v>3.6</v>
@@ -3738,19 +3738,19 @@
         <v>2.95</v>
       </c>
       <c r="P21">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="Q21">
         <v>3.7</v>
       </c>
       <c r="R21">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="S21">
         <v>1.47</v>
       </c>
       <c r="T21">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="U21">
         <v>3.2</v>
@@ -3771,13 +3771,13 @@
         <v>2.65</v>
       </c>
       <c r="AA21">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AB21">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AC21">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AD21">
         <v>1.17</v>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.49</v>
+        <v>1.34</v>
       </c>
       <c r="AK21">
         <v>1.38</v>
@@ -3895,49 +3895,49 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="O22">
         <v>4.1</v>
       </c>
       <c r="P22">
-        <v>5</v>
+        <v>5.15</v>
       </c>
       <c r="Q22">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R22">
         <v>2.38</v>
       </c>
       <c r="S22">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T22">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="U22">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="V22">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="W22">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X22">
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z22">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="AA22">
         <v>1.68</v>
       </c>
       <c r="AB22">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AC22">
         <v>2.62</v>
@@ -3949,10 +3949,10 @@
         <v>1.15</v>
       </c>
       <c r="AF22">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AG22">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AK22">
         <v>2.31</v>
@@ -4058,10 +4058,10 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="O23">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P23">
         <v>4.8</v>
@@ -4070,52 +4070,52 @@
         <v>2.1</v>
       </c>
       <c r="R23">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="S23">
         <v>1.3</v>
       </c>
       <c r="T23">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="U23">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="V23">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W23">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X23">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y23">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z23">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AA23">
         <v>1.77</v>
       </c>
       <c r="AB23">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AC23">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="AD23">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE23">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AF23">
         <v>1.74</v>
       </c>
       <c r="AG23">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK23">
         <v>2.15</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="O24">
         <v>3.8</v>
       </c>
       <c r="P24">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="Q24">
         <v>2.8</v>
       </c>
       <c r="R24">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="S24">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="T24">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U24">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="V24">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="W24">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X24">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
         <v>1.11</v>
       </c>
       <c r="Z24">
-        <v>6.41</v>
+        <v>6.86</v>
       </c>
       <c r="AA24">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AB24">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AC24">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="AD24">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AE24">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AF24">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG24">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AK24">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,25 +4384,25 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="O25">
         <v>3.4</v>
       </c>
       <c r="P25">
-        <v>2.9</v>
+        <v>3.18</v>
       </c>
       <c r="Q25">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="R25">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S25">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T25">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="U25">
         <v>2.75</v>
@@ -4417,7 +4417,7 @@
         <v>1.05</v>
       </c>
       <c r="Y25">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z25">
         <v>3.5</v>
@@ -4426,7 +4426,7 @@
         <v>1.89</v>
       </c>
       <c r="AB25">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC25">
         <v>3.25</v>
@@ -4435,13 +4435,13 @@
         <v>1.33</v>
       </c>
       <c r="AE25">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF25">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="AG25">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,7 +4454,7 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AK25">
         <v>1.62</v>
@@ -4547,31 +4547,31 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="O26">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="P26">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="Q26">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="R26">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="S26">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T26">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="U26">
-        <v>2.7</v>
+        <v>2.47</v>
       </c>
       <c r="V26">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="W26">
         <v>1.08</v>
@@ -4583,13 +4583,13 @@
         <v>1.25</v>
       </c>
       <c r="Z26">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AA26">
         <v>1.75</v>
       </c>
       <c r="AB26">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="AC26">
         <v>3</v>
@@ -4601,10 +4601,10 @@
         <v>1.14</v>
       </c>
       <c r="AF26">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="AG26">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="O27">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P27">
-        <v>4.65</v>
+        <v>4.56</v>
       </c>
       <c r="Q27">
         <v>2.12</v>
@@ -4725,16 +4725,16 @@
         <v>2.4</v>
       </c>
       <c r="S27">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T27">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U27">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="V27">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W27">
         <v>1.08</v>
@@ -4755,7 +4755,7 @@
         <v>1.92</v>
       </c>
       <c r="AC27">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AD27">
         <v>1.34</v>
@@ -4764,7 +4764,7 @@
         <v>1.1</v>
       </c>
       <c r="AF27">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AG27">
         <v>1.91</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.72</v>
+        <v>1.57</v>
       </c>
       <c r="O29">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="P29">
-        <v>2.5</v>
+        <v>6.35</v>
       </c>
       <c r="Q29">
-        <v>3.25</v>
+        <v>2.2</v>
       </c>
       <c r="R29">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="S29">
         <v>1.42</v>
       </c>
       <c r="T29">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="U29">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="V29">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="W29">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X29">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y29">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z29">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AA29">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="AB29">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AC29">
-        <v>3.82</v>
+        <v>3.85</v>
       </c>
       <c r="AD29">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE29">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF29">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="AG29">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK29">
-        <v>1.44</v>
+        <v>2.3</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,80 +5199,80 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.57</v>
+        <v>2.72</v>
       </c>
       <c r="O30">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P30">
-        <v>6.35</v>
+        <v>2.5</v>
       </c>
       <c r="Q30">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="R30">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="S30">
         <v>1.42</v>
       </c>
       <c r="T30">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="U30">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="V30">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="W30">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X30">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y30">
+        <v>1.4</v>
+      </c>
+      <c r="Z30">
+        <v>3.1</v>
+      </c>
+      <c r="AA30">
+        <v>2.15</v>
+      </c>
+      <c r="AB30">
+        <v>1.65</v>
+      </c>
+      <c r="AC30">
+        <v>3.82</v>
+      </c>
+      <c r="AD30">
+        <v>1.18</v>
+      </c>
+      <c r="AE30">
+        <v>1.06</v>
+      </c>
+      <c r="AF30">
+        <v>1.77</v>
+      </c>
+      <c r="AG30">
+        <v>1.91</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30">
         <v>1.36</v>
       </c>
-      <c r="Z30">
-        <v>2.88</v>
-      </c>
-      <c r="AA30">
-        <v>1.94</v>
-      </c>
-      <c r="AB30">
-        <v>1.72</v>
-      </c>
-      <c r="AC30">
-        <v>3.85</v>
-      </c>
-      <c r="AD30">
-        <v>1.22</v>
-      </c>
-      <c r="AE30">
-        <v>1.08</v>
-      </c>
-      <c r="AF30">
-        <v>2.05</v>
-      </c>
-      <c r="AG30">
-        <v>1.73</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ30">
-        <v>1.25</v>
-      </c>
       <c r="AK30">
-        <v>2.3</v>
+        <v>1.44</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.15</v>
+        <v>2.62</v>
       </c>
       <c r="O38">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="P38">
-        <v>2.9</v>
+        <v>2.23</v>
       </c>
       <c r="Q38">
-        <v>2.63</v>
+        <v>3.1</v>
       </c>
       <c r="R38">
+        <v>2.35</v>
+      </c>
+      <c r="S38">
+        <v>1.2</v>
+      </c>
+      <c r="T38">
+        <v>4</v>
+      </c>
+      <c r="U38">
         <v>2.2</v>
       </c>
-      <c r="S38">
-        <v>1.3</v>
-      </c>
-      <c r="T38">
-        <v>3.05</v>
-      </c>
-      <c r="U38">
-        <v>2.46</v>
-      </c>
       <c r="V38">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="W38">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X38">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y38">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="Z38">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="AA38">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AB38">
-        <v>2.1</v>
+        <v>2.55</v>
       </c>
       <c r="AC38">
-        <v>2.8</v>
+        <v>2.31</v>
       </c>
       <c r="AD38">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="AE38">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AF38">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AG38">
-        <v>2.2</v>
+        <v>2.53</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.62</v>
+        <v>2.15</v>
       </c>
       <c r="O39">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="P39">
-        <v>2.23</v>
+        <v>2.9</v>
       </c>
       <c r="Q39">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="R39">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="S39">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="T39">
+        <v>3.05</v>
+      </c>
+      <c r="U39">
+        <v>2.46</v>
+      </c>
+      <c r="V39">
+        <v>1.46</v>
+      </c>
+      <c r="W39">
+        <v>1.08</v>
+      </c>
+      <c r="X39">
+        <v>1.04</v>
+      </c>
+      <c r="Y39">
+        <v>1.26</v>
+      </c>
+      <c r="Z39">
         <v>4</v>
       </c>
-      <c r="U39">
+      <c r="AA39">
+        <v>1.7</v>
+      </c>
+      <c r="AB39">
+        <v>2.1</v>
+      </c>
+      <c r="AC39">
+        <v>2.8</v>
+      </c>
+      <c r="AD39">
+        <v>1.42</v>
+      </c>
+      <c r="AE39">
+        <v>1.11</v>
+      </c>
+      <c r="AF39">
+        <v>1.61</v>
+      </c>
+      <c r="AG39">
         <v>2.2</v>
-      </c>
-      <c r="V39">
-        <v>1.6</v>
-      </c>
-      <c r="W39">
-        <v>1.13</v>
-      </c>
-      <c r="X39">
-        <v>1.03</v>
-      </c>
-      <c r="Y39">
-        <v>1.16</v>
-      </c>
-      <c r="Z39">
-        <v>5.5</v>
-      </c>
-      <c r="AA39">
-        <v>1.55</v>
-      </c>
-      <c r="AB39">
-        <v>2.55</v>
-      </c>
-      <c r="AC39">
-        <v>2.31</v>
-      </c>
-      <c r="AD39">
-        <v>1.56</v>
-      </c>
-      <c r="AE39">
-        <v>1.2</v>
-      </c>
-      <c r="AF39">
-        <v>1.44</v>
-      </c>
-      <c r="AG39">
-        <v>2.53</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>1.35</v>
+        <v>1.62</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Real Salt Lake</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>FC Dallas</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,65 +7807,65 @@
         </is>
       </c>
       <c r="N46">
-        <v>2.73</v>
+        <v>1.87</v>
       </c>
       <c r="O46">
+        <v>3.5</v>
+      </c>
+      <c r="P46">
         <v>3.4</v>
       </c>
-      <c r="P46">
-        <v>2.3</v>
-      </c>
       <c r="Q46">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="R46">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="S46">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T46">
-        <v>3.22</v>
+        <v>3.65</v>
       </c>
       <c r="U46">
+        <v>2.12</v>
+      </c>
+      <c r="V46">
+        <v>1.63</v>
+      </c>
+      <c r="W46">
+        <v>1.13</v>
+      </c>
+      <c r="X46">
+        <v>1.03</v>
+      </c>
+      <c r="Y46">
+        <v>1.13</v>
+      </c>
+      <c r="Z46">
+        <v>5.5</v>
+      </c>
+      <c r="AA46">
+        <v>1.46</v>
+      </c>
+      <c r="AB46">
+        <v>2.65</v>
+      </c>
+      <c r="AC46">
+        <v>2.25</v>
+      </c>
+      <c r="AD46">
+        <v>1.58</v>
+      </c>
+      <c r="AE46">
+        <v>1.22</v>
+      </c>
+      <c r="AF46">
+        <v>1.44</v>
+      </c>
+      <c r="AG46">
         <v>2.5</v>
       </c>
-      <c r="V46">
-        <v>1.44</v>
-      </c>
-      <c r="W46">
-        <v>1.12</v>
-      </c>
-      <c r="X46">
-        <v>1.04</v>
-      </c>
-      <c r="Y46">
-        <v>1.22</v>
-      </c>
-      <c r="Z46">
-        <v>4</v>
-      </c>
-      <c r="AA46">
-        <v>1.73</v>
-      </c>
-      <c r="AB46">
-        <v>2.05</v>
-      </c>
-      <c r="AC46">
-        <v>2.7</v>
-      </c>
-      <c r="AD46">
-        <v>1.44</v>
-      </c>
-      <c r="AE46">
-        <v>1.11</v>
-      </c>
-      <c r="AF46">
-        <v>1.57</v>
-      </c>
-      <c r="AG46">
-        <v>2.3</v>
-      </c>
       <c r="AH46" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK46">
-        <v>1.38</v>
+        <v>1.83</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Real Salt Lake</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>FC Dallas</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="O47">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P47">
-        <v>3.4</v>
+        <v>4.53</v>
       </c>
       <c r="Q47">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="R47">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="S47">
         <v>1.22</v>
       </c>
       <c r="T47">
-        <v>3.65</v>
+        <v>3.34</v>
       </c>
       <c r="U47">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="V47">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="W47">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X47">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y47">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z47">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AA47">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="AB47">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="AC47">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="AD47">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AE47">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF47">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AG47">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AK47">
-        <v>1.83</v>
+        <v>2.24</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.65</v>
+        <v>2.73</v>
       </c>
       <c r="O48">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="P48">
-        <v>4.53</v>
+        <v>2.3</v>
       </c>
       <c r="Q48">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="R48">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S48">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T48">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="U48">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="V48">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="W48">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X48">
         <v>1.04</v>
       </c>
       <c r="Y48">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="Z48">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA48">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AB48">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="AC48">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="AD48">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AE48">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AF48">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG48">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AK48">
-        <v>2.24</v>
+        <v>1.38</v>
       </c>
       <c r="AL48">
         <v>0</v>

--- a/jogos_2026-08-19.xlsx
+++ b/jogos_2026-08-19.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.96</v>
+        <v>1.4</v>
       </c>
       <c r="O2">
-        <v>3.76</v>
+        <v>4.76</v>
       </c>
       <c r="P2">
-        <v>2.95</v>
+        <v>6</v>
       </c>
       <c r="Q2">
         <v>1.84</v>
       </c>
       <c r="R2">
-        <v>2.4</v>
+        <v>2.51</v>
       </c>
       <c r="S2">
         <v>1.2</v>
       </c>
       <c r="T2">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="U2">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V2">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="W2">
         <v>1.13</v>
       </c>
       <c r="X2">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y2">
         <v>1.1</v>
       </c>
       <c r="Z2">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AA2">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB2">
         <v>2.7</v>
       </c>
       <c r="AC2">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="AD2">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AE2">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AF2">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG2">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -708,7 +708,7 @@
         <v>1.11</v>
       </c>
       <c r="AK2">
-        <v>2.17</v>
+        <v>2.49</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,52 +798,52 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="O3">
-        <v>3.3</v>
+        <v>3.47</v>
       </c>
       <c r="P3">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="Q3">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="R3">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="S3">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T3">
-        <v>3.07</v>
+        <v>3.2</v>
       </c>
       <c r="U3">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="V3">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W3">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X3">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y3">
         <v>1.21</v>
       </c>
       <c r="Z3">
-        <v>3.58</v>
+        <v>3.62</v>
       </c>
       <c r="AA3">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AB3">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="AC3">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AD3">
         <v>1.36</v>
@@ -855,7 +855,7 @@
         <v>1.62</v>
       </c>
       <c r="AG3">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK3">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,31 +961,31 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="O4">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P4">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="Q4">
-        <v>3.8</v>
+        <v>4.53</v>
       </c>
       <c r="R4">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="S4">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T4">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="U4">
         <v>3.04</v>
       </c>
       <c r="V4">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W4">
         <v>1.04</v>
@@ -994,31 +994,31 @@
         <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z4">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="AA4">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB4">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC4">
-        <v>3.78</v>
+        <v>4.2</v>
       </c>
       <c r="AD4">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE4">
         <v>1.02</v>
       </c>
       <c r="AF4">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="AG4">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.3</v>
+        <v>1.94</v>
       </c>
       <c r="AK4">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,31 +1124,31 @@
         </is>
       </c>
       <c r="N5">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="O5">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P5">
-        <v>4.5</v>
+        <v>4.35</v>
       </c>
       <c r="Q5">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="R5">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="S5">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T5">
         <v>2.73</v>
       </c>
       <c r="U5">
-        <v>3.05</v>
+        <v>3.29</v>
       </c>
       <c r="V5">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W5">
         <v>1.03</v>
@@ -1160,41 +1160,41 @@
         <v>1.34</v>
       </c>
       <c r="Z5">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="AA5">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AB5">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC5">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AD5">
+        <v>1.19</v>
+      </c>
+      <c r="AE5">
+        <v>1.03</v>
+      </c>
+      <c r="AF5">
+        <v>1.9</v>
+      </c>
+      <c r="AG5">
+        <v>1.78</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5">
         <v>1.2</v>
-      </c>
-      <c r="AE5">
-        <v>1.04</v>
-      </c>
-      <c r="AF5">
-        <v>1.95</v>
-      </c>
-      <c r="AG5">
-        <v>1.76</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5">
-        <v>1.21</v>
       </c>
       <c r="AK5">
         <v>1.97</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="O8">
         <v>7.7</v>
       </c>
       <c r="P8">
-        <v>14.7</v>
+        <v>15.25</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -2428,37 +2428,37 @@
         </is>
       </c>
       <c r="N13">
-        <v>4.26</v>
+        <v>4.1</v>
       </c>
       <c r="O13">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="P13">
         <v>1.72</v>
       </c>
       <c r="Q13">
-        <v>4.47</v>
+        <v>4.46</v>
       </c>
       <c r="R13">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="S13">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="T13">
         <v>2.73</v>
       </c>
       <c r="U13">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="V13">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W13">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X13">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y13">
         <v>1.27</v>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AK13">
         <v>1.08</v>
@@ -3406,10 +3406,10 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="O19">
-        <v>2.65</v>
+        <v>3.05</v>
       </c>
       <c r="P19">
         <v>4.5</v>
@@ -3424,10 +3424,10 @@
         <v>1.5</v>
       </c>
       <c r="T19">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="U19">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="V19">
         <v>1.25</v>
@@ -3436,16 +3436,16 @@
         <v>1.05</v>
       </c>
       <c r="X19">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Y19">
         <v>1.49</v>
       </c>
       <c r="Z19">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="AA19">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AB19">
         <v>1.5</v>
@@ -4873,25 +4873,25 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="O28">
-        <v>3.6</v>
+        <v>3.23</v>
       </c>
       <c r="P28">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q28">
         <v>3.1</v>
       </c>
       <c r="R28">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="S28">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="T28">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="U28">
         <v>2.45</v>
@@ -4906,19 +4906,19 @@
         <v>1.03</v>
       </c>
       <c r="Y28">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z28">
         <v>4.2</v>
       </c>
       <c r="AA28">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AB28">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AC28">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AD28">
         <v>1.4</v>
@@ -4927,7 +4927,7 @@
         <v>1.12</v>
       </c>
       <c r="AF28">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AG28">
         <v>2.3</v>
@@ -4943,7 +4943,7 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.49</v>
+        <v>1.22</v>
       </c>
       <c r="AK28">
         <v>1.4</v>
@@ -5036,49 +5036,49 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="O29">
         <v>3.5</v>
       </c>
       <c r="P29">
-        <v>6.35</v>
+        <v>5</v>
       </c>
       <c r="Q29">
         <v>2.2</v>
       </c>
       <c r="R29">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S29">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T29">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="U29">
-        <v>2.9</v>
+        <v>3.09</v>
       </c>
       <c r="V29">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="W29">
         <v>1.05</v>
       </c>
       <c r="X29">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y29">
         <v>1.36</v>
       </c>
       <c r="Z29">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AA29">
         <v>1.94</v>
       </c>
       <c r="AB29">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AC29">
         <v>3.85</v>
@@ -5090,7 +5090,7 @@
         <v>1.08</v>
       </c>
       <c r="AF29">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AG29">
         <v>1.73</v>
@@ -5109,7 +5109,7 @@
         <v>1.25</v>
       </c>
       <c r="AK29">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="O30">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P30">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q30">
         <v>3.25</v>
@@ -5214,34 +5214,34 @@
         <v>2.05</v>
       </c>
       <c r="S30">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="T30">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="U30">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="V30">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W30">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X30">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y30">
         <v>1.4</v>
       </c>
       <c r="Z30">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AA30">
         <v>2.15</v>
       </c>
       <c r="AB30">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AC30">
         <v>3.82</v>
@@ -5250,13 +5250,13 @@
         <v>1.18</v>
       </c>
       <c r="AE30">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF30">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AG30">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5272,7 +5272,7 @@
         <v>1.36</v>
       </c>
       <c r="AK30">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,28 +5362,28 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="O31">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P31">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="Q31">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="R31">
         <v>2.3</v>
       </c>
       <c r="S31">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T31">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="U31">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="V31">
         <v>1.44</v>
@@ -5392,31 +5392,31 @@
         <v>1.09</v>
       </c>
       <c r="X31">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y31">
         <v>1.2</v>
       </c>
       <c r="Z31">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="AA31">
         <v>1.73</v>
       </c>
       <c r="AB31">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AC31">
-        <v>2.81</v>
+        <v>2.74</v>
       </c>
       <c r="AD31">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AE31">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF31">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AG31">
         <v>2</v>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AK31">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5528,7 +5528,7 @@
         <v>2.37</v>
       </c>
       <c r="O32">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="P32">
         <v>2.45</v>
@@ -5540,7 +5540,7 @@
         <v>2.35</v>
       </c>
       <c r="S32">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="T32">
         <v>3.5</v>
@@ -5561,10 +5561,10 @@
         <v>1.13</v>
       </c>
       <c r="Z32">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AA32">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AB32">
         <v>2.36</v>
@@ -5576,13 +5576,13 @@
         <v>1.51</v>
       </c>
       <c r="AE32">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF32">
         <v>1.5</v>
       </c>
       <c r="AG32">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.2</v>
+        <v>1.43</v>
       </c>
       <c r="AK32">
         <v>1.48</v>
@@ -5688,19 +5688,19 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="O33">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="P33">
-        <v>4.6</v>
+        <v>4.05</v>
       </c>
       <c r="Q33">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="R33">
-        <v>2.32</v>
+        <v>2.45</v>
       </c>
       <c r="S33">
         <v>1.25</v>
@@ -5730,16 +5730,16 @@
         <v>1.6</v>
       </c>
       <c r="AB33">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="AC33">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AD33">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AE33">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF33">
         <v>1.6</v>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AK33">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,31 +5851,31 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="O34">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P34">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="Q34">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="R34">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="S34">
         <v>1.3</v>
       </c>
       <c r="T34">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U34">
-        <v>2.36</v>
+        <v>2.51</v>
       </c>
       <c r="V34">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W34">
         <v>1.11</v>
@@ -5887,28 +5887,28 @@
         <v>1.2</v>
       </c>
       <c r="Z34">
-        <v>4.1</v>
+        <v>4.52</v>
       </c>
       <c r="AA34">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB34">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AC34">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="AD34">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AE34">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF34">
         <v>1.62</v>
       </c>
       <c r="AG34">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AK34">
         <v>1.6</v>
@@ -6017,16 +6017,16 @@
         <v>2.37</v>
       </c>
       <c r="O35">
-        <v>4.24</v>
+        <v>3.9</v>
       </c>
       <c r="P35">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="Q35">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="R35">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="S35">
         <v>1.2</v>
@@ -6038,7 +6038,7 @@
         <v>2</v>
       </c>
       <c r="V35">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="W35">
         <v>1.2</v>
@@ -6047,31 +6047,31 @@
         <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z35">
-        <v>5.55</v>
+        <v>6.25</v>
       </c>
       <c r="AA35">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AB35">
-        <v>2.68</v>
+        <v>3.1</v>
       </c>
       <c r="AC35">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AD35">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AE35">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AF35">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AG35">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="AK35">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="O36">
         <v>3.8</v>
       </c>
       <c r="P36">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q36">
         <v>2.9</v>
       </c>
       <c r="R36">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="S36">
         <v>1.2</v>
       </c>
       <c r="T36">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="U36">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="V36">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="W36">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="X36">
         <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z36">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="AA36">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AB36">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AC36">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="AD36">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AE36">
+        <v>1.33</v>
+      </c>
+      <c r="AF36">
         <v>1.36</v>
       </c>
-      <c r="AF36">
-        <v>1.3</v>
-      </c>
       <c r="AG36">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="O37">
-        <v>3.9</v>
+        <v>4.43</v>
       </c>
       <c r="P37">
-        <v>3.18</v>
+        <v>3.42</v>
       </c>
       <c r="Q37">
         <v>2.25</v>
@@ -6364,10 +6364,10 @@
         <v>2.01</v>
       </c>
       <c r="V37">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W37">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X37">
         <v>1.02</v>
@@ -6379,16 +6379,16 @@
         <v>6</v>
       </c>
       <c r="AA37">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AB37">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="AC37">
         <v>2.1</v>
       </c>
       <c r="AD37">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AE37">
         <v>1.3</v>
@@ -6397,7 +6397,7 @@
         <v>1.4</v>
       </c>
       <c r="AG37">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AK37">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>3.75</v>
       </c>
       <c r="P38">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="Q38">
         <v>3.1</v>
@@ -6521,34 +6521,34 @@
         <v>1.2</v>
       </c>
       <c r="T38">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="U38">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="V38">
         <v>1.6</v>
       </c>
       <c r="W38">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X38">
         <v>1.03</v>
       </c>
       <c r="Y38">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="Z38">
-        <v>5.5</v>
+        <v>4.65</v>
       </c>
       <c r="AA38">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AB38">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AC38">
-        <v>2.31</v>
+        <v>2.23</v>
       </c>
       <c r="AD38">
         <v>1.56</v>
@@ -6560,7 +6560,7 @@
         <v>1.44</v>
       </c>
       <c r="AG38">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6672,7 +6672,7 @@
         <v>3.5</v>
       </c>
       <c r="P39">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Q39">
         <v>2.63</v>
@@ -6681,16 +6681,16 @@
         <v>2.2</v>
       </c>
       <c r="S39">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T39">
         <v>3.05</v>
       </c>
       <c r="U39">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="V39">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W39">
         <v>1.08</v>
@@ -6699,7 +6699,7 @@
         <v>1.04</v>
       </c>
       <c r="Y39">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="Z39">
         <v>4</v>
@@ -6717,7 +6717,7 @@
         <v>1.42</v>
       </c>
       <c r="AE39">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF39">
         <v>1.61</v>
@@ -6736,7 +6736,7 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK39">
         <v>1.62</v>
@@ -6829,19 +6829,19 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="O40">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="P40">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="Q40">
         <v>2.93</v>
       </c>
       <c r="R40">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="S40">
         <v>1.59</v>
@@ -6850,7 +6850,7 @@
         <v>2.23</v>
       </c>
       <c r="U40">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="V40">
         <v>1.21</v>
@@ -6865,25 +6865,25 @@
         <v>1.57</v>
       </c>
       <c r="Z40">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="AA40">
-        <v>2.7</v>
+        <v>2.51</v>
       </c>
       <c r="AB40">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AC40">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="AD40">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AE40">
         <v>1.04</v>
       </c>
       <c r="AF40">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG40">
         <v>1.6</v>
@@ -6992,10 +6992,10 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="O41">
-        <v>4.5</v>
+        <v>4.35</v>
       </c>
       <c r="P41">
         <v>7</v>
@@ -7004,10 +7004,10 @@
         <v>1.85</v>
       </c>
       <c r="R41">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="S41">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T41">
         <v>2.9</v>
@@ -7019,34 +7019,34 @@
         <v>1.44</v>
       </c>
       <c r="W41">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X41">
         <v>1.03</v>
       </c>
       <c r="Y41">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z41">
+        <v>3.8</v>
+      </c>
+      <c r="AA41">
+        <v>1.79</v>
+      </c>
+      <c r="AB41">
+        <v>1.87</v>
+      </c>
+      <c r="AC41">
         <v>3.4</v>
       </c>
-      <c r="AA41">
-        <v>1.99</v>
-      </c>
-      <c r="AB41">
-        <v>1.83</v>
-      </c>
-      <c r="AC41">
-        <v>3.36</v>
-      </c>
       <c r="AD41">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AE41">
         <v>1.11</v>
       </c>
       <c r="AF41">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AG41">
         <v>1.62</v>
@@ -7065,7 +7065,7 @@
         <v>1.2</v>
       </c>
       <c r="AK41">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7164,55 +7164,55 @@
         <v>4.37</v>
       </c>
       <c r="Q42">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="R42">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="S42">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T42">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="U42">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="V42">
         <v>1.5</v>
       </c>
       <c r="W42">
+        <v>1.13</v>
+      </c>
+      <c r="X42">
+        <v>1</v>
+      </c>
+      <c r="Y42">
+        <v>1.22</v>
+      </c>
+      <c r="Z42">
+        <v>3.84</v>
+      </c>
+      <c r="AA42">
+        <v>1.7</v>
+      </c>
+      <c r="AB42">
+        <v>2.04</v>
+      </c>
+      <c r="AC42">
+        <v>2.7</v>
+      </c>
+      <c r="AD42">
+        <v>1.41</v>
+      </c>
+      <c r="AE42">
         <v>1.12</v>
       </c>
-      <c r="X42">
-        <v>1.03</v>
-      </c>
-      <c r="Y42">
-        <v>1.13</v>
-      </c>
-      <c r="Z42">
-        <v>4.5</v>
-      </c>
-      <c r="AA42">
+      <c r="AF42">
         <v>1.6</v>
       </c>
-      <c r="AB42">
-        <v>2.18</v>
-      </c>
-      <c r="AC42">
-        <v>2.55</v>
-      </c>
-      <c r="AD42">
-        <v>1.44</v>
-      </c>
-      <c r="AE42">
-        <v>1.14</v>
-      </c>
-      <c r="AF42">
-        <v>1.53</v>
-      </c>
       <c r="AG42">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>1.22</v>
       </c>
       <c r="AK42">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,34 +7318,34 @@
         </is>
       </c>
       <c r="N43">
-        <v>3.2</v>
+        <v>3.07</v>
       </c>
       <c r="O43">
-        <v>3.6</v>
+        <v>3.67</v>
       </c>
       <c r="P43">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="Q43">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="R43">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="S43">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T43">
         <v>3.8</v>
       </c>
       <c r="U43">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="V43">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="W43">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="X43">
         <v>1.01</v>
@@ -7357,10 +7357,10 @@
         <v>5.4</v>
       </c>
       <c r="AA43">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AB43">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AC43">
         <v>2.2</v>
@@ -7375,7 +7375,7 @@
         <v>1.44</v>
       </c>
       <c r="AG43">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AK43">
         <v>1.23</v>
@@ -7484,16 +7484,16 @@
         <v>1.78</v>
       </c>
       <c r="O44">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P44">
-        <v>3.8</v>
+        <v>4.25</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
       </c>
       <c r="R44">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S44">
         <v>1.3</v>
@@ -7502,34 +7502,34 @@
         <v>3.3</v>
       </c>
       <c r="U44">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="V44">
         <v>1.5</v>
       </c>
       <c r="W44">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="X44">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y44">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z44">
-        <v>4.05</v>
+        <v>4.33</v>
       </c>
       <c r="AA44">
         <v>1.7</v>
       </c>
       <c r="AB44">
-        <v>2.28</v>
+        <v>2.11</v>
       </c>
       <c r="AC44">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="AD44">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE44">
         <v>1.15</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK44">
         <v>1.95</v>
@@ -7653,7 +7653,7 @@
         <v>2.66</v>
       </c>
       <c r="Q45">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="R45">
         <v>1.9</v>
@@ -7674,31 +7674,31 @@
         <v>1.02</v>
       </c>
       <c r="X45">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y45">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="Z45">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AA45">
         <v>2.62</v>
       </c>
       <c r="AB45">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AC45">
-        <v>4.9</v>
+        <v>5.25</v>
       </c>
       <c r="AD45">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AE45">
         <v>1.04</v>
       </c>
       <c r="AF45">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AG45">
         <v>1.7</v>
@@ -7717,7 +7717,7 @@
         <v>1.4</v>
       </c>
       <c r="AK45">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7807,19 +7807,19 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="O46">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P46">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="Q46">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="R46">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="S46">
         <v>1.22</v>
@@ -7828,31 +7828,31 @@
         <v>3.65</v>
       </c>
       <c r="U46">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="V46">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W46">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X46">
         <v>1.03</v>
       </c>
       <c r="Y46">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="Z46">
-        <v>5.5</v>
+        <v>5.44</v>
       </c>
       <c r="AA46">
         <v>1.46</v>
       </c>
       <c r="AB46">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="AC46">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AD46">
         <v>1.58</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.65</v>
+        <v>2.72</v>
       </c>
       <c r="O47">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="P47">
-        <v>4.53</v>
+        <v>2.3</v>
       </c>
       <c r="Q47">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="R47">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="S47">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="T47">
-        <v>3.34</v>
+        <v>3.15</v>
       </c>
       <c r="U47">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="V47">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="W47">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X47">
         <v>1.04</v>
       </c>
       <c r="Y47">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="Z47">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA47">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AB47">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AC47">
-        <v>2.48</v>
+        <v>2.7</v>
       </c>
       <c r="AD47">
+        <v>1.44</v>
+      </c>
+      <c r="AE47">
+        <v>1.11</v>
+      </c>
+      <c r="AF47">
         <v>1.53</v>
       </c>
-      <c r="AE47">
-        <v>1.2</v>
-      </c>
-      <c r="AF47">
-        <v>1.56</v>
-      </c>
       <c r="AG47">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AK47">
-        <v>2.24</v>
+        <v>1.4</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.73</v>
+        <v>1.7</v>
       </c>
       <c r="O48">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="P48">
-        <v>2.3</v>
+        <v>4.3</v>
       </c>
       <c r="Q48">
-        <v>3.1</v>
+        <v>2.05</v>
       </c>
       <c r="R48">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S48">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T48">
-        <v>3.22</v>
+        <v>3.45</v>
       </c>
       <c r="U48">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="V48">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="W48">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X48">
         <v>1.04</v>
       </c>
       <c r="Y48">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z48">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA48">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AB48">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AC48">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="AD48">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AE48">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AF48">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AG48">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK48">
-        <v>1.38</v>
+        <v>2.15</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,31 +8296,31 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="O49">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P49">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="Q49">
-        <v>2.95</v>
+        <v>3.18</v>
       </c>
       <c r="R49">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S49">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T49">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U49">
         <v>2.63</v>
       </c>
       <c r="V49">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="W49">
         <v>1.06</v>
@@ -8329,19 +8329,19 @@
         <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="Z49">
-        <v>3.42</v>
+        <v>3.72</v>
       </c>
       <c r="AA49">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AB49">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AC49">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AD49">
         <v>1.36</v>
@@ -8350,7 +8350,7 @@
         <v>1.09</v>
       </c>
       <c r="AF49">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="AG49">
         <v>2.1</v>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="AK49">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,31 +8459,31 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="O50">
         <v>4</v>
       </c>
       <c r="P50">
-        <v>2.71</v>
+        <v>2.99</v>
       </c>
       <c r="Q50">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="R50">
-        <v>2.51</v>
+        <v>2.72</v>
       </c>
       <c r="S50">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T50">
-        <v>4.3</v>
+        <v>4.33</v>
       </c>
       <c r="U50">
         <v>1.95</v>
       </c>
       <c r="V50">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="W50">
         <v>1.2</v>
@@ -8501,22 +8501,22 @@
         <v>1.36</v>
       </c>
       <c r="AB50">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AC50">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AD50">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AE50">
         <v>1.36</v>
       </c>
       <c r="AF50">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AG50">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AK50">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,19 +8622,19 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="O51">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="P51">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Q51">
         <v>1.95</v>
       </c>
       <c r="R51">
-        <v>2.33</v>
+        <v>2.69</v>
       </c>
       <c r="S51">
         <v>1.25</v>
@@ -8643,28 +8643,28 @@
         <v>3.6</v>
       </c>
       <c r="U51">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="V51">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W51">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X51">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y51">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z51">
         <v>5.25</v>
       </c>
       <c r="AA51">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AB51">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="AC51">
         <v>2.33</v>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AK51">
         <v>2.45</v>
@@ -8785,25 +8785,25 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="O52">
-        <v>3.6</v>
+        <v>3.83</v>
       </c>
       <c r="P52">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="Q52">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="R52">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="S52">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T52">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="U52">
         <v>2.05</v>
@@ -8824,19 +8824,19 @@
         <v>6</v>
       </c>
       <c r="AA52">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="AB52">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="AC52">
         <v>2.12</v>
       </c>
       <c r="AD52">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AE52">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF52">
         <v>1.4</v>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AK52">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AL52">
         <v>0</v>

--- a/jogos_2026-08-19.xlsx
+++ b/jogos_2026-08-19.xlsx
@@ -3409,7 +3409,7 @@
         <v>1.83</v>
       </c>
       <c r="O19">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P19">
         <v>4.5</v>
@@ -3424,7 +3424,7 @@
         <v>1.5</v>
       </c>
       <c r="T19">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="U19">
         <v>3.4</v>
@@ -3439,10 +3439,10 @@
         <v>1.09</v>
       </c>
       <c r="Y19">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Z19">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="AA19">
         <v>2.55</v>
@@ -3451,7 +3451,7 @@
         <v>1.5</v>
       </c>
       <c r="AC19">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AD19">
         <v>1.15</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,80 +5036,80 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="O29">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="P29">
-        <v>5</v>
+        <v>2.6</v>
       </c>
       <c r="Q29">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="R29">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S29">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="T29">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="U29">
-        <v>3.09</v>
+        <v>2.91</v>
       </c>
       <c r="V29">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="W29">
         <v>1.05</v>
       </c>
       <c r="X29">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y29">
+        <v>1.4</v>
+      </c>
+      <c r="Z29">
+        <v>2.9</v>
+      </c>
+      <c r="AA29">
+        <v>2.15</v>
+      </c>
+      <c r="AB29">
+        <v>1.71</v>
+      </c>
+      <c r="AC29">
+        <v>3.82</v>
+      </c>
+      <c r="AD29">
+        <v>1.18</v>
+      </c>
+      <c r="AE29">
+        <v>1.07</v>
+      </c>
+      <c r="AF29">
+        <v>1.76</v>
+      </c>
+      <c r="AG29">
+        <v>1.9</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ29">
         <v>1.36</v>
       </c>
-      <c r="Z29">
-        <v>3.1</v>
-      </c>
-      <c r="AA29">
-        <v>1.94</v>
-      </c>
-      <c r="AB29">
-        <v>1.78</v>
-      </c>
-      <c r="AC29">
-        <v>3.85</v>
-      </c>
-      <c r="AD29">
-        <v>1.22</v>
-      </c>
-      <c r="AE29">
-        <v>1.08</v>
-      </c>
-      <c r="AF29">
-        <v>2.03</v>
-      </c>
-      <c r="AG29">
-        <v>1.73</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ29">
-        <v>1.25</v>
-      </c>
       <c r="AK29">
-        <v>2.25</v>
+        <v>1.43</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="O30">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="P30">
-        <v>2.6</v>
+        <v>5</v>
       </c>
       <c r="Q30">
-        <v>3.25</v>
+        <v>2.2</v>
       </c>
       <c r="R30">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S30">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="T30">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="U30">
-        <v>2.91</v>
+        <v>3.09</v>
       </c>
       <c r="V30">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="W30">
         <v>1.05</v>
       </c>
       <c r="X30">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y30">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z30">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AA30">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="AB30">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AC30">
-        <v>3.82</v>
+        <v>3.85</v>
       </c>
       <c r="AD30">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE30">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF30">
-        <v>1.76</v>
+        <v>2.03</v>
       </c>
       <c r="AG30">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK30">
-        <v>1.43</v>
+        <v>2.25</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.62</v>
+        <v>2.15</v>
       </c>
       <c r="O38">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="P38">
+        <v>3</v>
+      </c>
+      <c r="Q38">
+        <v>2.63</v>
+      </c>
+      <c r="R38">
         <v>2.2</v>
       </c>
-      <c r="Q38">
-        <v>3.1</v>
-      </c>
-      <c r="R38">
-        <v>2.35</v>
-      </c>
       <c r="S38">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="T38">
-        <v>3.7</v>
+        <v>3.05</v>
       </c>
       <c r="U38">
-        <v>2.29</v>
+        <v>2.55</v>
       </c>
       <c r="V38">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="W38">
+        <v>1.08</v>
+      </c>
+      <c r="X38">
+        <v>1.04</v>
+      </c>
+      <c r="Y38">
+        <v>1.24</v>
+      </c>
+      <c r="Z38">
+        <v>4</v>
+      </c>
+      <c r="AA38">
+        <v>1.7</v>
+      </c>
+      <c r="AB38">
+        <v>2.1</v>
+      </c>
+      <c r="AC38">
+        <v>2.8</v>
+      </c>
+      <c r="AD38">
+        <v>1.42</v>
+      </c>
+      <c r="AE38">
         <v>1.14</v>
       </c>
-      <c r="X38">
-        <v>1.03</v>
-      </c>
-      <c r="Y38">
-        <v>1.12</v>
-      </c>
-      <c r="Z38">
-        <v>4.65</v>
-      </c>
-      <c r="AA38">
-        <v>1.53</v>
-      </c>
-      <c r="AB38">
-        <v>2.4</v>
-      </c>
-      <c r="AC38">
-        <v>2.23</v>
-      </c>
-      <c r="AD38">
-        <v>1.56</v>
-      </c>
-      <c r="AE38">
-        <v>1.2</v>
-      </c>
       <c r="AF38">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="AG38">
-        <v>2.51</v>
+        <v>2.2</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK38">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.15</v>
+        <v>2.62</v>
       </c>
       <c r="O39">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="P39">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="Q39">
-        <v>2.63</v>
+        <v>3.1</v>
       </c>
       <c r="R39">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="S39">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="T39">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="U39">
-        <v>2.55</v>
+        <v>2.29</v>
       </c>
       <c r="V39">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="W39">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X39">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y39">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="Z39">
-        <v>4</v>
+        <v>4.65</v>
       </c>
       <c r="AA39">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AB39">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AC39">
-        <v>2.8</v>
+        <v>2.23</v>
       </c>
       <c r="AD39">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="AE39">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AF39">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AG39">
-        <v>2.2</v>
+        <v>2.51</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Colorado Rapids</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.72</v>
+        <v>1.7</v>
       </c>
       <c r="O47">
+        <v>3.85</v>
+      </c>
+      <c r="P47">
+        <v>4.3</v>
+      </c>
+      <c r="Q47">
+        <v>2.05</v>
+      </c>
+      <c r="R47">
+        <v>2.4</v>
+      </c>
+      <c r="S47">
+        <v>1.22</v>
+      </c>
+      <c r="T47">
         <v>3.45</v>
       </c>
-      <c r="P47">
-        <v>2.3</v>
-      </c>
-      <c r="Q47">
-        <v>3.1</v>
-      </c>
-      <c r="R47">
-        <v>2.25</v>
-      </c>
-      <c r="S47">
-        <v>1.31</v>
-      </c>
-      <c r="T47">
-        <v>3.15</v>
-      </c>
       <c r="U47">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="V47">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="W47">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X47">
         <v>1.04</v>
       </c>
       <c r="Y47">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z47">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AA47">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AB47">
         <v>2.25</v>
       </c>
       <c r="AC47">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="AD47">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AE47">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AF47">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AG47">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AK47">
-        <v>1.4</v>
+        <v>2.15</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Colorado Rapids</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.7</v>
+        <v>2.72</v>
       </c>
       <c r="O48">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="P48">
-        <v>4.3</v>
+        <v>2.3</v>
       </c>
       <c r="Q48">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="R48">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="S48">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="T48">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="U48">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="V48">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="W48">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X48">
         <v>1.04</v>
       </c>
       <c r="Y48">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z48">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA48">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AB48">
         <v>2.25</v>
       </c>
       <c r="AC48">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="AD48">
+        <v>1.44</v>
+      </c>
+      <c r="AE48">
+        <v>1.11</v>
+      </c>
+      <c r="AF48">
         <v>1.53</v>
       </c>
-      <c r="AE48">
-        <v>1.2</v>
-      </c>
-      <c r="AF48">
-        <v>1.56</v>
-      </c>
       <c r="AG48">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AK48">
-        <v>2.15</v>
+        <v>1.4</v>
       </c>
       <c r="AL48">
         <v>0</v>

--- a/jogos_2026-08-19.xlsx
+++ b/jogos_2026-08-19.xlsx
@@ -612,42 +612,42 @@
         </is>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2">
         <v>0</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="O2">
-        <v>4.76</v>
+        <v>5.55</v>
       </c>
       <c r="P2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q2">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="R2">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="S2">
         <v>1.2</v>
@@ -659,7 +659,7 @@
         <v>2.1</v>
       </c>
       <c r="V2">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="W2">
         <v>1.13</v>
@@ -677,13 +677,13 @@
         <v>1.4</v>
       </c>
       <c r="AB2">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AC2">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="AD2">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AE2">
         <v>1.29</v>
@@ -692,50 +692,50 @@
         <v>1.57</v>
       </c>
       <c r="AG2">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+1"]</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["22"]</t>
         </is>
       </c>
       <c r="AJ2">
         <v>1.11</v>
       </c>
       <c r="AK2">
-        <v>2.49</v>
+        <v>2.56</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -798,19 +798,19 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="O3">
-        <v>3.47</v>
+        <v>3.3</v>
       </c>
       <c r="P3">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="Q3">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="R3">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="S3">
         <v>1.3</v>
@@ -819,43 +819,43 @@
         <v>3.2</v>
       </c>
       <c r="U3">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="V3">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W3">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X3">
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z3">
-        <v>3.62</v>
+        <v>3.82</v>
       </c>
       <c r="AA3">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AB3">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="AC3">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="AD3">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE3">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF3">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG3">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK3">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,22 +961,22 @@
         </is>
       </c>
       <c r="N4">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="O4">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P4">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="Q4">
-        <v>4.53</v>
+        <v>4.62</v>
       </c>
       <c r="R4">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="S4">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T4">
         <v>2.53</v>
@@ -997,28 +997,28 @@
         <v>1.35</v>
       </c>
       <c r="Z4">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="AA4">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AB4">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AC4">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AD4">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AE4">
         <v>1.02</v>
       </c>
       <c r="AF4">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="AG4">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AK4">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -3406,25 +3406,25 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="O19">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P19">
         <v>4.5</v>
       </c>
       <c r="Q19">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="R19">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="S19">
         <v>1.5</v>
       </c>
       <c r="T19">
-        <v>2.46</v>
+        <v>2.32</v>
       </c>
       <c r="U19">
         <v>3.4</v>
@@ -3439,31 +3439,31 @@
         <v>1.09</v>
       </c>
       <c r="Y19">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Z19">
-        <v>2.61</v>
+        <v>2.55</v>
       </c>
       <c r="AA19">
         <v>2.55</v>
       </c>
       <c r="AB19">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AC19">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AD19">
         <v>1.15</v>
       </c>
       <c r="AE19">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF19">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AG19">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK19">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Portland Timbers</t>
+          <t>Vancouver Whitecaps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>San Diego</t>
+          <t>Houston Dynamo</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.12</v>
+        <v>1.5</v>
       </c>
       <c r="O50">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="P50">
-        <v>2.99</v>
+        <v>5</v>
       </c>
       <c r="Q50">
-        <v>2.56</v>
+        <v>1.95</v>
       </c>
       <c r="R50">
-        <v>2.72</v>
+        <v>2.69</v>
       </c>
       <c r="S50">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="T50">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="U50">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="V50">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="W50">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="X50">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y50">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z50">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="AA50">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="AB50">
-        <v>3.1</v>
+        <v>2.48</v>
       </c>
       <c r="AC50">
-        <v>1.98</v>
+        <v>2.33</v>
       </c>
       <c r="AD50">
-        <v>1.89</v>
+        <v>1.58</v>
       </c>
       <c r="AE50">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AF50">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="AG50">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AK50">
-        <v>1.71</v>
+        <v>2.45</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Vancouver Whitecaps</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Houston Dynamo</t>
+          <t>SJ Earthquakes</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>1.5</v>
+        <v>2.25</v>
       </c>
       <c r="O51">
-        <v>4.33</v>
+        <v>3.83</v>
       </c>
       <c r="P51">
-        <v>5</v>
+        <v>2.55</v>
       </c>
       <c r="Q51">
-        <v>1.95</v>
+        <v>2.55</v>
       </c>
       <c r="R51">
-        <v>2.69</v>
+        <v>2.4</v>
       </c>
       <c r="S51">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="T51">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="U51">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="V51">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="W51">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X51">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y51">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z51">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="AA51">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="AB51">
-        <v>2.48</v>
+        <v>2.85</v>
       </c>
       <c r="AC51">
-        <v>2.33</v>
+        <v>2.12</v>
       </c>
       <c r="AD51">
-        <v>1.58</v>
+        <v>1.69</v>
       </c>
       <c r="AE51">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AF51">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AG51">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="AK51">
-        <v>2.45</v>
+        <v>1.53</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>LA Galaxy</t>
+          <t>Portland Timbers</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SJ Earthquakes</t>
+          <t>San Diego</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="O52">
-        <v>3.83</v>
+        <v>4</v>
       </c>
       <c r="P52">
-        <v>2.55</v>
+        <v>2.99</v>
       </c>
       <c r="Q52">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="R52">
-        <v>2.4</v>
+        <v>2.72</v>
       </c>
       <c r="S52">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="T52">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="U52">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="V52">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="W52">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="X52">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z52">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AA52">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AB52">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="AC52">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="AD52">
-        <v>1.69</v>
+        <v>1.89</v>
       </c>
       <c r="AE52">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AF52">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG52">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AK52">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="AL52">
         <v>0</v>

--- a/jogos_2026-08-19.xlsx
+++ b/jogos_2026-08-19.xlsx
@@ -778,7 +778,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -790,11 +790,11 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
@@ -864,7 +864,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["48"]</t>
         </is>
       </c>
       <c r="AJ3">
@@ -877,16 +877,16 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AQ3">
         <v>0</v>
@@ -941,7 +941,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -953,11 +953,11 @@
         <v>0</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["53"]</t>
         </is>
       </c>
       <c r="AJ4">
@@ -1040,28 +1040,28 @@
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1116,36 +1116,36 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="O5">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="P5">
-        <v>4.35</v>
+        <v>3.76</v>
       </c>
       <c r="Q5">
         <v>2.38</v>
       </c>
       <c r="R5">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="S5">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T5">
-        <v>2.73</v>
+        <v>2.78</v>
       </c>
       <c r="U5">
-        <v>3.29</v>
+        <v>3.21</v>
       </c>
       <c r="V5">
         <v>1.33</v>
@@ -1157,31 +1157,31 @@
         <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Z5">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AA5">
-        <v>2.09</v>
+        <v>2.16</v>
       </c>
       <c r="AB5">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AC5">
-        <v>3.5</v>
+        <v>3.88</v>
       </c>
       <c r="AD5">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE5">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF5">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AG5">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["75"]</t>
         </is>
       </c>
       <c r="AJ5">
@@ -1203,28 +1203,28 @@
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="O6">
         <v>3.25</v>
       </c>
       <c r="P6">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="Q6">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="R6">
         <v>2</v>
       </c>
       <c r="S6">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="T6">
-        <v>2.55</v>
+        <v>2.36</v>
       </c>
       <c r="U6">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="V6">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="W6">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X6">
         <v>1.05</v>
       </c>
       <c r="Y6">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z6">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="AA6">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AB6">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AC6">
         <v>4.3</v>
       </c>
       <c r="AD6">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AE6">
         <v>1.03</v>
       </c>
       <c r="AF6">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG6">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK6">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,52 +1450,52 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="O7">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="P7">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="Q7">
-        <v>2.72</v>
+        <v>3.12</v>
       </c>
       <c r="R7">
-        <v>1.96</v>
+        <v>1.84</v>
       </c>
       <c r="S7">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="T7">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="U7">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="V7">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="W7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X7">
         <v>1.07</v>
       </c>
       <c r="Y7">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Z7">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="AA7">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AB7">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AC7">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AD7">
         <v>1.13</v>
@@ -1504,10 +1504,10 @@
         <v>1.01</v>
       </c>
       <c r="AF7">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="AG7">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AK7">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1753,26 +1753,26 @@
         </is>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["72", "89"]</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["34"]</t>
         </is>
       </c>
       <c r="AJ9">
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="N10">
-        <v>4.99</v>
+        <v>4.7</v>
       </c>
       <c r="O10">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="P10">
         <v>1.72</v>
@@ -2102,52 +2102,52 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="O11">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="P11">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q11">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="R11">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="S11">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T11">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="U11">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="V11">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W11">
         <v>1.01</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z11">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="AA11">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="AB11">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AC11">
-        <v>3.92</v>
+        <v>3.84</v>
       </c>
       <c r="AD11">
         <v>1.18</v>
@@ -2156,10 +2156,10 @@
         <v>1.02</v>
       </c>
       <c r="AF11">
-        <v>2.88</v>
+        <v>2.54</v>
       </c>
       <c r="AG11">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>1.15</v>
       </c>
       <c r="AK11">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="O12">
         <v>2.55</v>
@@ -2274,28 +2274,28 @@
         <v>3.1</v>
       </c>
       <c r="Q12">
-        <v>3.6</v>
+        <v>3.66</v>
       </c>
       <c r="R12">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="S12">
         <v>1.75</v>
       </c>
       <c r="T12">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="U12">
         <v>4.75</v>
       </c>
       <c r="V12">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W12">
         <v>1.02</v>
       </c>
       <c r="X12">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="Y12">
         <v>1.8</v>
@@ -2304,13 +2304,13 @@
         <v>1.93</v>
       </c>
       <c r="AA12">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AB12">
         <v>1.25</v>
       </c>
       <c r="AC12">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="AD12">
         <v>1.02</v>
@@ -2319,7 +2319,7 @@
         <v>1.01</v>
       </c>
       <c r="AF12">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AG12">
         <v>1.43</v>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AK12">
         <v>1.48</v>
@@ -2428,10 +2428,10 @@
         </is>
       </c>
       <c r="N13">
-        <v>4.1</v>
+        <v>4.96</v>
       </c>
       <c r="O13">
-        <v>3.65</v>
+        <v>3.72</v>
       </c>
       <c r="P13">
         <v>1.72</v>
@@ -2440,7 +2440,7 @@
         <v>4.46</v>
       </c>
       <c r="R13">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="S13">
         <v>1.41</v>
@@ -2449,13 +2449,13 @@
         <v>2.73</v>
       </c>
       <c r="U13">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="V13">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W13">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X13">
         <v>1</v>
@@ -2467,16 +2467,16 @@
         <v>3.14</v>
       </c>
       <c r="AA13">
-        <v>2.03</v>
+        <v>2.09</v>
       </c>
       <c r="AB13">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AC13">
-        <v>3.42</v>
+        <v>3.59</v>
       </c>
       <c r="AD13">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AE13">
         <v>1.04</v>
@@ -2591,16 +2591,16 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="O14">
         <v>3</v>
       </c>
       <c r="P14">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="Q14">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="R14">
         <v>1.85</v>
@@ -2621,7 +2621,7 @@
         <v>0</v>
       </c>
       <c r="X14">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="Y14">
         <v>1.62</v>
@@ -2645,10 +2645,10 @@
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AG14">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK14">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>3.82</v>
+        <v>3.25</v>
       </c>
       <c r="O15">
+        <v>3.1</v>
+      </c>
+      <c r="P15">
+        <v>2.1</v>
+      </c>
+      <c r="Q15">
+        <v>4.1</v>
+      </c>
+      <c r="R15">
+        <v>2.05</v>
+      </c>
+      <c r="S15">
+        <v>1.47</v>
+      </c>
+      <c r="T15">
+        <v>2.44</v>
+      </c>
+      <c r="U15">
         <v>3.2</v>
       </c>
-      <c r="P15">
-        <v>1.8</v>
-      </c>
-      <c r="Q15">
-        <v>4.92</v>
-      </c>
-      <c r="R15">
-        <v>2.02</v>
-      </c>
-      <c r="S15">
-        <v>1.44</v>
-      </c>
-      <c r="T15">
-        <v>2.55</v>
-      </c>
-      <c r="U15">
-        <v>3.1</v>
-      </c>
       <c r="V15">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="W15">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X15">
+        <v>1.06</v>
+      </c>
+      <c r="Y15">
+        <v>1.39</v>
+      </c>
+      <c r="Z15">
+        <v>2.64</v>
+      </c>
+      <c r="AA15">
+        <v>2.2</v>
+      </c>
+      <c r="AB15">
+        <v>1.56</v>
+      </c>
+      <c r="AC15">
+        <v>4</v>
+      </c>
+      <c r="AD15">
+        <v>1.16</v>
+      </c>
+      <c r="AE15">
         <v>1.05</v>
       </c>
-      <c r="Y15">
-        <v>1.41</v>
-      </c>
-      <c r="Z15">
-        <v>2.7</v>
-      </c>
-      <c r="AA15">
-        <v>2.25</v>
-      </c>
-      <c r="AB15">
-        <v>1.57</v>
-      </c>
-      <c r="AC15">
-        <v>4.2</v>
-      </c>
-      <c r="AD15">
-        <v>1.18</v>
-      </c>
-      <c r="AE15">
-        <v>1.03</v>
-      </c>
       <c r="AF15">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="AG15">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.84</v>
+        <v>1.58</v>
       </c>
       <c r="AK15">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,19 +2917,19 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="O16">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P16">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="Q16">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="R16">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="S16">
         <v>1.37</v>
@@ -2938,43 +2938,43 @@
         <v>2.88</v>
       </c>
       <c r="U16">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="V16">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W16">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X16">
         <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z16">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="AA16">
         <v>2.05</v>
       </c>
       <c r="AB16">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC16">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AD16">
         <v>1.24</v>
       </c>
       <c r="AE16">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF16">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AG16">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="AK16">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="O17">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P17">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="Q17">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="R17">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="S17">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="T17">
-        <v>2.85</v>
+        <v>2.51</v>
       </c>
       <c r="U17">
-        <v>2.75</v>
+        <v>3.01</v>
       </c>
       <c r="V17">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="W17">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X17">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y17">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z17">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AA17">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AB17">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AC17">
-        <v>3.4</v>
+        <v>3.84</v>
       </c>
       <c r="AD17">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AE17">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF17">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG17">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="AK17">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="O18">
         <v>5.5</v>
       </c>
       <c r="P18">
-        <v>13</v>
+        <v>9.51</v>
       </c>
       <c r="Q18">
         <v>1.65</v>
       </c>
       <c r="R18">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="S18">
         <v>1.29</v>
       </c>
       <c r="T18">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U18">
-        <v>2.39</v>
+        <v>2.52</v>
       </c>
       <c r="V18">
         <v>1.5</v>
       </c>
       <c r="W18">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X18">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z18">
         <v>4.5</v>
       </c>
       <c r="AA18">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="AB18">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AC18">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="AD18">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE18">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF18">
-        <v>2.05</v>
+        <v>2.27</v>
       </c>
       <c r="AG18">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="AK18">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="O20">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="P20">
-        <v>5.03</v>
+        <v>5.79</v>
       </c>
       <c r="Q20">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="R20">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="S20">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="T20">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="U20">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="V20">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W20">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X20">
         <v>1.03</v>
       </c>
       <c r="Y20">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z20">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AA20">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB20">
         <v>1.7</v>
       </c>
       <c r="AC20">
-        <v>3.6</v>
+        <v>3.82</v>
       </c>
       <c r="AD20">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AE20">
         <v>1.05</v>
       </c>
       <c r="AF20">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AG20">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="AK20">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,52 +3732,52 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="O21">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="P21">
         <v>2.32</v>
       </c>
       <c r="Q21">
-        <v>3.7</v>
+        <v>4.13</v>
       </c>
       <c r="R21">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="S21">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="T21">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="U21">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="V21">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="W21">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X21">
         <v>1.05</v>
       </c>
       <c r="Y21">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Z21">
-        <v>2.65</v>
+        <v>2.54</v>
       </c>
       <c r="AA21">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="AB21">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AC21">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AD21">
         <v>1.17</v>
@@ -3789,7 +3789,7 @@
         <v>2</v>
       </c>
       <c r="AG21">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AK21">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="O22">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="P22">
-        <v>5.15</v>
+        <v>3.95</v>
       </c>
       <c r="Q22">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="R22">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S22">
         <v>1.3</v>
       </c>
       <c r="T22">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="U22">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="V22">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="W22">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X22">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z22">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AA22">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AB22">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="AC22">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="AD22">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="AE22">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF22">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AG22">
-        <v>1.9</v>
+        <v>2.16</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK22">
-        <v>2.31</v>
+        <v>2</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,28 +4058,28 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="O23">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="P23">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="Q23">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="R23">
         <v>2.3</v>
       </c>
       <c r="S23">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T23">
-        <v>3.15</v>
+        <v>2.89</v>
       </c>
       <c r="U23">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="V23">
         <v>1.48</v>
@@ -4088,34 +4088,34 @@
         <v>1.07</v>
       </c>
       <c r="X23">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y23">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z23">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AA23">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AB23">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="AC23">
         <v>2.8</v>
       </c>
       <c r="AD23">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AE23">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF23">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AG23">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK23">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,58 +4221,58 @@
         </is>
       </c>
       <c r="N24">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="O24">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="P24">
-        <v>2.49</v>
+        <v>2.37</v>
       </c>
       <c r="Q24">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R24">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="S24">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="T24">
         <v>4</v>
       </c>
       <c r="U24">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="V24">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="W24">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X24">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z24">
-        <v>6.86</v>
+        <v>6.31</v>
       </c>
       <c r="AA24">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB24">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="AC24">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AD24">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AE24">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AF24">
         <v>1.36</v>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AK24">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="O25">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P25">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="Q25">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="R25">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S25">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T25">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="U25">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="V25">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="W25">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X25">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y25">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z25">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA25">
-        <v>1.89</v>
+        <v>1.75</v>
       </c>
       <c r="AB25">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC25">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AD25">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE25">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF25">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AG25">
-        <v>2.03</v>
+        <v>2.11</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AK25">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="O26">
         <v>5.25</v>
       </c>
       <c r="P26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q26">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="R26">
         <v>2.44</v>
       </c>
       <c r="S26">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T26">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="U26">
-        <v>2.47</v>
+        <v>2.3</v>
       </c>
       <c r="V26">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="W26">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X26">
         <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z26">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="AA26">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AB26">
-        <v>1.97</v>
+        <v>2.12</v>
       </c>
       <c r="AC26">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="AD26">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AE26">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF26">
-        <v>2.19</v>
+        <v>1.91</v>
       </c>
       <c r="AG26">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AK26">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4719,52 +4719,52 @@
         <v>4.56</v>
       </c>
       <c r="Q27">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="R27">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="S27">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T27">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="U27">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="V27">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W27">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y27">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Z27">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AA27">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AB27">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AC27">
-        <v>2.88</v>
+        <v>2.81</v>
       </c>
       <c r="AD27">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AE27">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF27">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AG27">
         <v>1.91</v>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AK27">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5036,16 +5036,16 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="O29">
+        <v>3.2</v>
+      </c>
+      <c r="P29">
         <v>3</v>
       </c>
-      <c r="P29">
-        <v>2.6</v>
-      </c>
       <c r="Q29">
-        <v>3.25</v>
+        <v>3.02</v>
       </c>
       <c r="R29">
         <v>2.05</v>
@@ -5054,46 +5054,46 @@
         <v>1.46</v>
       </c>
       <c r="T29">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="U29">
-        <v>2.91</v>
+        <v>3.05</v>
       </c>
       <c r="V29">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="W29">
         <v>1.05</v>
       </c>
       <c r="X29">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y29">
         <v>1.4</v>
       </c>
       <c r="Z29">
-        <v>2.9</v>
+        <v>3.14</v>
       </c>
       <c r="AA29">
         <v>2.15</v>
       </c>
       <c r="AB29">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AC29">
-        <v>3.82</v>
+        <v>4</v>
       </c>
       <c r="AD29">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE29">
         <v>1.07</v>
       </c>
       <c r="AF29">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AG29">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>1.36</v>
       </c>
       <c r="AK29">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="O30">
         <v>3.5</v>
@@ -5208,25 +5208,25 @@
         <v>5</v>
       </c>
       <c r="Q30">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="R30">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="S30">
         <v>1.4</v>
       </c>
       <c r="T30">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="U30">
-        <v>3.09</v>
+        <v>3.18</v>
       </c>
       <c r="V30">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="W30">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X30">
         <v>1.06</v>
@@ -5238,25 +5238,25 @@
         <v>3.1</v>
       </c>
       <c r="AA30">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="AB30">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AC30">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AD30">
         <v>1.22</v>
       </c>
       <c r="AE30">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF30">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="AG30">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK30">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.15</v>
+        <v>2.62</v>
       </c>
       <c r="O38">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="P38">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="Q38">
-        <v>2.63</v>
+        <v>3.1</v>
       </c>
       <c r="R38">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="S38">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="T38">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="U38">
-        <v>2.55</v>
+        <v>2.29</v>
       </c>
       <c r="V38">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="W38">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X38">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y38">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="Z38">
-        <v>4</v>
+        <v>4.65</v>
       </c>
       <c r="AA38">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AB38">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AC38">
-        <v>2.8</v>
+        <v>2.23</v>
       </c>
       <c r="AD38">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="AE38">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AF38">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AG38">
-        <v>2.2</v>
+        <v>2.51</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK38">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.62</v>
+        <v>2.15</v>
       </c>
       <c r="O39">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="P39">
+        <v>3</v>
+      </c>
+      <c r="Q39">
+        <v>2.63</v>
+      </c>
+      <c r="R39">
         <v>2.2</v>
       </c>
-      <c r="Q39">
-        <v>3.1</v>
-      </c>
-      <c r="R39">
-        <v>2.35</v>
-      </c>
       <c r="S39">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="T39">
-        <v>3.7</v>
+        <v>3.05</v>
       </c>
       <c r="U39">
-        <v>2.29</v>
+        <v>2.55</v>
       </c>
       <c r="V39">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="W39">
+        <v>1.08</v>
+      </c>
+      <c r="X39">
+        <v>1.04</v>
+      </c>
+      <c r="Y39">
+        <v>1.24</v>
+      </c>
+      <c r="Z39">
+        <v>4</v>
+      </c>
+      <c r="AA39">
+        <v>1.7</v>
+      </c>
+      <c r="AB39">
+        <v>2.1</v>
+      </c>
+      <c r="AC39">
+        <v>2.8</v>
+      </c>
+      <c r="AD39">
+        <v>1.42</v>
+      </c>
+      <c r="AE39">
         <v>1.14</v>
       </c>
-      <c r="X39">
-        <v>1.03</v>
-      </c>
-      <c r="Y39">
-        <v>1.12</v>
-      </c>
-      <c r="Z39">
-        <v>4.65</v>
-      </c>
-      <c r="AA39">
-        <v>1.53</v>
-      </c>
-      <c r="AB39">
-        <v>2.4</v>
-      </c>
-      <c r="AC39">
-        <v>2.23</v>
-      </c>
-      <c r="AD39">
-        <v>1.56</v>
-      </c>
-      <c r="AE39">
-        <v>1.2</v>
-      </c>
       <c r="AF39">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="AG39">
-        <v>2.51</v>
+        <v>2.2</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK39">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,31 +6829,31 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.17</v>
+        <v>2.06</v>
       </c>
       <c r="O40">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="P40">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="Q40">
-        <v>2.93</v>
+        <v>2.81</v>
       </c>
       <c r="R40">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="S40">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="T40">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="U40">
         <v>3.5</v>
       </c>
       <c r="V40">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W40">
         <v>1.04</v>
@@ -6862,31 +6862,31 @@
         <v>1.06</v>
       </c>
       <c r="Y40">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="Z40">
+        <v>2.4</v>
+      </c>
+      <c r="AA40">
         <v>2.47</v>
       </c>
-      <c r="AA40">
-        <v>2.51</v>
-      </c>
       <c r="AB40">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AC40">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AD40">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AE40">
         <v>1.04</v>
       </c>
       <c r="AF40">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AG40">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6992,22 +6992,22 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="O41">
-        <v>4.35</v>
+        <v>4.6</v>
       </c>
       <c r="P41">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="Q41">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="R41">
-        <v>2.13</v>
+        <v>2.21</v>
       </c>
       <c r="S41">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T41">
         <v>2.9</v>
@@ -7019,28 +7019,28 @@
         <v>1.44</v>
       </c>
       <c r="W41">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X41">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y41">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z41">
-        <v>3.8</v>
+        <v>3.34</v>
       </c>
       <c r="AA41">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AB41">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AC41">
         <v>3.4</v>
       </c>
       <c r="AD41">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE41">
         <v>1.11</v>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AK41">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7653,19 +7653,19 @@
         <v>2.66</v>
       </c>
       <c r="Q45">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="R45">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="S45">
         <v>1.5</v>
       </c>
       <c r="T45">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="U45">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="V45">
         <v>1.22</v>
@@ -7674,22 +7674,22 @@
         <v>1.02</v>
       </c>
       <c r="X45">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y45">
         <v>1.53</v>
       </c>
       <c r="Z45">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AA45">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="AB45">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AC45">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="AD45">
         <v>1.16</v>
@@ -7698,10 +7698,10 @@
         <v>1.04</v>
       </c>
       <c r="AF45">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG45">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>1.4</v>
       </c>
       <c r="AK45">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AL45">
         <v>0</v>

--- a/jogos_2026-08-19.xlsx
+++ b/jogos_2026-08-19.xlsx
@@ -1264,26 +1264,26 @@
         </is>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6">
         <v>0</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["51", "86"]</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["28"]</t>
         </is>
       </c>
       <c r="AJ6">
@@ -1366,28 +1366,28 @@
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1427,26 +1427,26 @@
         </is>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
@@ -1511,12 +1511,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["50", "90+3"]</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["17", "81"]</t>
         </is>
       </c>
       <c r="AJ7">
@@ -1529,28 +1529,28 @@
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1590,36 +1590,36 @@
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
         <v>1.1</v>
       </c>
       <c r="O8">
-        <v>7.7</v>
+        <v>6.5</v>
       </c>
       <c r="P8">
-        <v>15.25</v>
+        <v>13</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1674,12 +1674,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["18", "51"]</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["72"]</t>
         </is>
       </c>
       <c r="AJ8">
@@ -1692,28 +1692,28 @@
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1916,26 +1916,26 @@
         </is>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["83"]</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["22"]</t>
         </is>
       </c>
       <c r="AJ10">
@@ -2079,26 +2079,26 @@
         </is>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["7", "21", "47", "90+3"]</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["65"]</t>
         </is>
       </c>
       <c r="AJ11">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
@@ -2405,26 +2405,26 @@
         </is>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I13">
         <v>0</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["52", "68", "90+2"]</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["20", "58"]</t>
         </is>
       </c>
       <c r="AJ13">
@@ -2507,28 +2507,28 @@
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN13">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AP13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>0.85</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -2568,10 +2568,10 @@
         </is>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -2580,14 +2580,14 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14">
@@ -2652,12 +2652,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["46"]</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["82"]</t>
         </is>
       </c>
       <c r="AJ14">
@@ -2731,26 +2731,26 @@
         </is>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["8", "50"]</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["29", "90+1"]</t>
         </is>
       </c>
       <c r="AJ15">
@@ -2833,28 +2833,28 @@
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP15">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
@@ -2894,26 +2894,26 @@
         </is>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H16">
         <v>0</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16">
         <v>0</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16">
         <v>0</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["23", "40", "57"]</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
@@ -2996,28 +2996,28 @@
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN16">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO16">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
@@ -3057,10 +3057,10 @@
         </is>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -3069,14 +3069,14 @@
         <v>0</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+6"]</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["51"]</t>
         </is>
       </c>
       <c r="AJ17">
@@ -3159,28 +3159,28 @@
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO17">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
@@ -3220,26 +3220,26 @@
         </is>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18">
         <v>0</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18">
         <v>0</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18">
         <v>0</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["21", "67"]</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
@@ -3322,28 +3322,28 @@
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN18">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO18">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AP18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N19">
@@ -3415,7 +3415,7 @@
         <v>4.5</v>
       </c>
       <c r="Q19">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="R19">
         <v>1.93</v>
@@ -3430,7 +3430,7 @@
         <v>3.4</v>
       </c>
       <c r="V19">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="W19">
         <v>1.05</v>
@@ -3442,7 +3442,7 @@
         <v>1.52</v>
       </c>
       <c r="Z19">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="AA19">
         <v>2.55</v>
@@ -3460,7 +3460,7 @@
         <v>1.04</v>
       </c>
       <c r="AF19">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AG19">
         <v>1.65</v>
@@ -3491,10 +3491,10 @@
         <v>-1</v>
       </c>
       <c r="AO19">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AP19">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AQ19">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
@@ -3546,10 +3546,10 @@
         </is>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -3558,14 +3558,14 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N20">
@@ -3630,12 +3630,12 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["61", "90+5"]</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["52"]</t>
         </is>
       </c>
       <c r="AJ20">
@@ -3648,28 +3648,28 @@
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO20">
-        <v>-1</v>
+        <v>22</v>
       </c>
       <c r="AP20">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N21">
@@ -3811,28 +3811,28 @@
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AN21">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO21">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AP21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>0.61</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
@@ -4687,26 +4687,26 @@
         </is>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27">
         <v>0</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N27">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["9"]</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["33", "53", "90+3"]</t>
         </is>
       </c>
       <c r="AJ27">
@@ -4789,28 +4789,28 @@
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP27">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ27">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AR27">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS27">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AT27">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
@@ -4873,31 +4873,31 @@
         </is>
       </c>
       <c r="N28">
+        <v>2.32</v>
+      </c>
+      <c r="O28">
+        <v>3.6</v>
+      </c>
+      <c r="P28">
         <v>2.48</v>
       </c>
-      <c r="O28">
-        <v>3.23</v>
-      </c>
-      <c r="P28">
-        <v>2.15</v>
-      </c>
       <c r="Q28">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="R28">
         <v>2.3</v>
       </c>
       <c r="S28">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="T28">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="U28">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="V28">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="W28">
         <v>1.11</v>
@@ -4918,19 +4918,19 @@
         <v>2.15</v>
       </c>
       <c r="AC28">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AD28">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE28">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AF28">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AG28">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK28">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,64 +5362,64 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.61</v>
+        <v>2.37</v>
       </c>
       <c r="O31">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="P31">
-        <v>4.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q31">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="R31">
         <v>2.3</v>
       </c>
       <c r="S31">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T31">
-        <v>3.04</v>
+        <v>3.8</v>
       </c>
       <c r="U31">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="V31">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="W31">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X31">
         <v>1.01</v>
       </c>
       <c r="Y31">
+        <v>1.15</v>
+      </c>
+      <c r="Z31">
+        <v>4.5</v>
+      </c>
+      <c r="AA31">
+        <v>1.5</v>
+      </c>
+      <c r="AB31">
+        <v>2.36</v>
+      </c>
+      <c r="AC31">
+        <v>2.42</v>
+      </c>
+      <c r="AD31">
+        <v>1.51</v>
+      </c>
+      <c r="AE31">
         <v>1.2</v>
       </c>
-      <c r="Z31">
-        <v>3.95</v>
-      </c>
-      <c r="AA31">
-        <v>1.73</v>
-      </c>
-      <c r="AB31">
-        <v>2.02</v>
-      </c>
-      <c r="AC31">
-        <v>2.74</v>
-      </c>
-      <c r="AD31">
-        <v>1.41</v>
-      </c>
-      <c r="AE31">
-        <v>1.13</v>
-      </c>
       <c r="AF31">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="AG31">
-        <v>2</v>
+        <v>2.46</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.13</v>
+        <v>1.43</v>
       </c>
       <c r="AK31">
-        <v>2.1</v>
+        <v>1.48</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.37</v>
+        <v>1.61</v>
       </c>
       <c r="O32">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P32">
-        <v>2.45</v>
+        <v>4.4</v>
       </c>
       <c r="Q32">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="R32">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="S32">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T32">
-        <v>3.5</v>
+        <v>3.04</v>
       </c>
       <c r="U32">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="V32">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="W32">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X32">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y32">
+        <v>1.2</v>
+      </c>
+      <c r="Z32">
+        <v>3.95</v>
+      </c>
+      <c r="AA32">
+        <v>1.7</v>
+      </c>
+      <c r="AB32">
+        <v>2.1</v>
+      </c>
+      <c r="AC32">
+        <v>2.74</v>
+      </c>
+      <c r="AD32">
+        <v>1.41</v>
+      </c>
+      <c r="AE32">
         <v>1.13</v>
       </c>
-      <c r="Z32">
-        <v>4.5</v>
-      </c>
-      <c r="AA32">
-        <v>1.5</v>
-      </c>
-      <c r="AB32">
-        <v>2.36</v>
-      </c>
-      <c r="AC32">
-        <v>2.42</v>
-      </c>
-      <c r="AD32">
-        <v>1.51</v>
-      </c>
-      <c r="AE32">
-        <v>1.18</v>
-      </c>
       <c r="AF32">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="AG32">
-        <v>2.46</v>
+        <v>1.99</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.43</v>
+        <v>1.13</v>
       </c>
       <c r="AK32">
-        <v>1.48</v>
+        <v>2.11</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5688,16 +5688,16 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="O33">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="P33">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="Q33">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="R33">
         <v>2.45</v>
@@ -5706,13 +5706,13 @@
         <v>1.25</v>
       </c>
       <c r="T33">
-        <v>3.6</v>
+        <v>3.42</v>
       </c>
       <c r="U33">
         <v>2.25</v>
       </c>
       <c r="V33">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W33">
         <v>1.15</v>
@@ -5721,19 +5721,19 @@
         <v>1.01</v>
       </c>
       <c r="Y33">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="Z33">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="AA33">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AB33">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="AC33">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="AD33">
         <v>1.5</v>
@@ -5745,7 +5745,7 @@
         <v>1.6</v>
       </c>
       <c r="AG33">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AK33">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,34 +5851,34 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="O34">
+        <v>3.96</v>
+      </c>
+      <c r="P34">
+        <v>2.84</v>
+      </c>
+      <c r="Q34">
+        <v>2.75</v>
+      </c>
+      <c r="R34">
+        <v>2.24</v>
+      </c>
+      <c r="S34">
+        <v>1.28</v>
+      </c>
+      <c r="T34">
         <v>3.6</v>
       </c>
-      <c r="P34">
-        <v>2.74</v>
-      </c>
-      <c r="Q34">
-        <v>2.7</v>
-      </c>
-      <c r="R34">
-        <v>2.21</v>
-      </c>
-      <c r="S34">
-        <v>1.3</v>
-      </c>
-      <c r="T34">
-        <v>3.3</v>
-      </c>
       <c r="U34">
-        <v>2.51</v>
+        <v>2.3</v>
       </c>
       <c r="V34">
         <v>1.5</v>
       </c>
       <c r="W34">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X34">
         <v>1.04</v>
@@ -5887,28 +5887,28 @@
         <v>1.2</v>
       </c>
       <c r="Z34">
-        <v>4.52</v>
+        <v>4.4</v>
       </c>
       <c r="AA34">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="AB34">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="AC34">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="AD34">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AE34">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF34">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG34">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -6014,31 +6014,31 @@
         </is>
       </c>
       <c r="N35">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="O35">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="P35">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="Q35">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="R35">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="S35">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T35">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="U35">
         <v>2</v>
       </c>
       <c r="V35">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="W35">
         <v>1.2</v>
@@ -6047,31 +6047,31 @@
         <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z35">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="AA35">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AB35">
-        <v>3.1</v>
+        <v>3.17</v>
       </c>
       <c r="AC35">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AD35">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AE35">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AF35">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AG35">
-        <v>2.98</v>
+        <v>3.08</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AK35">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,16 +6177,16 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="O36">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="P36">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="Q36">
-        <v>2.9</v>
+        <v>3.06</v>
       </c>
       <c r="R36">
         <v>2.63</v>
@@ -6195,16 +6195,16 @@
         <v>1.2</v>
       </c>
       <c r="T36">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="U36">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="V36">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="W36">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X36">
         <v>1.01</v>
@@ -6219,13 +6219,13 @@
         <v>1.33</v>
       </c>
       <c r="AB36">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="AC36">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AD36">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AE36">
         <v>1.33</v>
@@ -6250,7 +6250,7 @@
         <v>1.24</v>
       </c>
       <c r="AK36">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>DC United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>New England Revolution</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.94</v>
+        <v>2.4</v>
       </c>
       <c r="O37">
-        <v>4.43</v>
+        <v>3.3</v>
       </c>
       <c r="P37">
-        <v>3.42</v>
+        <v>2.5</v>
       </c>
       <c r="Q37">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="R37">
-        <v>2.41</v>
+        <v>2.2</v>
       </c>
       <c r="S37">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="T37">
+        <v>3.05</v>
+      </c>
+      <c r="U37">
+        <v>2.55</v>
+      </c>
+      <c r="V37">
+        <v>1.5</v>
+      </c>
+      <c r="W37">
+        <v>1.08</v>
+      </c>
+      <c r="X37">
+        <v>1.04</v>
+      </c>
+      <c r="Y37">
+        <v>1.2</v>
+      </c>
+      <c r="Z37">
         <v>4</v>
       </c>
-      <c r="U37">
-        <v>2.01</v>
-      </c>
-      <c r="V37">
-        <v>1.69</v>
-      </c>
-      <c r="W37">
+      <c r="AA37">
+        <v>1.7</v>
+      </c>
+      <c r="AB37">
+        <v>2.1</v>
+      </c>
+      <c r="AC37">
+        <v>2.8</v>
+      </c>
+      <c r="AD37">
+        <v>1.42</v>
+      </c>
+      <c r="AE37">
         <v>1.14</v>
       </c>
-      <c r="X37">
-        <v>1.02</v>
-      </c>
-      <c r="Y37">
-        <v>1.08</v>
-      </c>
-      <c r="Z37">
-        <v>6</v>
-      </c>
-      <c r="AA37">
-        <v>1.42</v>
-      </c>
-      <c r="AB37">
-        <v>2.76</v>
-      </c>
-      <c r="AC37">
-        <v>2.1</v>
-      </c>
-      <c r="AD37">
-        <v>1.7</v>
-      </c>
-      <c r="AE37">
-        <v>1.3</v>
-      </c>
       <c r="AF37">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AG37">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AK37">
-        <v>1.8</v>
+        <v>1.47</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>New York RB</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>2.62</v>
+        <v>1.87</v>
       </c>
       <c r="O38">
-        <v>3.75</v>
+        <v>4.52</v>
       </c>
       <c r="P38">
-        <v>2.2</v>
+        <v>3.61</v>
       </c>
       <c r="Q38">
-        <v>3.1</v>
+        <v>2.34</v>
       </c>
       <c r="R38">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="S38">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T38">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="U38">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="V38">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="W38">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X38">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="Z38">
-        <v>4.65</v>
+        <v>6.1</v>
       </c>
       <c r="AA38">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AB38">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="AC38">
-        <v>2.23</v>
+        <v>1.99</v>
       </c>
       <c r="AD38">
-        <v>1.56</v>
+        <v>1.72</v>
       </c>
       <c r="AE38">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AF38">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AG38">
-        <v>2.51</v>
+        <v>2.8</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK38">
-        <v>1.36</v>
+        <v>1.85</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>DC United</t>
+          <t>New York RB</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>New England Revolution</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,65 +6666,65 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.15</v>
+        <v>2.6</v>
       </c>
       <c r="O39">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P39">
-        <v>3</v>
+        <v>2.28</v>
       </c>
       <c r="Q39">
+        <v>3.1</v>
+      </c>
+      <c r="R39">
+        <v>2.35</v>
+      </c>
+      <c r="S39">
+        <v>1.2</v>
+      </c>
+      <c r="T39">
+        <v>3.6</v>
+      </c>
+      <c r="U39">
+        <v>2.27</v>
+      </c>
+      <c r="V39">
+        <v>1.6</v>
+      </c>
+      <c r="W39">
+        <v>1.14</v>
+      </c>
+      <c r="X39">
+        <v>1.03</v>
+      </c>
+      <c r="Y39">
+        <v>1.16</v>
+      </c>
+      <c r="Z39">
+        <v>4.7</v>
+      </c>
+      <c r="AA39">
+        <v>1.53</v>
+      </c>
+      <c r="AB39">
+        <v>2.4</v>
+      </c>
+      <c r="AC39">
+        <v>2.23</v>
+      </c>
+      <c r="AD39">
+        <v>1.58</v>
+      </c>
+      <c r="AE39">
+        <v>1.21</v>
+      </c>
+      <c r="AF39">
+        <v>1.44</v>
+      </c>
+      <c r="AG39">
         <v>2.63</v>
       </c>
-      <c r="R39">
-        <v>2.2</v>
-      </c>
-      <c r="S39">
-        <v>1.33</v>
-      </c>
-      <c r="T39">
-        <v>3.05</v>
-      </c>
-      <c r="U39">
-        <v>2.55</v>
-      </c>
-      <c r="V39">
-        <v>1.48</v>
-      </c>
-      <c r="W39">
-        <v>1.08</v>
-      </c>
-      <c r="X39">
-        <v>1.04</v>
-      </c>
-      <c r="Y39">
-        <v>1.24</v>
-      </c>
-      <c r="Z39">
-        <v>4</v>
-      </c>
-      <c r="AA39">
-        <v>1.7</v>
-      </c>
-      <c r="AB39">
-        <v>2.1</v>
-      </c>
-      <c r="AC39">
-        <v>2.8</v>
-      </c>
-      <c r="AD39">
-        <v>1.42</v>
-      </c>
-      <c r="AE39">
-        <v>1.14</v>
-      </c>
-      <c r="AF39">
-        <v>1.61</v>
-      </c>
-      <c r="AG39">
-        <v>2.2</v>
-      </c>
       <c r="AH39" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7164,55 +7164,55 @@
         <v>4.37</v>
       </c>
       <c r="Q42">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="R42">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="S42">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="T42">
-        <v>3.12</v>
+        <v>3.28</v>
       </c>
       <c r="U42">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V42">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W42">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X42">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y42">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z42">
-        <v>3.84</v>
+        <v>4.2</v>
       </c>
       <c r="AA42">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AB42">
-        <v>2.04</v>
+        <v>2.19</v>
       </c>
       <c r="AC42">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AD42">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE42">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF42">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AG42">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AK42">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>3.07</v>
+        <v>3.95</v>
       </c>
       <c r="O43">
-        <v>3.67</v>
+        <v>3.6</v>
       </c>
       <c r="P43">
         <v>1.9</v>
       </c>
       <c r="Q43">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="R43">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="S43">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T43">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="U43">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="V43">
         <v>1.63</v>
       </c>
       <c r="W43">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X43">
         <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="Z43">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="AA43">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="AB43">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AC43">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AD43">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AE43">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF43">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AG43">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>1.18</v>
       </c>
       <c r="AK43">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7481,13 +7481,13 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="O44">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="P44">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="Q44">
         <v>2.25</v>
@@ -7496,65 +7496,65 @@
         <v>2.3</v>
       </c>
       <c r="S44">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T44">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U44">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="V44">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W44">
         <v>1.12</v>
       </c>
       <c r="X44">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y44">
         <v>1.2</v>
       </c>
       <c r="Z44">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AA44">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AB44">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="AC44">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="AD44">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AE44">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF44">
         <v>1.58</v>
       </c>
       <c r="AG44">
+        <v>2.25</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ44">
+        <v>1.16</v>
+      </c>
+      <c r="AK44">
         <v>2.1</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ44">
-        <v>1.25</v>
-      </c>
-      <c r="AK44">
-        <v>1.95</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7807,31 +7807,31 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="O46">
         <v>3.6</v>
       </c>
       <c r="P46">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="Q46">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="R46">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="S46">
         <v>1.22</v>
       </c>
       <c r="T46">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="U46">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="V46">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W46">
         <v>1.12</v>
@@ -7840,7 +7840,7 @@
         <v>1.03</v>
       </c>
       <c r="Y46">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="Z46">
         <v>5.44</v>
@@ -7852,10 +7852,10 @@
         <v>2.63</v>
       </c>
       <c r="AC46">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AD46">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AE46">
         <v>1.22</v>
@@ -7864,7 +7864,7 @@
         <v>1.44</v>
       </c>
       <c r="AG46">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7970,28 +7970,28 @@
         </is>
       </c>
       <c r="N47">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="O47">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="P47">
-        <v>4.3</v>
+        <v>4.14</v>
       </c>
       <c r="Q47">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="R47">
         <v>2.4</v>
       </c>
       <c r="S47">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T47">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="U47">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="V47">
         <v>1.58</v>
@@ -8000,25 +8000,25 @@
         <v>1.13</v>
       </c>
       <c r="X47">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y47">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z47">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AA47">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB47">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC47">
-        <v>2.49</v>
+        <v>2.54</v>
       </c>
       <c r="AD47">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AE47">
         <v>1.2</v>
@@ -8040,7 +8040,7 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AK47">
         <v>2.15</v>
@@ -8133,25 +8133,25 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.72</v>
+        <v>2.46</v>
       </c>
       <c r="O48">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P48">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q48">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="R48">
         <v>2.25</v>
       </c>
       <c r="S48">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T48">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="U48">
         <v>2.5</v>
@@ -8160,7 +8160,7 @@
         <v>1.44</v>
       </c>
       <c r="W48">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X48">
         <v>1.04</v>
@@ -8169,7 +8169,7 @@
         <v>1.22</v>
       </c>
       <c r="Z48">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AA48">
         <v>1.75</v>
@@ -8178,35 +8178,35 @@
         <v>2.25</v>
       </c>
       <c r="AC48">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="AD48">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE48">
         <v>1.11</v>
       </c>
       <c r="AF48">
+        <v>1.55</v>
+      </c>
+      <c r="AG48">
+        <v>2.38</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ48">
+        <v>1.25</v>
+      </c>
+      <c r="AK48">
         <v>1.53</v>
-      </c>
-      <c r="AG48">
-        <v>2.3</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ48">
-        <v>1.3</v>
-      </c>
-      <c r="AK48">
-        <v>1.4</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.51</v>
+        <v>2.36</v>
       </c>
       <c r="O49">
         <v>3.3</v>
@@ -8308,22 +8308,22 @@
         <v>3.18</v>
       </c>
       <c r="R49">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S49">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T49">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U49">
         <v>2.63</v>
       </c>
       <c r="V49">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="W49">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X49">
         <v>1.01</v>
@@ -8332,7 +8332,7 @@
         <v>1.27</v>
       </c>
       <c r="Z49">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="AA49">
         <v>1.8</v>
@@ -8347,7 +8347,7 @@
         <v>1.36</v>
       </c>
       <c r="AE49">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF49">
         <v>1.65</v>
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="O50">
-        <v>4.33</v>
+        <v>4.05</v>
       </c>
       <c r="P50">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="Q50">
         <v>1.95</v>
       </c>
       <c r="R50">
-        <v>2.69</v>
+        <v>2.57</v>
       </c>
       <c r="S50">
         <v>1.25</v>
       </c>
       <c r="T50">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U50">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="V50">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="W50">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X50">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y50">
+        <v>1.18</v>
+      </c>
+      <c r="Z50">
+        <v>4.5</v>
+      </c>
+      <c r="AA50">
+        <v>1.62</v>
+      </c>
+      <c r="AB50">
+        <v>2.15</v>
+      </c>
+      <c r="AC50">
+        <v>2.59</v>
+      </c>
+      <c r="AD50">
+        <v>1.48</v>
+      </c>
+      <c r="AE50">
         <v>1.14</v>
       </c>
-      <c r="Z50">
-        <v>5.25</v>
-      </c>
-      <c r="AA50">
-        <v>1.52</v>
-      </c>
-      <c r="AB50">
-        <v>2.48</v>
-      </c>
-      <c r="AC50">
-        <v>2.33</v>
-      </c>
-      <c r="AD50">
-        <v>1.58</v>
-      </c>
-      <c r="AE50">
-        <v>1.23</v>
-      </c>
       <c r="AF50">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AG50">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AK50">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,7 +8622,7 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="O51">
         <v>3.83</v>
@@ -8631,28 +8631,28 @@
         <v>2.55</v>
       </c>
       <c r="Q51">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="R51">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S51">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T51">
         <v>4</v>
       </c>
       <c r="U51">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="V51">
         <v>1.68</v>
       </c>
       <c r="W51">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
         <v>1.13</v>
@@ -8661,25 +8661,25 @@
         <v>6</v>
       </c>
       <c r="AA51">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AB51">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="AC51">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AD51">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AE51">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AF51">
         <v>1.4</v>
       </c>
       <c r="AG51">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AK51">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,31 +8785,31 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="O52">
-        <v>4</v>
+        <v>4.44</v>
       </c>
       <c r="P52">
-        <v>2.99</v>
+        <v>3.16</v>
       </c>
       <c r="Q52">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="R52">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="S52">
         <v>1.19</v>
       </c>
       <c r="T52">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="U52">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V52">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="W52">
         <v>1.2</v>
@@ -8821,28 +8821,28 @@
         <v>1.1</v>
       </c>
       <c r="Z52">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AA52">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB52">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AC52">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AD52">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="AE52">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AF52">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AG52">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         <v>1.33</v>
       </c>
       <c r="AK52">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="AL52">
         <v>0</v>
